--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="367">
   <si>
     <r>
       <rPr>
@@ -176,7 +176,24 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">판정</t>
+      <t xml:space="preserve">변형 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종 — 판정</t>
     </r>
     <r>
       <rPr>
@@ -193,7 +210,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">피해</t>
+      <t xml:space="preserve">부가 능력</t>
     </r>
     <r>
       <rPr>
@@ -210,7 +227,29 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">부가 능력</t>
+      <t xml:space="preserve">이펙트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(data/scoring.json)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">사기주사위</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">면 구성</t>
     </r>
     <r>
       <rPr>
@@ -227,29 +266,29 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이펙트 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(data/scoring.json)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">사기주사위</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">면 구성</t>
+      <t xml:space="preserve">특수 규칙 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(data/dice.json)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">유물</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">효과</t>
     </r>
     <r>
       <rPr>
@@ -266,29 +305,29 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">특수 규칙 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(data/dice.json)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">유물</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">효과</t>
+      <t xml:space="preserve">훅 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(data/relics.json)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">적</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개체 스탯</t>
     </r>
     <r>
       <rPr>
@@ -305,45 +344,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">훅 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(data/relics.json)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">적</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개체 스탯</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">패턴 </t>
     </r>
     <r>
@@ -378,7 +378,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v0.6 </t>
+      <t xml:space="preserve">v0.8 </t>
     </r>
     <r>
       <rPr>
@@ -522,16 +522,33 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">레벨캡 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
+      <t xml:space="preserve">족보 변형제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">레벨 없음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -705,1688 +722,2166 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">족보 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">변형 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">id</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">변형 이름</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부가 능력</t>
+  </si>
+  <si>
+    <t xml:space="preserve">변형 등급</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시작</t>
+  </si>
+  <si>
+    <t xml:space="preserve">성립 조건</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피해</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대상</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EV(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">참고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">이펙트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">예시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">찬스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instinct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">떠돌이의 직감</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부가 없음 — 언제나 믿을 수 있는 한 수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">common</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◎</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조건 없음 — 항상 성립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가장 높은 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개의 합만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상위 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개의 합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">단일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">베기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚅ ⚄ ⚂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">whisper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">숲의 속삭임</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 턴 리롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">uncommon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">에이스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">needle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">바늘 한 땀</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">굴린 주사위 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 합만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[1] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈의 합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚀ ⚀ ⚀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silver_needle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">은바늘</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">twos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">듀스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cloak_hem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">붉은 망토 자락</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">굴린 주사위 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 합만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[2] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈의 합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚁ ⚁ ⚁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thorn_fence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가시 울타리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+7</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">threes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">트레이</t>
+  </si>
+  <si>
+    <t xml:space="preserve">herbs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">약초 한 줌</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">굴린 주사위 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[3]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 합만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[3] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈의 합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3†</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚂ ⚂ ⚂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">berry_jam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">산딸기 잼</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">fours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oak_shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">참나무 방패</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점수</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">굴린 주사위 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[4]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 합만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[4] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈의 합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4†</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚃ ⚃ ⚃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iron_pot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무쇠 냄비</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+9</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">파이브</t>
+  </si>
+  <si>
+    <t xml:space="preserve">powder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화약 재기</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 족보 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">굴린 주사위 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[5]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 합만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[5] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈의 합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6†</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚄ ⚄ ⚄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">five_claws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다섯 발톱</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+3 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 턴 리롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">sixes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">식스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wolfshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">늑대 사냥탄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부가 없음 — 순수 화력</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">굴린 주사위 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[6]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 합만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[6] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈의 합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚅ ⚅ ⚅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화약 과적</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 족보 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+8</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">threeKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">트리플</t>
+  </si>
+  <si>
+    <t xml:space="preserve">triple_axe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">세 번 찍는 도끼</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 족보 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 이상이면 성립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그 같은 눈들의 합 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 눈들의 합 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자 이중 베기</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">woodsman_breath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">나무꾼의 호흡</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 턴 리롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">fourKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">four_fangs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">네 개의 송곳니</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피해 준 적의 다음 행동 취소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rare</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 이상이면 성립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">그 같은 눈들의 합 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">충격파</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">베기</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">⚃ ⚃ ⚃ ⚃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heavy_blow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">묵직한 일격</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 족보 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+12</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">fullHouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">풀하우스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cottage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">할머니의 오두막</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+15</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다른 같은 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 5·5·5·2·2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">면 성립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금빛 파문</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚄ ⚄ ⚄ ⚁ ⚁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hearth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">따뜻한 화덕</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">smallStraight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스몰 스트레이트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">windpath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">바람길</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이번 적 공격 회피</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연속된 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 2·3·4·5)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">면 성립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모든 적에게 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빛의 파도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">⚁ ⚂ ⚃ ⚄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunt_drive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">몰이사냥</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+10</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">largeStraight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라지 스트레이트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moonpath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">달빛 오솔길</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회피 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 턴 리롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연속된 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1~5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">또는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2~6)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">면 성립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모든 적에게 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">교차 파도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">섬광</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">⚁ ⚂ ⚃ ⚄ ⚅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">storm_run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭풍 질주</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회피 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+8</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">yahtzee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">야찌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">judgment_night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">심판의 밤</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적 행동 취소 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주사위 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개가 모두 같은 눈이면 성립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">심판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">섬광</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이중 파문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">⚅ ⚅ ⚅ ⚅ ⚅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blood_moon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">핏빛 만월</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적 행동 취소 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+15</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
     <t xml:space="preserve">이름</t>
   </si>
   <si>
-    <t xml:space="preserve">분류</t>
-  </si>
-  <si>
-    <t xml:space="preserve">성립 조건</t>
-  </si>
-  <si>
-    <t xml:space="preserve">피해</t>
-  </si>
-  <si>
-    <t xml:space="preserve">대상</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부가 능력</t>
-  </si>
-  <si>
-    <t xml:space="preserve">레벨 규칙</t>
-  </si>
-  <si>
-    <t xml:space="preserve">시작</t>
+    <t xml:space="preserve">면 구성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">특수 규칙</t>
   </si>
   <si>
     <t xml:space="preserve">등급</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFF5EBD8"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EV(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFF5EBD8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">참고</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFF5EBD8"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">이펙트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">예시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">찬스</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조건 없음 — 항상 성립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가장 높은 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개의 합만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상위 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개의 합</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">단일</t>
-  </si>
-  <si>
-    <t xml:space="preserve">언제나 성립</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+2/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">레벨</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">○</t>
-  </si>
-  <si>
-    <t xml:space="preserve">common</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">베기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚅ ⚄ ⚂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">에이스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upper</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">굴린 주사위 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 합만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[1] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈의 합</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다음 턴 리롤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">레벨</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚀ ⚀ ⚀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">twos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">듀스</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">굴린 주사위 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 합만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[2] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈의 합</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×2</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚁ ⚁ ⚁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">threes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">트레이</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">굴린 주사위 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[3]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 합만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[3] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈의 합</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HP 3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회복</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3†</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚂ ⚂ ⚂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포스</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">굴린 주사위 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[4]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 합만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[4] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈의 합</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점수</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4†</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚃ ⚃ ⚃</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">파이브</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">굴린 주사위 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[5]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 합만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[5] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈의 합</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다음 족보 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+5</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6†</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚄ ⚄ ⚄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sixes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">식스</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">굴린 주사위 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[6]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 합만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[6] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈의 합</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">부가 없음 — 순수 화력</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚅ ⚅ ⚅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">threeKind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">트리플</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ofKind</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">같은 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 이상이면 성립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그 같은 눈들의 합 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">같은 눈들의 합 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">해제 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">디버프 개편 예정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자 이중 베기</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">fourKind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포카드</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">같은 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 이상이면 성립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그 같은 눈들의 합 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">적 다음 행동 취소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">충격파</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">베기</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">⚃ ⚃ ⚃ ⚃</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fullHouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">풀하우스</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">같은 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다른 같은 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 5·5·5·2·2)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">면 성립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">25.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+15</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">uncommon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">금빛 파문</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚄ ⚄ ⚄ ⚁ ⚁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smallStraight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">스몰 스트레이트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">straight</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연속된 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 2·3·4·5)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">면 성립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모든 적에게 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전체</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이번 적 공격 회피</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빛의 파도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">⚁ ⚂ ⚃ ⚄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">largeStraight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">라지 스트레이트</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연속된 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(1~5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">또는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2~6)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">면 성립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모든 적에게 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">40.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회피 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다음 턴 리롤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">교차 파도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">섬광</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">⚁ ⚂ ⚃ ⚄ ⚅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yahtzee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">야찌</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주사위 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개가 모두 같은 눈이면 성립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">적 행동 취소 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">심판</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">섬광</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이중 파문</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">⚅ ⚅ ⚅ ⚅ ⚅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">면 구성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">특수 규칙</t>
   </si>
   <si>
     <t xml:space="preserve">설명</t>
@@ -3961,7 +4456,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FFA02C25"/>
+      <color rgb="FF2F5B8C"/>
       <name val="Malgun Gothic"/>
       <family val="0"/>
       <charset val="1"/>
@@ -3969,7 +4464,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF2F5B8C"/>
+      <color rgb="FFA02C25"/>
       <name val="Malgun Gothic"/>
       <family val="0"/>
       <charset val="1"/>
@@ -4117,11 +4612,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4129,7 +4620,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4435,7 +4930,7 @@
       </c>
       <c r="C5" s="4" t="n">
         <f aca="false">COUNTA(족보!A2:A100)</f>
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4512,93 +5007,94 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M1" s="3" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+      <c r="B2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="10" t="s">
         <v>32</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="4" t="s">
         <v>38</v>
       </c>
       <c r="K2" s="9" t="s">
@@ -4611,476 +5107,983 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="E3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="F3" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>47</v>
-      </c>
+      <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>40</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="J4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>52</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>56</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>40</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>59</v>
+        <v>46</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>62</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>40</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>66</v>
+        <v>57</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>69</v>
+      <c r="G6" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>40</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>73</v>
+        <v>57</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="5"/>
-      <c r="J7" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>38</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>40</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>80</v>
+        <v>69</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>81</v>
+        <v>71</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>72</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>83</v>
-      </c>
+      <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>38</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>40</v>
       </c>
       <c r="M8" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
+      <c r="F10" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="I10" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="J10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="L10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="5" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="D11" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" s="11" t="s">
+      <c r="G12" s="4"/>
+      <c r="H12" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="K9" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="L9" s="11" t="s">
+      <c r="K12" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="M9" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="B13" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="13" t="s">
+      <c r="C13" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="I13" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="J13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K13" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="L13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M13" s="11" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="5"/>
-      <c r="J13" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B18" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="C18" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="D18" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="E18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="K14" s="9" t="s">
+      <c r="G23" s="5"/>
+      <c r="H23" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F24" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="L14" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>136</v>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -5112,162 +6115,162 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>18</v>
+        <v>196</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>138</v>
+        <v>198</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>26</v>
+        <v>199</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>139</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>144</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>146</v>
+        <v>207</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>147</v>
+        <v>208</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>148</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>149</v>
+        <v>210</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>150</v>
+        <v>211</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>151</v>
+        <v>212</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>152</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>153</v>
+        <v>214</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>154</v>
+        <v>215</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>155</v>
+        <v>216</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>107</v>
+        <v>204</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>45</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>156</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>158</v>
+        <v>219</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>160</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>161</v>
+        <v>222</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>162</v>
+        <v>223</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>163</v>
+        <v>224</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>164</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>167</v>
+        <v>228</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>168</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -5299,142 +6302,142 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>18</v>
+        <v>196</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>26</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>172</v>
+        <v>233</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>173</v>
+        <v>234</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>175</v>
+        <v>236</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>98</v>
+        <v>237</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>177</v>
+        <v>238</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>179</v>
+        <v>240</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>107</v>
+        <v>242</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>183</v>
+        <v>244</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>184</v>
+        <v>245</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>185</v>
+        <v>246</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>186</v>
+        <v>247</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>187</v>
+        <v>248</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>188</v>
+        <v>249</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>189</v>
+        <v>250</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>190</v>
+        <v>251</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>191</v>
+        <v>252</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>193</v>
+        <v>254</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>194</v>
+        <v>255</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>196</v>
+        <v>257</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>198</v>
+        <v>259</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>199</v>
+        <v>260</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>200</v>
+        <v>261</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>107</v>
+        <v>262</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -5468,53 +6471,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>202</v>
+        <v>263</v>
       </c>
       <c r="B1" s="18" t="n">
         <v>0.1</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>203</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>18</v>
+        <v>196</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>205</v>
+        <v>266</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>206</v>
+        <v>267</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>207</v>
+        <v>268</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>208</v>
+        <v>269</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>209</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>210</v>
+        <v>271</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
       <c r="E3" s="4" t="n">
         <f aca="false">ROUND(37*(1+$B$1*10),0)</f>
@@ -5524,7 +6527,7 @@
         <v>3</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>213</v>
+        <v>274</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>1</v>
@@ -5532,16 +6535,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>214</v>
+        <v>275</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>215</v>
+        <v>276</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>216</v>
+        <v>277</v>
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">ROUND(34*(1+$B$1*10),0)</f>
@@ -5551,7 +6554,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>1</v>
@@ -5559,16 +6562,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>218</v>
+        <v>279</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>219</v>
+        <v>280</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>220</v>
+        <v>281</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">ROUND(40*(1+$B$1*10),0)</f>
@@ -5578,7 +6581,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>221</v>
+        <v>282</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>1</v>
@@ -5586,16 +6589,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>222</v>
+        <v>283</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>223</v>
+        <v>284</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>224</v>
+        <v>285</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">ROUND(44*(1+$B$1*10),0)</f>
@@ -5605,7 +6608,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>225</v>
+        <v>286</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>1</v>
@@ -5613,16 +6616,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>226</v>
+        <v>287</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>228</v>
+        <v>289</v>
       </c>
       <c r="E7" s="4" t="n">
         <f aca="false">ROUND(47*(1+$B$1*10),0)</f>
@@ -5632,7 +6635,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>229</v>
+        <v>290</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>1</v>
@@ -5640,16 +6643,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>230</v>
+        <v>291</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>231</v>
+        <v>292</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="E8" s="5" t="n">
         <f aca="false">ROUND(55*(1+$B$1*10),0)</f>
@@ -5659,7 +6662,7 @@
         <v>3</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>1</v>
@@ -5667,16 +6670,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>235</v>
+        <v>296</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="E9" s="4" t="n">
         <f aca="false">ROUND(70*(1+$B$1*10),0)</f>
@@ -5686,7 +6689,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>1</v>
@@ -5694,16 +6697,16 @@
     </row>
     <row r="10" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>240</v>
+        <v>301</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>241</v>
+        <v>302</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>242</v>
+        <v>303</v>
       </c>
       <c r="E10" s="5" t="n">
         <f aca="false">ROUND(115*(1+$B$1*10),0)</f>
@@ -5713,7 +6716,7 @@
         <v>5</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>243</v>
+        <v>304</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>2</v>
@@ -5748,542 +6751,542 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>244</v>
+        <v>305</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>245</v>
+        <v>306</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>246</v>
+        <v>307</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>247</v>
+        <v>308</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>169</v>
+        <v>230</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>248</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>210</v>
+        <v>271</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>251</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>210</v>
+        <v>271</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>252</v>
+        <v>313</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>253</v>
+        <v>314</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>254</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>210</v>
+        <v>271</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>255</v>
+        <v>316</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>256</v>
+        <v>317</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>214</v>
+        <v>275</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>215</v>
+        <v>276</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>258</v>
+        <v>319</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>259</v>
+        <v>320</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>260</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>214</v>
+        <v>275</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>215</v>
+        <v>276</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>261</v>
+        <v>322</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>214</v>
+        <v>275</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>215</v>
+        <v>276</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>263</v>
+        <v>324</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>264</v>
+        <v>325</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>265</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>218</v>
+        <v>279</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>219</v>
+        <v>280</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>266</v>
+        <v>327</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>267</v>
+        <v>328</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>260</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>218</v>
+        <v>279</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>219</v>
+        <v>280</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>268</v>
+        <v>329</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>269</v>
+        <v>330</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>218</v>
+        <v>279</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>219</v>
+        <v>280</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>270</v>
+        <v>331</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>265</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>222</v>
+        <v>283</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>223</v>
+        <v>284</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>266</v>
+        <v>327</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>272</v>
+        <v>333</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>254</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>222</v>
+        <v>283</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>223</v>
+        <v>284</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>273</v>
+        <v>334</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>274</v>
+        <v>335</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>222</v>
+        <v>283</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>223</v>
+        <v>284</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>275</v>
+        <v>336</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>277</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>226</v>
+        <v>287</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>278</v>
+        <v>339</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>279</v>
+        <v>340</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>260</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>226</v>
+        <v>287</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>280</v>
+        <v>341</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>281</v>
+        <v>342</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>226</v>
+        <v>287</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>227</v>
+        <v>288</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>282</v>
+        <v>343</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>283</v>
+        <v>344</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>284</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>230</v>
+        <v>291</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>231</v>
+        <v>292</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>285</v>
+        <v>346</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>286</v>
+        <v>347</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>287</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>230</v>
+        <v>291</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>231</v>
+        <v>292</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>288</v>
+        <v>349</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>289</v>
+        <v>350</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>230</v>
+        <v>291</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>231</v>
+        <v>292</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>290</v>
+        <v>351</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>292</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>235</v>
+        <v>296</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>266</v>
+        <v>327</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>272</v>
+        <v>333</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>265</v>
+        <v>326</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>235</v>
+        <v>296</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>293</v>
+        <v>354</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>294</v>
+        <v>355</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>235</v>
+        <v>296</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>295</v>
+        <v>356</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>296</v>
+        <v>357</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>297</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>240</v>
+        <v>301</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>266</v>
+        <v>327</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>272</v>
+        <v>333</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>298</v>
+        <v>359</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>240</v>
+        <v>301</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>293</v>
+        <v>354</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>294</v>
+        <v>355</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>240</v>
+        <v>301</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>299</v>
+        <v>360</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>300</v>
+        <v>361</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>240</v>
+        <v>301</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>301</v>
+        <v>362</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>302</v>
+        <v>363</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>240</v>
+        <v>301</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>304</v>
+        <v>365</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>305</v>
+        <v>366</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>292</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -14,6 +14,8 @@
     <sheet name="유물" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="적" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="적행동" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="무기" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="대화이벤트" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="461">
   <si>
     <r>
       <rPr>
@@ -378,7 +380,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">v0.8 </t>
+      <t xml:space="preserve">v0.10 </t>
     </r>
     <r>
       <rPr>
@@ -522,33 +524,109 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">족보 변형제</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">레벨 없음</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">족보 변형 누적 수집 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등급 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">체계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(common/uncommon/rare(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보라</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)/epic(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시작 족보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무기 선택</t>
     </r>
   </si>
   <si>
@@ -777,9 +855,6 @@
     <t xml:space="preserve">변형 등급</t>
   </si>
   <si>
-    <t xml:space="preserve">시작</t>
-  </si>
-  <si>
     <t xml:space="preserve">성립 조건</t>
   </si>
   <si>
@@ -847,9 +922,6 @@
     <t xml:space="preserve">common</t>
   </si>
   <si>
-    <t xml:space="preserve">◎</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2664,6 +2736,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">epic</t>
+  </si>
+  <si>
     <t xml:space="preserve">yahtzee</t>
   </si>
   <si>
@@ -2878,7 +2953,10 @@
     <t xml:space="preserve">면 구성</t>
   </si>
   <si>
-    <t xml:space="preserve">특수 규칙</t>
+    <t xml:space="preserve">효과 유형</t>
+  </si>
+  <si>
+    <t xml:space="preserve">효과</t>
   </si>
   <si>
     <t xml:space="preserve">등급</t>
@@ -2918,13 +2996,219 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">납 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 2 · 3 · 4 · 6 · 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 눈금형</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대신 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 하나 더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 잘 나온다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">even</t>
+  </si>
+  <si>
+    <t xml:space="preserve">짝눈 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 · 2 · 4 · 4 · 6 · 6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">짝수만 나온다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">odd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">홀눈 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 1 · 3 · 3 · 5 · 5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">홀수만 나온다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">높은 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 · 4 · 4 · 5 · 5 · 6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">낮은 눈이 없다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">외눈 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 1 · 1 · 1 · 1 · 6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">거의 항상 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에이스 빌드의 심장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">gold</t>
   </si>
   <si>
     <t xml:space="preserve">금박 주사위</t>
   </si>
   <si>
-    <t xml:space="preserve">기여 시 자기 눈만큼 추가 피해</t>
+    <t xml:space="preserve">② 기여 시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">자기 눈만큼 추가 피해</t>
   </si>
   <si>
     <r>
@@ -2946,65 +3230,75 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">납 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 · 2 · 3 · 4 · 6 · 6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대신 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이 하나 더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. 6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이 잘 나온다</t>
+    <t xml:space="preserve">cursed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저주 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 1 · 6 · 6 · 6 · 6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자신에게 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">탐스러운 눈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">족보에 기여하면 나도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피해를 받는다</t>
     </r>
     <r>
       <rPr>
@@ -3017,22 +3311,64 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">even</t>
-  </si>
-  <si>
-    <t xml:space="preserve">짝눈 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 · 2 · 4 · 4 · 6 · 6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">짝수만 나온다</t>
+    <t xml:space="preserve">fang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">송곳니 주사위</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">족보에 기여하면 피를 마셔 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복</t>
     </r>
     <r>
       <rPr>
@@ -3045,22 +3381,167 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">odd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">홀눈 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 · 1 · 3 · 3 · 5 · 5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">홀수만 나온다</t>
+    <t xml:space="preserve">straw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">밀짚 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 1 · 2 · 2 · 3 · 3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">③ 확정 시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기여 무관</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈은 낮지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기여하지 않아도 족보를 확정할 때마다 방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ember</t>
+  </si>
+  <si>
+    <t xml:space="preserve">잿불 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 · 2 · 3 · 3 · 4 · 4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">족보를 확정할 때마다 온기가 스민다 — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복</t>
     </r>
     <r>
       <rPr>
@@ -3073,80 +3554,118 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">ace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">외눈 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 · 1 · 1 · 1 · 1 · 6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">거의 항상 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에이스 빌드의 심장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">high</t>
-  </si>
-  <si>
-    <t xml:space="preserve">높은 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 · 4 · 4 · 5 · 5 · 6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">낮은 눈이 없다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">효과</t>
+    <t xml:space="preserve">moonlit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">달빛 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 1 · 2 · 3 · 4 · 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">④ 패시브</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리롤 추가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈은 흐릿하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">달빛이 손을 이끈다 — 매 턴 리롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">bramble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가시덤불 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 2 · 2 · 3 · 3 · 4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">턴 시작 방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">품고만 있어도 가시가 돋는다 — 매 턴 시작 시 방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
   </si>
   <si>
     <r>
@@ -4346,6 +4865,1454 @@
   </si>
   <si>
     <t xml:space="preserve">갈기갈기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">컨셉</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시작 족보</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">변형</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">gun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔫 사냥꾼의 총</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">멀리서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">크게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한 방</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">떠돌이의 직감</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">찬스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">늑대 사냥탄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">식스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">묵직한 일격</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">포카드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">scythe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🗡️ 녹슨 낫</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">숲을 베어 넘기는 큰 호선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">떠돌이의 직감</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">찬스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">세 번 찍는 도끼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트리플</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">몰이사냥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스몰 스트레이트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">lantern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏮 붉은 랜턴</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">어둠을 밀어내고 숨을 고른다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">숲의 속삭임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">찬스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">약초 한 줌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트레이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">할머니의 오두막</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">풀하우스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">shovel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⛏️ 무덤지기의 삽</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">막고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">버틴다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">떠돌이의 직감</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">찬스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">참나무 방패</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">포스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가시 울타리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">듀스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">crossbow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🏹 물푸레 쇠뇌</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조용히 재고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정확히 맞힌다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">떠돌이의 직감</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">찬스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">화약 재기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파이브</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">바람길</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스몰 스트레이트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">dagger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔪 빵칼 단검</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">작고 빠른 손놀림의 연속</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">숲의 속삭임</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">찬스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">바늘 한 땀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에이스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">붉은 망토 자락</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">듀스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시작 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 무작위 제안 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모든 세트에 찬스 계열 포함</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">소프트락 방지</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이벤트 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">id</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">선택지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">결과 대사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ash_crone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🧓 잿빛 노파</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🧪 검은 물약을 마신다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">쓰디쓴 물약이 상처를 봉한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">🩸 피의 거래</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">감소 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무작위 유물</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노파가 웃으며 보따리에서 무언가를 꺼내 쥐여 준다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">🚪 조용히 지나친다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">노파의 시선이 등 뒤에 오래 남는다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">signpost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🪧 부러진 이정표</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🪓 밑동을 파헤친다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무작위 족보 변형</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기름먹인 천에 싸인 낡은 두루마리 조각이 나왔다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">🙏 무사한 여행을 빈다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">최대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">몸이 조금 단단해진 기분이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">🚶 갈 길을 간다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">바람이 이정표를 삐걱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">흔들었다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">altar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🕯️ 이끼 낀 제단</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🙇 무릎 꿇고 기도한다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">촛불이 한 번 크게 흔들리고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">통증이 가라앉았다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">🎲 제물을 훔친다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무작위 주사위</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">교체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">제단 위의 주사위가 손안에서 차갑게 식어 있다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">🚶 떠난다</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">돌아보지 않는 편이 좋을 것 같았다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -4355,7 +6322,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4464,7 +6431,15 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FFA02C25"/>
+      <color rgb="FF7D5BA6"/>
+      <name val="Malgun Gothic"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFB08948"/>
       <name val="Malgun Gothic"/>
       <family val="0"/>
       <charset val="1"/>
@@ -4559,7 +6534,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4628,11 +6603,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4697,8 +6680,8 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF7D5BA6"/>
+      <rgbColor rgb="FFB08948"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -4942,7 +6925,7 @@
       </c>
       <c r="C6" s="5" t="n">
         <f aca="false">COUNTA(사기주사위!A2:A100)</f>
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5007,7 +6990,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -5016,13 +6999,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5053,1037 +7035,1002 @@
       <c r="I1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="3" t="s">
         <v>26</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="9" t="s">
         <v>39</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="C3" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="H3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="E4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="K4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C5" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>56</v>
-      </c>
       <c r="F5" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="K5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="D6" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="E6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="F6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="H6" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="4" t="s">
+      <c r="I6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="K6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>68</v>
-      </c>
       <c r="F7" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="K7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" s="11" t="s">
         <v>63</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="D8" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="F8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="H8" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="K8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="9" t="s">
         <v>75</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C9" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>80</v>
-      </c>
       <c r="F9" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="K9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="D10" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="E10" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="F10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="H10" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4" t="s">
+      <c r="I10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="K10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="9" t="s">
         <v>87</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>92</v>
-      </c>
       <c r="F11" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="K11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11" s="11" t="s">
         <v>87</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="D12" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="E12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="F12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="H12" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="K12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C13" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>104</v>
-      </c>
       <c r="F13" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="K13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="11" t="s">
         <v>99</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="D14" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="E14" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="F14" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="H14" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4" t="s">
+      <c r="I14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="K14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>116</v>
-      </c>
       <c r="F15" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="K15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L15" s="11" t="s">
         <v>111</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K15" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="M15" s="11" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="D16" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="E16" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="F16" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="4" t="s">
+      <c r="I16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="K16" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="L16" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>128</v>
-      </c>
       <c r="F17" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G17" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>120</v>
+      </c>
       <c r="H17" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="K17" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="J17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>124</v>
-      </c>
       <c r="L17" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="D18" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="E18" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="F18" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="H18" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4" t="s">
+      <c r="K18" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K18" s="9" t="s">
+      <c r="L18" s="9" t="s">
         <v>136</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>141</v>
-      </c>
       <c r="F19" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G19" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>133</v>
+      </c>
       <c r="H19" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="K19" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K19" s="11" t="s">
+      <c r="L19" s="11" t="s">
         <v>136</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="M19" s="11" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="D20" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="E20" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="F20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="H20" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4" t="s">
+      <c r="I20" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="K20" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="J20" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K20" s="9" t="s">
+      <c r="L20" s="9" t="s">
         <v>149</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C21" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>154</v>
-      </c>
       <c r="F21" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J21" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="K21" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="J21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K21" s="11" t="s">
+      <c r="L21" s="11" t="s">
         <v>149</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="M21" s="11" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="D22" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="E22" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="F22" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="H22" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F22" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4" t="s">
+      <c r="I22" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="J22" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="K22" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="L22" s="9" t="s">
         <v>163</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="F23" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="I23" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="J23" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="K23" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="K23" s="11" t="s">
+      <c r="L23" s="11" t="s">
         <v>163</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="D24" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="E24" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="F24" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="H24" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="F24" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4" t="s">
+      <c r="I24" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="K24" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="J24" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="K24" s="9" t="s">
+      <c r="L24" s="9" t="s">
         <v>176</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="F25" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5" t="s">
+      <c r="G25" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="J25" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="K25" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="J25" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="K25" s="11" t="s">
+      <c r="L25" s="11" t="s">
         <v>176</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="M25" s="11" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="C26" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="D26" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="E26" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="F26" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="F26" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="I26" s="9" t="s">
+      <c r="I26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="J26" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K26" s="9" t="s">
+      <c r="K26" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="L26" s="4" t="s">
+      <c r="L26" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>183</v>
-      </c>
       <c r="C27" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="D27" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="E27" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5" t="s">
+      <c r="F27" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="H27" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J27" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="J27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K27" s="11" t="s">
+      <c r="K27" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="L27" s="5" t="s">
+      <c r="L27" s="11" t="s">
         <v>190</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -6102,34 +8049,38 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>200</v>
       </c>
     </row>
@@ -6147,13 +8098,16 @@
         <v>204</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
         <v>206</v>
       </c>
@@ -6161,116 +8115,272 @@
         <v>207</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F3" s="5" t="s">
         <v>209</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="D4" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="E4" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>213</v>
+      <c r="F4" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="D5" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>217</v>
+      <c r="F5" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="D6" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>221</v>
+      <c r="F6" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="D7" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="E7" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F7" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>229</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -6302,19 +8412,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="C1" s="3" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>199</v>
@@ -6322,122 +8432,122 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>236</v>
+        <v>268</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>269</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>241</v>
+        <v>273</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>45</v>
+        <v>274</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>251</v>
+        <v>283</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>252</v>
+        <v>284</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>254</v>
+        <v>286</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>256</v>
+        <v>288</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>258</v>
+        <v>290</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>259</v>
+        <v>291</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>261</v>
+        <v>293</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -6470,54 +8580,54 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="B1" s="18" t="n">
+      <c r="A1" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="B1" s="20" t="n">
         <v>0.1</v>
       </c>
-      <c r="C1" s="19" t="s">
-        <v>264</v>
+      <c r="C1" s="21" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="C2" s="3" t="s">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>268</v>
+        <v>300</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>201</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>273</v>
+        <v>305</v>
       </c>
       <c r="E3" s="4" t="n">
         <f aca="false">ROUND(37*(1+$B$1*10),0)</f>
@@ -6527,7 +8637,7 @@
         <v>3</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>1</v>
@@ -6535,16 +8645,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>201</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>277</v>
+        <v>309</v>
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">ROUND(34*(1+$B$1*10),0)</f>
@@ -6554,7 +8664,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>1</v>
@@ -6562,16 +8672,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>201</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>281</v>
+        <v>313</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">ROUND(40*(1+$B$1*10),0)</f>
@@ -6581,7 +8691,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>1</v>
@@ -6589,16 +8699,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>283</v>
+        <v>315</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>201</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>285</v>
+        <v>317</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">ROUND(44*(1+$B$1*10),0)</f>
@@ -6608,7 +8718,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>1</v>
@@ -6616,16 +8726,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>201</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="E7" s="4" t="n">
         <f aca="false">ROUND(47*(1+$B$1*10),0)</f>
@@ -6635,7 +8745,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>290</v>
+        <v>322</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>1</v>
@@ -6643,16 +8753,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>201</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="E8" s="5" t="n">
         <f aca="false">ROUND(55*(1+$B$1*10),0)</f>
@@ -6662,7 +8772,7 @@
         <v>3</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>1</v>
@@ -6670,16 +8780,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>298</v>
+        <v>330</v>
       </c>
       <c r="E9" s="4" t="n">
         <f aca="false">ROUND(70*(1+$B$1*10),0)</f>
@@ -6689,7 +8799,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>299</v>
+        <v>331</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>1</v>
@@ -6697,16 +8807,16 @@
     </row>
     <row r="10" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>302</v>
+        <v>334</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="E10" s="5" t="n">
         <f aca="false">ROUND(115*(1+$B$1*10),0)</f>
@@ -6716,7 +8826,7 @@
         <v>5</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>304</v>
+        <v>336</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>2</v>
@@ -6751,79 +8861,79 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>306</v>
+        <v>338</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>307</v>
+        <v>339</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>308</v>
+        <v>340</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>314</v>
+        <v>346</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>315</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>317</v>
+        <v>349</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>204</v>
@@ -6831,39 +8941,39 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>204</v>
@@ -6871,59 +8981,59 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>204</v>
@@ -6931,59 +9041,59 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>280</v>
+        <v>312</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>283</v>
+        <v>315</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>315</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>283</v>
+        <v>315</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>204</v>
@@ -6991,59 +9101,59 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>283</v>
+        <v>315</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>339</v>
+        <v>371</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>341</v>
+        <v>373</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>342</v>
+        <v>374</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>204</v>
@@ -7051,59 +9161,59 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>343</v>
+        <v>375</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>346</v>
+        <v>378</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>347</v>
+        <v>379</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>349</v>
+        <v>381</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>318</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>204</v>
@@ -7111,59 +9221,59 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>291</v>
+        <v>323</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>353</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>204</v>
@@ -7171,59 +9281,59 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>295</v>
+        <v>327</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>359</v>
+        <v>391</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>204</v>
@@ -7231,19 +9341,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>361</v>
+        <v>393</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>204</v>
@@ -7251,42 +9361,365 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>362</v>
+        <v>394</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>364</v>
+        <v>396</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>366</v>
+        <v>398</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>353</v>
+        <v>385</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>426</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>460</v>
       </c>
     </row>
   </sheetData>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="487">
   <si>
     <r>
       <rPr>
@@ -4216,7 +4216,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">[peck:3, dive:2, circle:1] · 2</t>
+      <t xml:space="preserve">[peck:3, dive:2, caw:2] · 2</t>
     </r>
     <r>
       <rPr>
@@ -4423,7 +4423,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: slam → root → crush (</t>
+      <t xml:space="preserve">: slam → root → crush → mend (</t>
     </r>
     <r>
       <rPr>
@@ -4545,7 +4545,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: bite → howl → pounce (</t>
+      <t xml:space="preserve">: bite → stalk → pounce (</t>
     </r>
     <r>
       <rPr>
@@ -4596,7 +4596,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">[bite:2, rend:3, pounce:1, howl:1] · 2</t>
+      <t xml:space="preserve">[rend:3, bite:2, howl:2, lick:1, pounce:1] · 2</t>
     </r>
     <r>
       <rPr>
@@ -4669,7 +4669,26 @@
     <t xml:space="preserve">쪼기</t>
   </si>
   <si>
-    <t xml:space="preserve">5</t>
+    <t xml:space="preserve">⚔️공격</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">️공격 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">dive</t>
@@ -4678,39 +4697,149 @@
     <t xml:space="preserve">급강하</t>
   </si>
   <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">circle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">선회</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">준비</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">행동 없음</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">️공격 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">caw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어지러운 날갯짓</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">⚔️공격 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ 🌀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">혼란</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">️공격 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">혼란 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">scorch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">지지기</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">️공격 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">flicker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">명멸</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">❓의문 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(💪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강화</t>
     </r>
     <r>
       <rPr>
@@ -4723,19 +4852,23 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">scorch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">지지기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flicker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">명멸</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강화 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">flare</t>
@@ -4744,7 +4877,23 @@
     <t xml:space="preserve">불꽃 폭발</t>
   </si>
   <si>
-    <t xml:space="preserve">11</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">️공격 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">bite</t>
@@ -4759,6 +4908,28 @@
     <t xml:space="preserve">거미줄</t>
   </si>
   <si>
+    <t xml:space="preserve">🌀혼란</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">혼란 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">ambush</t>
   </si>
   <si>
@@ -4768,19 +4939,120 @@
     <t xml:space="preserve">물어뜯기</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">️공격 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">growl</t>
   </si>
   <si>
     <t xml:space="preserve">으르렁</t>
   </si>
   <si>
+    <t xml:space="preserve">💪강화</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강화 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">maul</t>
   </si>
   <si>
     <t xml:space="preserve">사냥</t>
   </si>
   <si>
-    <t xml:space="preserve">14</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">⚔️공격 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ 💪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강화</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">️공격 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강화 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">scratch</t>
@@ -4795,13 +5067,92 @@
     <t xml:space="preserve">가시 세우기</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">🛡방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ 🌀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">혼란</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">혼란 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">lash</t>
   </si>
   <si>
     <t xml:space="preserve">덩굴 채찍</t>
   </si>
   <si>
-    <t xml:space="preserve">13</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">️공격 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">slam</t>
@@ -4810,22 +5161,85 @@
     <t xml:space="preserve">내리찍기</t>
   </si>
   <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
     <t xml:space="preserve">root</t>
   </si>
   <si>
     <t xml:space="preserve">뿌리내림</t>
   </si>
   <si>
+    <t xml:space="preserve">🛡방어</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">crush</t>
   </si>
   <si>
     <t xml:space="preserve">짓뭉개기</t>
   </si>
   <si>
-    <t xml:space="preserve">16</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">️공격 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">mend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">수액 빨아올리기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">💚치료</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">치료 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">howl</t>
@@ -4834,22 +5248,187 @@
     <t xml:space="preserve">울부짖음</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">🛡방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ 💪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강화</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강화 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">frenzy</t>
   </si>
   <si>
     <t xml:space="preserve">광란</t>
   </si>
   <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lurk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">웅크리기</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">️공격 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">stalk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어둠 속 발소리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">❓의문 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(🛡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ 💪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강화 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">pounce</t>
@@ -4858,13 +5437,120 @@
     <t xml:space="preserve">덮치기</t>
   </si>
   <si>
-    <t xml:space="preserve">22</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">️공격 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">핏빛 울부짖음</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">💪강화 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ 🌀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">혼란</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">강화 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">혼란 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">rend</t>
   </si>
   <si>
     <t xml:space="preserve">갈기갈기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상처 핥기</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">치료 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">무기</t>
@@ -6961,7 +7647,7 @@
       </c>
       <c r="C9" s="4" t="n">
         <f aca="false">COUNTA(적행동!A2:A200)</f>
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8769,7 +9455,7 @@
         <v>110</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>326</v>
@@ -8823,7 +9509,7 @@
         <v>230</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>336</v>
@@ -8848,15 +9534,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8893,10 +9579,10 @@
         <v>343</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="9" t="s">
         <v>344</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8907,16 +9593,16 @@
         <v>304</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>347</v>
+        <v>344</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8927,16 +9613,16 @@
         <v>304</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>204</v>
+        <v>351</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8947,16 +9633,16 @@
         <v>308</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>353</v>
+        <v>344</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8967,16 +9653,16 @@
         <v>308</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>204</v>
+        <v>358</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8987,16 +9673,16 @@
         <v>308</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>358</v>
+        <v>344</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9007,16 +9693,16 @@
         <v>312</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>353</v>
+        <v>344</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9027,16 +9713,16 @@
         <v>312</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>204</v>
+        <v>367</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9047,16 +9733,16 @@
         <v>312</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>358</v>
+        <v>344</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9067,16 +9753,16 @@
         <v>316</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>347</v>
+        <v>344</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9087,16 +9773,16 @@
         <v>316</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>204</v>
+        <v>375</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9107,16 +9793,16 @@
         <v>316</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>370</v>
+        <v>379</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9127,16 +9813,16 @@
         <v>320</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>353</v>
+        <v>344</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9147,16 +9833,16 @@
         <v>320</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>204</v>
+        <v>385</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9167,16 +9853,16 @@
         <v>320</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>377</v>
+        <v>344</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9187,16 +9873,16 @@
         <v>324</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>380</v>
+        <v>344</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9207,16 +9893,16 @@
         <v>324</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>204</v>
+        <v>394</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9227,36 +9913,36 @@
         <v>324</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>385</v>
+        <v>344</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>359</v>
+        <v>399</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>365</v>
+        <v>400</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>358</v>
+        <v>401</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9267,16 +9953,16 @@
         <v>328</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>204</v>
+        <v>344</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9287,36 +9973,36 @@
         <v>328</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>390</v>
+        <v>405</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>359</v>
+        <v>407</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>365</v>
+        <v>408</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>391</v>
+        <v>344</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9327,16 +10013,16 @@
         <v>333</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>204</v>
+        <v>344</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9347,16 +10033,16 @@
         <v>333</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>204</v>
+        <v>412</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9367,16 +10053,16 @@
         <v>333</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>396</v>
+        <v>344</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9387,16 +10073,56 @@
         <v>333</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D27" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>385</v>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -9429,102 +10155,102 @@
         <v>194</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>401</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>413</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>426</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -9554,172 +10280,172 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>198</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>430</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>435</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>437</v>
+        <v>463</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>438</v>
+        <v>464</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>204</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>440</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>447</v>
+        <v>473</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>204</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>204</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="488">
   <si>
     <r>
       <rPr>
@@ -649,7 +649,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(EV)</t>
+      <t xml:space="preserve">(EV)=</t>
     </r>
     <r>
       <rPr>
@@ -659,7 +659,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">는 몬테카를로 </t>
+      <t xml:space="preserve">몬테카를로 </t>
     </r>
     <r>
       <rPr>
@@ -701,7 +701,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">전용 리롤 전략</t>
+      <t xml:space="preserve">전용 전략</t>
     </r>
     <r>
       <rPr>
@@ -712,7 +712,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve">) </t>
     </r>
     <r>
       <rPr>
@@ -722,7 +722,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">일반 주사위 </t>
+      <t xml:space="preserve">측정</t>
     </r>
     <r>
       <rPr>
@@ -733,7 +733,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">5</t>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -743,7 +743,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">개</t>
+      <t xml:space="preserve">능력 제외</t>
     </r>
     <r>
       <rPr>
@@ -754,7 +754,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) </t>
+      <t xml:space="preserve">. v0.12 </t>
     </r>
     <r>
       <rPr>
@@ -764,7 +764,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">측정값</t>
+      <t xml:space="preserve">밸런스</t>
     </r>
     <r>
       <rPr>
@@ -775,7 +775,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. †</t>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
@@ -785,7 +785,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">표시는 측정치에서 보간</t>
+      <t xml:space="preserve">변형 턴가치 </t>
     </r>
     <r>
       <rPr>
@@ -796,3267 +796,3357 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFF5EBD8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">족보 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFF5EBD8"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">id</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFF5EBD8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">변형 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFF5EBD8"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">id</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">변형 이름</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부가 능력</t>
-  </si>
-  <si>
-    <t xml:space="preserve">변형 등급</t>
-  </si>
-  <si>
-    <t xml:space="preserve">성립 조건</t>
-  </si>
-  <si>
-    <t xml:space="preserve">피해</t>
-  </si>
-  <si>
-    <t xml:space="preserve">대상</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFF5EBD8"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EV(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFF5EBD8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">참고</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFF5EBD8"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">이펙트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">예시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">찬스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instinct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">떠돌이의 직감</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부가 없음 — 언제나 믿을 수 있는 한 수</t>
-  </si>
-  <si>
-    <t xml:space="preserve">common</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">조건 없음 — 항상 성립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가장 높은 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개의 합만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상위 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개의 합</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">단일</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">베기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚅ ⚄ ⚂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">whisper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">숲의 속삭임</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다음 턴 리롤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">uncommon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">에이스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">needle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">바늘 한 땀</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">굴린 주사위 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[1]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 합만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[1] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈의 합</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚀ ⚀ ⚀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silver_needle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">은바늘</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HP 2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회복</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">twos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">듀스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cloak_hem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">붉은 망토 자락</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">굴린 주사위 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[2]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 합만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[2] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈의 합</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚁ ⚁ ⚁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thorn_fence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가시 울타리</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+7</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">threes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">트레이</t>
-  </si>
-  <si>
-    <t xml:space="preserve">herbs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">약초 한 줌</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HP 3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회복</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">굴린 주사위 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[3]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 합만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[3] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈의 합</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3†</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚂ ⚂ ⚂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">berry_jam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">산딸기 잼</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HP 2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회복 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">fours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oak_shield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">참나무 방패</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">점수</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">굴린 주사위 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[4]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 합만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[4] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈의 합</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4†</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚃ ⚃ ⚃</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iron_pot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">무쇠 냄비</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+9</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">파이브</t>
-  </si>
-  <si>
-    <t xml:space="preserve">powder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화약 재기</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다음 족보 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">굴린 주사위 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[5]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 합만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[5] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈의 합</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6†</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚄ ⚄ ⚄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">five_claws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">다섯 발톱</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다음 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+3 + </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다음 턴 리롤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">sixes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">식스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wolfshot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">늑대 사냥탄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">부가 없음 — 순수 화력</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">굴린 주사위 중 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[6]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">의 합만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[6] </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈의 합</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚅ ⚅ ⚅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">overload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화약 과적</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다음 족보 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+8</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">threeKind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">트리플</t>
-  </si>
-  <si>
-    <t xml:space="preserve">triple_axe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">세 번 찍는 도끼</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다음 족보 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">같은 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 이상이면 성립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그 같은 눈들의 합 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">같은 눈들의 합 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×2</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자 이중 베기</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">woodsman_breath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">나무꾼의 호흡</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4 + </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다음 턴 리롤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">fourKind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">포카드</t>
-  </si>
-  <si>
-    <t xml:space="preserve">four_fangs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">네 개의 송곳니</t>
-  </si>
-  <si>
-    <t xml:space="preserve">피해 준 적의 다음 행동 취소</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rare</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">같은 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 이상이면 성립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">그 같은 눈들의 합 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">만큼 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">충격파</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">베기</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">⚃ ⚃ ⚃ ⚃</t>
-  </si>
-  <si>
-    <t xml:space="preserve">heavy_blow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">묵직한 일격</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다음 족보 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+12</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">fullHouse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">풀하우스</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cottage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">할머니의 오두막</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+15</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">같은 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다른 같은 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 5·5·5·2·2)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">면 성립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">25.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">금빛 파문</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚄ ⚄ ⚄ ⚁ ⚁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hearth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">따뜻한 화덕</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HP 6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회복 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">smallStraight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">스몰 스트레이트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">windpath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">바람길</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이번 적 공격 회피</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연속된 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">예</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 2·3·4·5)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">면 성립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모든 적에게 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전체</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">빛의 파도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">⚁ ⚂ ⚃ ⚄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hunt_drive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">몰이사냥</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+10</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">largeStraight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">라지 스트레이트</t>
-  </si>
-  <si>
-    <t xml:space="preserve">moonpath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">달빛 오솔길</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회피 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다음 턴 리롤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연속된 눈 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(1~5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">또는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2~6)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">면 성립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">모든 적에게 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">40.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">교차 파도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">섬광</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전체</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">⚁ ⚂ ⚃ ⚄ ⚅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">storm_run</t>
-  </si>
-  <si>
-    <t xml:space="preserve">폭풍 질주</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회피 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다음 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+8</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">epic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yahtzee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">야찌</t>
-  </si>
-  <si>
-    <t xml:space="preserve">judgment_night</t>
-  </si>
-  <si>
-    <t xml:space="preserve">심판의 밤</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">적 행동 취소 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주사위 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">개가 모두 같은 눈이면 성립</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">심판</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">섬광</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이중 파문</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">⚅ ⚅ ⚅ ⚅ ⚅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blood_moon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">핏빛 만월</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">적 행동 취소 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">다음 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+15</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">이름</t>
-  </si>
-  <si>
-    <t xml:space="preserve">면 구성</t>
-  </si>
-  <si>
-    <t xml:space="preserve">효과 유형</t>
-  </si>
-  <si>
-    <t xml:space="preserve">효과</t>
-  </si>
-  <si>
-    <t xml:space="preserve">등급</t>
-  </si>
-  <si>
-    <t xml:space="preserve">설명</t>
-  </si>
-  <si>
-    <t xml:space="preserve">normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">나무 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 · 2 · 3 · 4 · 5 · 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">평범한 주사위</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">납 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 · 2 · 3 · 4 · 6 · 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">① 눈금형</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대신 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이 하나 더</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. 6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이 잘 나온다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">even</t>
-  </si>
-  <si>
-    <t xml:space="preserve">짝눈 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 · 2 · 4 · 4 · 6 · 6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">짝수만 나온다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">odd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">홀눈 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 · 1 · 3 · 3 · 5 · 5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">홀수만 나온다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">high</t>
-  </si>
-  <si>
-    <t xml:space="preserve">높은 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 · 4 · 4 · 5 · 5 · 6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">낮은 눈이 없다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">외눈 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 · 1 · 1 · 1 · 1 · 6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">거의 항상 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에이스 빌드의 심장</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">금박 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">② 기여 시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">자기 눈만큼 추가 피해</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">족보에 기여하면 자기 눈만큼 추가 피해</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">cursed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">저주 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 · 1 · 6 · 6 · 6 · 6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자신에게 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">탐스러운 눈</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">족보에 기여하면 나도 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">피해를 받는다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">fang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">송곳니 주사위</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HP </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회복 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">족보에 기여하면 피를 마셔 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HP 2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회복</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">straw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">밀짚 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 · 1 · 2 · 2 · 3 · 3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">③ 확정 시</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기여 무관</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">방어 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈은 낮지만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기여하지 않아도 족보를 확정할 때마다 방어 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ember</t>
-  </si>
-  <si>
-    <t xml:space="preserve">잿불 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 · 2 · 3 · 3 · 4 · 4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HP </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회복 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">족보를 확정할 때마다 온기가 스민다 — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HP 1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회복</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">moonlit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">달빛 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 · 1 · 2 · 3 · 4 · 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">④ 패시브</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">리롤 추가 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">눈은 흐릿하지만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">달빛이 손을 이끈다 — 매 턴 리롤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">bramble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가시덤불 주사위</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 · 2 · 2 · 3 · 3 · 4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">턴 시작 방어 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">품고만 있어도 가시가 돋는다 — 매 턴 시작 시 방어 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFF5EBD8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">훅</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFF5EBD8"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFF5EBD8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">엔진</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFF5EBD8"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">파라미터</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silver_bullet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🔫 은탄환</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에이스 족보 점수 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">categoryMult</t>
-  </si>
-  <si>
-    <t xml:space="preserve">category=ones, mult=5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">red_cloak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🧣 붉은 망토</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">매 턴 리롤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">extraReroll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amount=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hunters_charm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🪬 사냥꾼의 부적</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">풀하우스 점수 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+15.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">categoryBonus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">category=fullHouse, bonus=15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wolf_fang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🦷 늑대 이빨</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">족보를 확정할 때마다 추가 피해 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+3.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">flatDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amount=3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">breadcrumbs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🍞 빵부스러기</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전투에서 승리하면 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HP 4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회복</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">healOnVictory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amount=4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ledger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📒 가계부</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상단 보너스 발동 기준 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">40 → 30.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">upperBonusThreshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value=30</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">층당 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HP </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">배율</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">):</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">14.6~22.2 </t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF7A5C38"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">← act1.json hpScalePerFloor. </t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정렬 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF7A5C38"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">파란 글씨</t>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF7A5C38"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">야찌</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF7A5C38"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">입력값 </t>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF7A5C38"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(11</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">잭팟 예외</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF7A5C38"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">층 실효 </t>
-    </r>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">족보 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">변형 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">id</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">변형 이름</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부가 능력</t>
+  </si>
+  <si>
+    <t xml:space="preserve">변형 등급</t>
+  </si>
+  <si>
+    <t xml:space="preserve">성립 조건</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피해</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대상</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EV(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">참고</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">이펙트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">예시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">찬스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instinct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">떠돌이의 직감</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부가 없음 — 언제나 믿을 수 있는 한 수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">common</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">조건 없음 — 항상 성립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가장 높은 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개의 합만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상위 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개의 합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">단일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">베기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚅ ⚄ ⚂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">whisper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">숲의 속삭임</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 턴 리롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">uncommon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">에이스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">needle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">바늘 한 땀</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 턴 리롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">굴린 주사위 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[1]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 합만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[1] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈의 합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚀ ⚀ ⚀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silver_needle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">은바늘</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">twos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">듀스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cloak_hem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">붉은 망토 자락</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">굴린 주사위 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[2]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 합만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[2] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈의 합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚁ ⚁ ⚁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thorn_fence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가시 울타리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">threes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">트레이</t>
+  </si>
+  <si>
+    <t xml:space="preserve">herbs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">약초 한 줌</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">굴린 주사위 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[3]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 합만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[3] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈의 합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚂ ⚂ ⚂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">berry_jam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">산딸기 잼</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">fours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oak_shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">참나무 방패</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">점수의 절반</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">굴린 주사위 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[4]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 합만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[4] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈의 합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚃ ⚃ ⚃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iron_pot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무쇠 냄비</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+6</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">파이브</t>
+  </si>
+  <si>
+    <t xml:space="preserve">powder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화약 재기</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 족보 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">굴린 주사위 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[5]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 합만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[5] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈의 합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚄ ⚄ ⚄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">five_claws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">다섯 발톱</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">sixes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">식스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wolfshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">늑대 사냥탄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">부가 없음 — 순수 화력</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">굴린 주사위 중 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[6]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 합만큼 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[6] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈의 합</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚅ ⚅ ⚅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화약 과적</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 족보 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">threeKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">트리플</t>
+  </si>
+  <si>
+    <t xml:space="preserve">triple_axe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">세 번 찍는 도끼</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 족보 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 이상 — 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 눈들의 합 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×1.5 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 눈들의 합 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×1.5 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자 이중 베기</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">woodsman_breath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">나무꾼의 호흡</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 턴 리롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">fourKind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">포카드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">four_fangs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">네 개의 송곳니</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피해 준 적의 다음 행동 취소</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rare</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 이상 — 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 눈들의 합 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 눈들의 합 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">충격파</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">베기</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">⚃ ⚃ ⚃ ⚃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heavy_blow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">묵직한 일격</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 족보 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+12</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">fullHouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">풀하우스</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cottage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">할머니의 오두막</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+15</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다른 같은 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 5·5·5·2·2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">면 성립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금빛 파문</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚄ ⚄ ⚄ ⚁ ⚁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hearth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">따뜻한 화덕</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">smallStraight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스몰 스트레이트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">windpath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">바람길</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이번 적 공격 회피</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연속된 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 2·3·4·5)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">면 성립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모든 적에게 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">빛의 파도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">⚁ ⚂ ⚃ ⚄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunt_drive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">몰이사냥</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+10</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">largeStraight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라지 스트레이트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moonpath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">달빛 오솔길</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회피 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 턴 리롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연속된 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1~5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">또는 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2~6)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">면 성립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">모든 적에게 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">교차 파도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">섬광</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">⚁ ⚂ ⚃ ⚄ ⚅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">storm_run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">폭풍 질주</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회피 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+12</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">epic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yahtzee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">야찌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">judgment_night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">심판의 밤</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적 행동 취소 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주사위 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개가 모두 같은 눈이면 성립</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">심판</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">섬광</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이중 파문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">⚅ ⚅ ⚅ ⚅ ⚅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blood_moon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">핏빛 만월</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적 행동 취소 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+15</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이름</t>
+  </si>
+  <si>
+    <t xml:space="preserve">면 구성</t>
+  </si>
+  <si>
+    <t xml:space="preserve">효과 유형</t>
+  </si>
+  <si>
+    <t xml:space="preserve">효과</t>
+  </si>
+  <si>
+    <t xml:space="preserve">등급</t>
+  </si>
+  <si>
+    <t xml:space="preserve">설명</t>
+  </si>
+  <si>
+    <t xml:space="preserve">normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">나무 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 2 · 3 · 4 · 5 · 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">평범한 주사위</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">납 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 2 · 3 · 4 · 6 · 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 눈금형</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대신 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 하나 더</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 잘 나온다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">even</t>
+  </si>
+  <si>
+    <t xml:space="preserve">짝눈 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 · 2 · 4 · 4 · 6 · 6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">짝수만 나온다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">odd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">홀눈 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 1 · 3 · 3 · 5 · 5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">홀수만 나온다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">높은 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 · 4 · 4 · 5 · 5 · 6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">낮은 눈이 없다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">외눈 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 1 · 1 · 1 · 1 · 6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">거의 항상 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에이스 빌드의 심장</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금박 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">② 기여 시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">자기 눈만큼 추가 피해</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">족보에 기여하면 자기 눈만큼 추가 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">cursed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">저주 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 1 · 6 · 6 · 6 · 6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자신에게 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">탐스러운 눈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">족보에 기여하면 나도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피해를 받는다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">fang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">송곳니 주사위</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">족보에 기여하면 피를 마셔 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">straw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">밀짚 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 1 · 2 · 2 · 3 · 3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">③ 확정 시</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기여 무관</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈은 낮지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기여하지 않아도 족보를 확정할 때마다 방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ember</t>
+  </si>
+  <si>
+    <t xml:space="preserve">잿불 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 · 2 · 3 · 3 · 4 · 4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">족보를 확정할 때마다 온기가 스민다 — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">moonlit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">달빛 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 1 · 2 · 3 · 4 · 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">④ 패시브</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">리롤 추가 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">눈은 흐릿하지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">달빛이 손을 이끈다 — 매 턴 리롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">bramble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가시덤불 주사위</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 · 2 · 2 · 3 · 3 · 4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">턴 시작 방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">품고만 있어도 가시가 돋는다 — 매 턴 시작 시 방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">훅</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">엔진</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFF5EBD8"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">파라미터</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silver_bullet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🔫 은탄환</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에이스 족보 점수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">categoryMult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">category=ones, mult=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">red_cloak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🧣 붉은 망토</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">매 턴 리롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">extraReroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amount=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunters_charm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🪬 사냥꾼의 부적</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">풀하우스 점수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+15.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">categoryBonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">category=fullHouse, bonus=15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wolf_fang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🦷 늑대 이빨</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">족보를 확정할 때마다 추가 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+3.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">flatDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amount=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">breadcrumbs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🍞 빵부스러기</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전투에서 승리하면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">healOnVictory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amount=4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ledger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📒 가계부</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상단 보너스 발동 기준 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40 → 30.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">upperBonusThreshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value=30</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">층당 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배율</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">):</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -4066,7 +4156,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">HP</t>
+      <t xml:space="preserve">← act1.json hpScalePerFloor. </t>
     </r>
     <r>
       <rPr>
@@ -4076,7 +4166,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">가 자동 재계산</t>
+      <t xml:space="preserve">파란 글씨</t>
     </r>
     <r>
       <rPr>
@@ -4087,6 +4177,69 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">입력값 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(11</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">층 실효 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 자동 재계산</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">)</t>
     </r>
   </si>
@@ -4451,9 +4604,6 @@
   </si>
   <si>
     <t xml:space="preserve">elite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
   </si>
   <si>
     <r>
@@ -7807,7 +7957,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
         <v>44</v>
       </c>
@@ -7821,28 +7971,28 @@
         <v>47</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>38</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7853,870 +8003,870 @@
         <v>45</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>36</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>38</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>38</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="5" t="s">
         <v>66</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>36</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>38</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>38</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>36</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>38</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>38</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>36</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>38</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>38</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" s="5" t="s">
         <v>102</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="F13" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>36</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>38</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>38</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>36</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>38</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>36</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F19" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>36</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F20" s="15" t="s">
         <v>43</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>36</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>43</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>33</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="L25" s="11" t="s">
         <v>178</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="L25" s="11" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F26" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>180</v>
-      </c>
       <c r="G26" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F27" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>180</v>
-      </c>
       <c r="G27" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>36</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -8749,324 +8899,324 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>206</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>204</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>209</v>
-      </c>
       <c r="E4" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>43</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>43</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F6" s="15" t="s">
         <v>43</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>33</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>43</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F14" s="15" t="s">
         <v>43</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -9098,79 +9248,79 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>43</v>
@@ -9178,19 +9328,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>33</v>
@@ -9198,19 +9348,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>33</v>
@@ -9218,19 +9368,19 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>43</v>
@@ -9267,53 +9417,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B1" s="20" t="n">
         <v>0.1</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E3" s="4" t="n">
         <f aca="false">ROUND(37*(1+$B$1*10),0)</f>
@@ -9323,7 +9473,7 @@
         <v>3</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>1</v>
@@ -9331,16 +9481,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">ROUND(34*(1+$B$1*10),0)</f>
@@ -9350,7 +9500,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>1</v>
@@ -9358,16 +9508,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">ROUND(40*(1+$B$1*10),0)</f>
@@ -9377,7 +9527,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>1</v>
@@ -9385,16 +9535,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">ROUND(44*(1+$B$1*10),0)</f>
@@ -9404,7 +9554,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>1</v>
@@ -9412,16 +9562,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E7" s="4" t="n">
         <f aca="false">ROUND(47*(1+$B$1*10),0)</f>
@@ -9431,7 +9581,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>1</v>
@@ -9439,16 +9589,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E8" s="5" t="n">
         <f aca="false">ROUND(55*(1+$B$1*10),0)</f>
@@ -9458,7 +9608,7 @@
         <v>4</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>1</v>
@@ -9466,16 +9616,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>330</v>
+        <v>189</v>
       </c>
       <c r="E9" s="4" t="n">
         <f aca="false">ROUND(70*(1+$B$1*10),0)</f>
@@ -9485,7 +9635,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>1</v>
@@ -9493,16 +9643,16 @@
     </row>
     <row r="10" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E10" s="5" t="n">
         <f aca="false">ROUND(115*(1+$B$1*10),0)</f>
@@ -9512,7 +9662,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>2</v>
@@ -9547,582 +9697,582 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C21" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>363</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -10152,105 +10302,105 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -10280,172 +10430,172 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="577">
   <si>
     <r>
       <rPr>
@@ -865,6 +865,375 @@
   <si>
     <r>
       <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보상 경제</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(v0.13): </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일반전투</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">커먼</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">~</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">언커먼</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">족보</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주사위</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) · </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">엘리트</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">언커먼</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">~</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">레어</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일반유물 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보스</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">정예유물</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전설 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상점</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">커먼</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">~</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">레어 주사위</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일반유물</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(🪙) · </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF7A5C38"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">족보 누적 시 주사위 확률↑</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <b val="true"/>
         <sz val="10"/>
         <color rgb="FFF5EBD8"/>
@@ -3868,6 +4237,931 @@
     <t xml:space="preserve">파라미터</t>
   </si>
   <si>
+    <t xml:space="preserve">wolf_fang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🦷 늑대 이빨</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">족보를 확정할 때마다 추가 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+3.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">flatDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amount=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">일반</t>
+  </si>
+  <si>
+    <t xml:space="preserve">breadcrumbs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🍞 빵부스러기</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전투에서 승리하면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">healOnVictory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amount=4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🧵 붉은 실타래</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">찬스 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+4.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">categoryBonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">category=chance, bonus=4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warm_milk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🥛 따뜻한 우유</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">매 턴 시작 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">turnHeal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amount=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">firewood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🪵 마른 장작</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">매 턴 시작 시 방어 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">turnBlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amount=2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leather_gloves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🧤 가죽 장갑</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상단 족보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에이스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">~</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">식스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+3.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">kindBonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kind=upper, bonus=3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crow_feather</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🪶 까마귀 깃털</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스몰 스트레이트 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+8.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">category=smallStraight, bonus=8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hunters_charm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🪬 사냥꾼의 부적</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">풀하우스 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+15.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">category=fullHouse, bonus=15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ledger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📒 가계부</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상단 보너스 발동 기준 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40 → 30.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">upperBonusThreshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value=30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moss_compass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🧭 이끼 나침반</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전체 공격 족보 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+6.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">aoeBonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bonus=6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silver_scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚖️ 은저울</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">상단 보너스 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25 → 35.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">upperBonusDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value=35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tallow_candle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🕯️ 수지 양초</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">혼란</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(🌀)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에 면역 — 주사위가 뒤틀리지 않는다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">confuseImmune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">old_bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🦴 오래된 뼈</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 눈 족보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">트리플</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">포카드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">야찌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+6.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">kind=ofKind, bonus=6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glass_jar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🫙 유리병 속 반딧불</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">얻는 즉시 최대 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP +10.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">maxHp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amount=10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wolf_pelt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🐺 늑대 가죽</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">적을 처치할 때마다 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">healOnKill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poison_apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🍎 독사과 조각</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 절반 이하일 때 모든 족보 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+5.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">lowHpDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ratio=0.5, amount=5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">honey_pot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🍯 꿀단지</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전투에서 승리하면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HP 8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">회복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">amount=8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">red_cloak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🧣 붉은 망토</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">매 턴 리롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">extraReroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">정예</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acorn_charm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🌰 도토리 부적</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">풀하우스 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">categoryMult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">category=fullHouse, mult=2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gate_bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🚪 문지기의 빗장</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도가 턴이 지나도 사라지지 않는다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">blockKeep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🍀 네잎클로버</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">보상에서 레어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">에픽이 나올 확률 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">luck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mult=2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silver_knife</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🗡️ 은식칼</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">스트레이트 족보 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+10.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">kind=straight, bonus=10</t>
+  </si>
+  <si>
     <t xml:space="preserve">silver_bullet</t>
   </si>
   <si>
@@ -3880,7 +5174,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">에이스 족보 점수 </t>
+      <t xml:space="preserve">에이스 족보 피해 </t>
     </r>
     <r>
       <rPr>
@@ -3910,16 +5204,13 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">categoryMult</t>
-  </si>
-  <si>
     <t xml:space="preserve">category=ones, mult=5</t>
   </si>
   <si>
-    <t xml:space="preserve">red_cloak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🧣 붉은 망토</t>
+    <t xml:space="preserve">fate_thimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🪡 운명의 골무</t>
   </si>
   <si>
     <r>
@@ -3937,51 +5228,14 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+1.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">extraReroll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amount=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hunters_charm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🪬 사냥꾼의 부적</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">풀하우스 점수 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+15.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">categoryBonus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">category=fullHouse, bonus=15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wolf_fang</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🦷 늑대 이빨</t>
+      <t xml:space="preserve">+2.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">wolfmoon_pendant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🌕 늑대달 목걸이</t>
   </si>
   <si>
     <r>
@@ -3999,46 +5253,43 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+3.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">flatDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amount=3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">breadcrumbs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🍞 빵부스러기</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전투에서 승리하면 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HP 4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">회복</t>
+      <t xml:space="preserve">+6.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">amount=6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grandma_book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">📕 할머니의 동화책</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">야찌 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배</t>
     </r>
     <r>
       <rPr>
@@ -4051,41 +5302,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">healOnVictory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amount=4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ledger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">📒 가계부</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">상단 보너스 발동 기준 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">40 → 30.</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">upperBonusThreshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value=30</t>
+    <t xml:space="preserve">category=yahtzee, mult=2</t>
   </si>
   <si>
     <r>
@@ -7158,7 +8375,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7283,6 +8500,13 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FFB08948"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <name val="Malgun Gothic"/>
       <family val="0"/>
       <charset val="1"/>
@@ -7370,7 +8594,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7447,11 +8671,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7711,7 +8943,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -7773,7 +9005,7 @@
       </c>
       <c r="C7" s="4" t="n">
         <f aca="false">COUNTA(유물!A2:A100)</f>
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7808,6 +9040,11 @@
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -7845,1028 +9082,1028 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="G5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="11" t="s">
         <v>65</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="11" t="s">
         <v>77</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L11" s="11" t="s">
         <v>89</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L13" s="11" t="s">
         <v>101</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L15" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J15" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L15" s="11" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="K17" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J17" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>124</v>
-      </c>
       <c r="L17" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="L19" s="11" t="s">
         <v>139</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="L19" s="11" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="L21" s="11" t="s">
         <v>152</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="L23" s="11" t="s">
         <v>166</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="L25" s="11" t="s">
         <v>179</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="L25" s="11" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F26" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>182</v>
-      </c>
       <c r="G26" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F27" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C27" s="11" t="s">
+      <c r="G27" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="L27" s="11" t="s">
         <v>193</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J27" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="L27" s="11" t="s">
-        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -8899,324 +10136,324 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -9235,7 +10472,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -9248,142 +10485,538 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>182</v>
+        <v>272</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>273</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>43</v>
+        <v>283</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>33</v>
+        <v>288</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B6" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="B7" s="12" t="s">
+      <c r="F19" s="19" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="19" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>295</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>43</v>
+      <c r="F25" s="19" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -9416,54 +11049,54 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="B1" s="20" t="n">
+      <c r="A1" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1" s="22" t="n">
         <v>0.1</v>
       </c>
-      <c r="C1" s="21" t="s">
-        <v>298</v>
+      <c r="C1" s="23" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>299</v>
+        <v>388</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>300</v>
+        <v>389</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>302</v>
+        <v>391</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>303</v>
+        <v>392</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>304</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>305</v>
+        <v>394</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>306</v>
+        <v>395</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>307</v>
+        <v>396</v>
       </c>
       <c r="E3" s="4" t="n">
         <f aca="false">ROUND(37*(1+$B$1*10),0)</f>
@@ -9473,7 +11106,7 @@
         <v>3</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>308</v>
+        <v>397</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>1</v>
@@ -9481,16 +11114,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>309</v>
+        <v>398</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>310</v>
+        <v>399</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>311</v>
+        <v>400</v>
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">ROUND(34*(1+$B$1*10),0)</f>
@@ -9500,7 +11133,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>312</v>
+        <v>401</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>1</v>
@@ -9508,16 +11141,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>313</v>
+        <v>402</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>314</v>
+        <v>403</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>315</v>
+        <v>404</v>
       </c>
       <c r="E5" s="4" t="n">
         <f aca="false">ROUND(40*(1+$B$1*10),0)</f>
@@ -9527,7 +11160,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>316</v>
+        <v>405</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>1</v>
@@ -9535,16 +11168,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>317</v>
+        <v>406</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>318</v>
+        <v>407</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>319</v>
+        <v>408</v>
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">ROUND(44*(1+$B$1*10),0)</f>
@@ -9554,7 +11187,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>320</v>
+        <v>409</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>1</v>
@@ -9562,16 +11195,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>321</v>
+        <v>410</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>322</v>
+        <v>411</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>323</v>
+        <v>412</v>
       </c>
       <c r="E7" s="4" t="n">
         <f aca="false">ROUND(47*(1+$B$1*10),0)</f>
@@ -9581,7 +11214,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>324</v>
+        <v>413</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>1</v>
@@ -9589,16 +11222,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>325</v>
+        <v>414</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>326</v>
+        <v>415</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>327</v>
+        <v>416</v>
       </c>
       <c r="E8" s="5" t="n">
         <f aca="false">ROUND(55*(1+$B$1*10),0)</f>
@@ -9608,7 +11241,7 @@
         <v>4</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>328</v>
+        <v>417</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>1</v>
@@ -9616,16 +11249,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>329</v>
+        <v>418</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>330</v>
+        <v>419</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>331</v>
+        <v>420</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E9" s="4" t="n">
         <f aca="false">ROUND(70*(1+$B$1*10),0)</f>
@@ -9635,7 +11268,7 @@
         <v>3</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>332</v>
+        <v>421</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>1</v>
@@ -9643,16 +11276,16 @@
     </row>
     <row r="10" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>333</v>
+        <v>422</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>334</v>
+        <v>423</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>335</v>
+        <v>424</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>336</v>
+        <v>425</v>
       </c>
       <c r="E10" s="5" t="n">
         <f aca="false">ROUND(115*(1+$B$1*10),0)</f>
@@ -9662,7 +11295,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>337</v>
+        <v>426</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>2</v>
@@ -9697,582 +11330,582 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>338</v>
+        <v>427</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>339</v>
+        <v>428</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>340</v>
+        <v>429</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>341</v>
+        <v>430</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>342</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>305</v>
+        <v>394</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>306</v>
+        <v>395</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>343</v>
+        <v>432</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>344</v>
+        <v>433</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>346</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>305</v>
+        <v>394</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>306</v>
+        <v>395</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>347</v>
+        <v>436</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>348</v>
+        <v>437</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>349</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>305</v>
+        <v>394</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>306</v>
+        <v>395</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>350</v>
+        <v>439</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>351</v>
+        <v>440</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>352</v>
+        <v>441</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>353</v>
+        <v>442</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>309</v>
+        <v>398</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>310</v>
+        <v>399</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>354</v>
+        <v>443</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>355</v>
+        <v>444</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>356</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>309</v>
+        <v>398</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>310</v>
+        <v>399</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>357</v>
+        <v>446</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>358</v>
+        <v>447</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>359</v>
+        <v>448</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>360</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>309</v>
+        <v>398</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>310</v>
+        <v>399</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>361</v>
+        <v>450</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>362</v>
+        <v>451</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>363</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>313</v>
+        <v>402</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>314</v>
+        <v>403</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>365</v>
+        <v>454</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>356</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>313</v>
+        <v>402</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>314</v>
+        <v>403</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>366</v>
+        <v>455</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>367</v>
+        <v>456</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>368</v>
+        <v>457</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>369</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>313</v>
+        <v>402</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>314</v>
+        <v>403</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>370</v>
+        <v>459</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>371</v>
+        <v>460</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>363</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>317</v>
+        <v>406</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>318</v>
+        <v>407</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>372</v>
+        <v>461</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>373</v>
+        <v>462</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>317</v>
+        <v>406</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>318</v>
+        <v>407</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>374</v>
+        <v>463</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>375</v>
+        <v>464</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>376</v>
+        <v>465</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>377</v>
+        <v>466</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>317</v>
+        <v>406</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>318</v>
+        <v>407</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>378</v>
+        <v>467</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>379</v>
+        <v>468</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>380</v>
+        <v>469</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>381</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>321</v>
+        <v>410</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>322</v>
+        <v>411</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>382</v>
+        <v>471</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>383</v>
+        <v>472</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>356</v>
+        <v>445</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>321</v>
+        <v>410</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>322</v>
+        <v>411</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>384</v>
+        <v>473</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>385</v>
+        <v>474</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>386</v>
+        <v>475</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>387</v>
+        <v>476</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>321</v>
+        <v>410</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>322</v>
+        <v>411</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>388</v>
+        <v>477</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>389</v>
+        <v>478</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>390</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>325</v>
+        <v>414</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>326</v>
+        <v>415</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>391</v>
+        <v>480</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>392</v>
+        <v>481</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>349</v>
+        <v>438</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>325</v>
+        <v>414</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>326</v>
+        <v>415</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>393</v>
+        <v>482</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>395</v>
+        <v>484</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>396</v>
+        <v>485</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>325</v>
+        <v>414</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>326</v>
+        <v>415</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>397</v>
+        <v>486</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>398</v>
+        <v>487</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>399</v>
+        <v>488</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>325</v>
+        <v>414</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>326</v>
+        <v>415</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>400</v>
+        <v>489</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>401</v>
+        <v>490</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>402</v>
+        <v>491</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>403</v>
+        <v>492</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>329</v>
+        <v>418</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>330</v>
+        <v>419</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>372</v>
+        <v>461</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>363</v>
+        <v>452</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>329</v>
+        <v>418</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>330</v>
+        <v>419</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>404</v>
+        <v>493</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>405</v>
+        <v>494</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>406</v>
+        <v>495</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>407</v>
+        <v>496</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>329</v>
+        <v>418</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>330</v>
+        <v>419</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>408</v>
+        <v>497</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>409</v>
+        <v>498</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>410</v>
+        <v>499</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>333</v>
+        <v>422</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>334</v>
+        <v>423</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>372</v>
+        <v>461</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>390</v>
+        <v>479</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>333</v>
+        <v>422</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>334</v>
+        <v>423</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>411</v>
+        <v>500</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>412</v>
+        <v>501</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>413</v>
+        <v>502</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>414</v>
+        <v>503</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>333</v>
+        <v>422</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>334</v>
+        <v>423</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>415</v>
+        <v>504</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>416</v>
+        <v>505</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>417</v>
+        <v>506</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>333</v>
+        <v>422</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>334</v>
+        <v>423</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>404</v>
+        <v>493</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>418</v>
+        <v>507</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>419</v>
+        <v>508</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>420</v>
+        <v>509</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>333</v>
+        <v>422</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>334</v>
+        <v>423</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>421</v>
+        <v>510</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>422</v>
+        <v>511</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>399</v>
+        <v>488</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>333</v>
+        <v>422</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>334</v>
+        <v>423</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>423</v>
+        <v>512</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>424</v>
+        <v>513</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>402</v>
+        <v>491</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>425</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -10302,105 +11935,105 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>426</v>
+        <v>515</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>427</v>
+        <v>516</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>428</v>
+        <v>517</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>429</v>
+        <v>518</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>430</v>
+        <v>519</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>431</v>
+        <v>520</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>432</v>
+        <v>521</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>433</v>
+        <v>522</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>434</v>
+        <v>523</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>435</v>
+        <v>524</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>436</v>
+        <v>525</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>437</v>
+        <v>526</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>438</v>
+        <v>527</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>439</v>
+        <v>528</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>440</v>
+        <v>529</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>441</v>
+        <v>530</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>442</v>
+        <v>531</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>443</v>
+        <v>532</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>444</v>
+        <v>533</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>445</v>
+        <v>534</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>446</v>
+        <v>535</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>447</v>
+        <v>536</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>448</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>449</v>
+        <v>538</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>450</v>
+        <v>539</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>451</v>
+        <v>540</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>452</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>453</v>
+        <v>542</v>
       </c>
     </row>
   </sheetData>
@@ -10430,172 +12063,172 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>454</v>
+        <v>543</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>455</v>
+        <v>544</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>456</v>
+        <v>545</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>457</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>458</v>
+        <v>547</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>459</v>
+        <v>548</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>460</v>
+        <v>549</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>461</v>
+        <v>550</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>462</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>458</v>
+        <v>547</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>459</v>
+        <v>548</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>463</v>
+        <v>552</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>464</v>
+        <v>553</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>465</v>
+        <v>554</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>458</v>
+        <v>547</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>459</v>
+        <v>548</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>466</v>
+        <v>555</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>467</v>
+        <v>556</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>468</v>
+        <v>557</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>469</v>
+        <v>558</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>470</v>
+        <v>559</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>471</v>
+        <v>560</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>472</v>
+        <v>561</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>468</v>
+        <v>557</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>469</v>
+        <v>558</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>473</v>
+        <v>562</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>474</v>
+        <v>563</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>475</v>
+        <v>564</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>468</v>
+        <v>557</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>469</v>
+        <v>558</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>476</v>
+        <v>565</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>477</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>478</v>
+        <v>567</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>479</v>
+        <v>568</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>480</v>
+        <v>569</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>481</v>
+        <v>570</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>482</v>
+        <v>571</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>478</v>
+        <v>567</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>479</v>
+        <v>568</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>483</v>
+        <v>572</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>484</v>
+        <v>573</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>485</v>
+        <v>574</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>478</v>
+        <v>567</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>479</v>
+        <v>568</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>486</v>
+        <v>575</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>487</v>
+        <v>576</v>
       </c>
     </row>
   </sheetData>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="1118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2037" uniqueCount="1130">
   <si>
     <r>
       <rPr>
@@ -2273,6 +2273,261 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">twoPair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">투페어</t>
+  </si>
+  <si>
+    <t xml:space="preserve">twin_sisters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">쌍둥이 자매</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">방어도 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">서로 다른 눈 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">쌍 — 피해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">두 쌍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주사위 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">의 합 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×1.25 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">같은 눈들의 합 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×1.25 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">내림</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자 이중 베기</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">⚄ ⚄ ⚂ ⚂ ⚀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">two_moons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">두 개의 달</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 턴 리롤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">다음 피해 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+3</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">threeKind</t>
   </si>
   <si>
@@ -2411,25 +2666,6 @@
   </si>
   <si>
     <t xml:space="preserve">14.9</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">X</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">자 이중 베기</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">woodsman_breath</t>
@@ -15116,7 +15352,7 @@
       </c>
       <c r="C5" s="4" t="n">
         <f aca="false">COUNTA(족보!A2:A100)</f>
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15198,7 +15434,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -15820,7 +16056,7 @@
         <v>125</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15831,13 +16067,13 @@
         <v>118</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>44</v>
@@ -15858,27 +16094,27 @@
         <v>125</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F18" s="14" t="s">
         <v>134</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>135</v>
@@ -15892,28 +16128,28 @@
       <c r="J18" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="D19" s="12" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="11" t="s">
+      <c r="E19" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="F19" s="13" t="s">
         <v>44</v>
@@ -15930,315 +16166,391 @@
       <c r="J19" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="K19" s="5" t="s">
-        <v>138</v>
+      <c r="K19" s="11" t="s">
+        <v>125</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="D20" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="E20" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="F20" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="G20" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="H20" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J20" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="K20" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="L20" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="L20" s="9" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C21" s="11" t="s">
+      <c r="D21" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="E21" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>134</v>
+      <c r="F21" s="13" t="s">
+        <v>44</v>
       </c>
       <c r="G21" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>149</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="J21" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="K21" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="L21" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="D22" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="E22" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>160</v>
       </c>
       <c r="F22" s="15" t="s">
         <v>44</v>
       </c>
       <c r="G22" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="H22" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="I22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="K22" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="L22" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>157</v>
-      </c>
       <c r="C23" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>34</v>
+      <c r="F23" s="16" t="s">
+        <v>146</v>
       </c>
       <c r="G23" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H23" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="I23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="K23" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="J23" s="11" t="s">
+      <c r="L23" s="11" t="s">
         <v>164</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="D24" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="E24" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="F24" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="H24" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="F24" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="I24" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="J24" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="J24" s="9" t="s">
+      <c r="K24" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="K24" s="4" t="s">
+      <c r="L24" s="9" t="s">
         <v>178</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C25" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D25" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="E25" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="B26" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="C26" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="I26" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="H25" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="L25" s="11" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="J26" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="H27" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="F26" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="I27" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="J27" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="K27" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="L27" s="11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="I28" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J26" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="D27" s="12" t="s">
+      <c r="J28" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F29" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="I27" s="5" t="s">
+      <c r="G29" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J27" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="L27" s="11" t="s">
-        <v>193</v>
+      <c r="J29" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -16271,324 +16583,324 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>44</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>44</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E5" s="11" t="s">
         <v>219</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>207</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>44</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C6" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>212</v>
-      </c>
       <c r="E6" s="9" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F6" s="15" t="s">
         <v>44</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>34</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>44</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="F14" s="15" t="s">
         <v>44</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -16620,538 +16932,538 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>285</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="19" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="F22" s="20" t="s">
         <v>364</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -17186,1318 +17498,1318 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="B1" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>4</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>6</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>4</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="H25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F26" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="H27" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>4</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F29" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>4</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="F31" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="H31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="F32" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="F33" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="H33" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="H34" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="H35" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="F37" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="H37" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>4</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="H38" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="H39" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>4</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="F41" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="H41" s="4" t="n">
         <v>2</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>4</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="H42" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="F43" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="H43" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="H44" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="F45" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="H45" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="H46" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
     </row>
   </sheetData>
@@ -18529,2962 +18841,2962 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>670</v>
+        <v>682</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="C41" s="11" t="s">
+        <v>740</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>728</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>729</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>619</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="11" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="9" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="11" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="9" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="11" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="9" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="11" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="9" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="11" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="9" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="11" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="9" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="11" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="9" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="11" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="9" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="11" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="9" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="11" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="9" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>827</v>
+        <v>839</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="11" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="9" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="11" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="9" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="11" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>844</v>
+        <v>856</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="11" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="9" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="11" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>850</v>
+        <v>862</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="9" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="11" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="9" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>859</v>
+        <v>871</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="11" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="9" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="11" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="9" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="11" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>868</v>
+        <v>880</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="9" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>870</v>
+        <v>882</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="11" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="9" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="C104" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="11" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>875</v>
+        <v>887</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="9" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="11" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="9" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="11" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="9" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="11" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="C111" s="11" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="9" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>889</v>
+        <v>901</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="11" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="C113" s="11" t="s">
-        <v>890</v>
+        <v>902</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="9" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>893</v>
+        <v>905</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="11" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>894</v>
+        <v>906</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>895</v>
+        <v>907</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>896</v>
+        <v>908</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="9" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>897</v>
+        <v>909</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>898</v>
+        <v>910</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="11" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>899</v>
+        <v>911</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="9" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>900</v>
+        <v>912</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="11" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>901</v>
+        <v>913</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="9" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="11" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="9" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>905</v>
+        <v>917</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>906</v>
+        <v>918</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>896</v>
+        <v>908</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="11" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>908</v>
+        <v>920</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="9" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>909</v>
+        <v>921</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>910</v>
+        <v>922</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="11" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>911</v>
+        <v>923</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>912</v>
+        <v>924</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>913</v>
+        <v>925</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="9" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>914</v>
+        <v>926</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>915</v>
+        <v>927</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>916</v>
+        <v>928</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="11" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>917</v>
+        <v>929</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>918</v>
+        <v>930</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="9" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>920</v>
+        <v>932</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>921</v>
+        <v>933</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="11" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>922</v>
+        <v>934</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>923</v>
+        <v>935</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>896</v>
+        <v>908</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="9" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>924</v>
+        <v>936</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>925</v>
+        <v>937</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>927</v>
+        <v>939</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="11" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>928</v>
+        <v>940</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>929</v>
+        <v>941</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="9" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>931</v>
+        <v>943</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>932</v>
+        <v>944</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="11" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>933</v>
+        <v>945</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>934</v>
+        <v>946</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="9" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>935</v>
+        <v>947</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>936</v>
+        <v>948</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>937</v>
+        <v>949</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="11" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="C135" s="11" t="s">
-        <v>938</v>
+        <v>950</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>939</v>
+        <v>951</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>940</v>
+        <v>952</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="9" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>941</v>
+        <v>953</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>942</v>
+        <v>954</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="11" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="C137" s="11" t="s">
         <v>41</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>943</v>
+        <v>955</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="9" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>944</v>
+        <v>956</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>945</v>
+        <v>957</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="11" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>946</v>
+        <v>958</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>947</v>
+        <v>959</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>948</v>
+        <v>960</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="9" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>949</v>
+        <v>961</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>950</v>
+        <v>962</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="11" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>951</v>
+        <v>963</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>952</v>
+        <v>964</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="9" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>953</v>
+        <v>965</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>954</v>
+        <v>966</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>955</v>
+        <v>967</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="11" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="C143" s="11" t="s">
-        <v>930</v>
+        <v>942</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>956</v>
+        <v>968</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>957</v>
+        <v>969</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="9" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>958</v>
+        <v>970</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>959</v>
+        <v>971</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="11" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="C145" s="11" t="s">
-        <v>960</v>
+        <v>972</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>961</v>
+        <v>973</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="9" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>962</v>
+        <v>974</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="11" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>965</v>
+        <v>977</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="9" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>966</v>
+        <v>978</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>967</v>
+        <v>979</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
     </row>
   </sheetData>
@@ -21514,105 +21826,105 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>968</v>
+        <v>980</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>969</v>
+        <v>981</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>970</v>
+        <v>982</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>972</v>
+        <v>984</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>973</v>
+        <v>985</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>974</v>
+        <v>986</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>975</v>
+        <v>987</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>976</v>
+        <v>988</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>977</v>
+        <v>989</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>978</v>
+        <v>990</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>979</v>
+        <v>991</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>980</v>
+        <v>992</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>981</v>
+        <v>993</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>982</v>
+        <v>994</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>983</v>
+        <v>995</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>984</v>
+        <v>996</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>985</v>
+        <v>997</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>986</v>
+        <v>998</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>987</v>
+        <v>999</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>990</v>
+        <v>1002</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>991</v>
+        <v>1003</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>992</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>993</v>
+        <v>1005</v>
       </c>
     </row>
   </sheetData>
@@ -21642,529 +21954,529 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>994</v>
+        <v>1006</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>995</v>
+        <v>1007</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>996</v>
+        <v>1008</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>997</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>998</v>
+        <v>1010</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>1000</v>
+        <v>1012</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1001</v>
+        <v>1013</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>1002</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>998</v>
+        <v>1010</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1003</v>
+        <v>1015</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>1004</v>
+        <v>1016</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1005</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>998</v>
+        <v>1010</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>999</v>
+        <v>1011</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1006</v>
+        <v>1018</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1007</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>1008</v>
+        <v>1020</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>1010</v>
+        <v>1022</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1011</v>
+        <v>1023</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>1012</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>1008</v>
+        <v>1020</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1013</v>
+        <v>1025</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>1014</v>
+        <v>1026</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>1015</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>1008</v>
+        <v>1020</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>1016</v>
+        <v>1028</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>1017</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>1018</v>
+        <v>1030</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1019</v>
+        <v>1031</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1020</v>
+        <v>1032</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>1021</v>
+        <v>1033</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1022</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>1018</v>
+        <v>1030</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1019</v>
+        <v>1031</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>1023</v>
+        <v>1035</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1024</v>
+        <v>1036</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>1025</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>1018</v>
+        <v>1030</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1019</v>
+        <v>1031</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1026</v>
+        <v>1038</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>1027</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>1028</v>
+        <v>1040</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>1029</v>
+        <v>1041</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>1030</v>
+        <v>1042</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>1031</v>
+        <v>1043</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>1032</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>1028</v>
+        <v>1040</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1029</v>
+        <v>1041</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>1033</v>
+        <v>1045</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>1034</v>
+        <v>1046</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>1035</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>1028</v>
+        <v>1040</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>1029</v>
+        <v>1041</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1036</v>
+        <v>1048</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1037</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>1038</v>
+        <v>1050</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1039</v>
+        <v>1051</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1040</v>
+        <v>1052</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>1041</v>
+        <v>1053</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>1042</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>1038</v>
+        <v>1050</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1039</v>
+        <v>1051</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>1043</v>
+        <v>1055</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>1044</v>
+        <v>1056</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>1045</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>1038</v>
+        <v>1050</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1039</v>
+        <v>1051</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1046</v>
+        <v>1058</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>1047</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>1048</v>
+        <v>1060</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>1049</v>
+        <v>1061</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>1050</v>
+        <v>1062</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>1051</v>
+        <v>1063</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>1052</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>1048</v>
+        <v>1060</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1049</v>
+        <v>1061</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>1053</v>
+        <v>1065</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>1014</v>
+        <v>1026</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>1054</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>1048</v>
+        <v>1060</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>1049</v>
+        <v>1061</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>1055</v>
+        <v>1067</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>1056</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>1057</v>
+        <v>1069</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1058</v>
+        <v>1070</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1059</v>
+        <v>1071</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>1060</v>
+        <v>1072</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>1061</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>1057</v>
+        <v>1069</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>1058</v>
+        <v>1070</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>1062</v>
+        <v>1074</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>1063</v>
+        <v>1075</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>1064</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>1057</v>
+        <v>1069</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1058</v>
+        <v>1070</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>1067</v>
+        <v>1079</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>1068</v>
+        <v>1080</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>1069</v>
+        <v>1081</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1070</v>
+        <v>1082</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>1071</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>1067</v>
+        <v>1079</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1068</v>
+        <v>1080</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>1072</v>
+        <v>1084</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>1073</v>
+        <v>1085</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>1074</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>1067</v>
+        <v>1079</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>1068</v>
+        <v>1080</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>1075</v>
+        <v>1087</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>1076</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>1077</v>
+        <v>1089</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1078</v>
+        <v>1090</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>1079</v>
+        <v>1091</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>1080</v>
+        <v>1092</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>1081</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>1077</v>
+        <v>1089</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>1078</v>
+        <v>1090</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>1082</v>
+        <v>1094</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>1083</v>
+        <v>1095</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>1084</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>1077</v>
+        <v>1089</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1078</v>
+        <v>1090</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>1085</v>
+        <v>1097</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>1086</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>1087</v>
+        <v>1099</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>1088</v>
+        <v>1100</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>1089</v>
+        <v>1101</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>1090</v>
+        <v>1102</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>1091</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>1087</v>
+        <v>1099</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1088</v>
+        <v>1100</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>1092</v>
+        <v>1104</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>1093</v>
+        <v>1105</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>1094</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>1087</v>
+        <v>1099</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>1088</v>
+        <v>1100</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>1095</v>
+        <v>1107</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>1096</v>
+        <v>1108</v>
       </c>
     </row>
   </sheetData>
@@ -22192,10 +22504,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>1097</v>
+        <v>1109</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22203,7 +22515,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1098</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22211,7 +22523,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1099</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22219,7 +22531,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1100</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22227,7 +22539,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>1101</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22235,7 +22547,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1102</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22243,7 +22555,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1103</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22251,7 +22563,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1104</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22259,7 +22571,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1105</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22267,7 +22579,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1106</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22275,7 +22587,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>1107</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22283,7 +22595,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1108</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22291,7 +22603,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>1109</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22299,7 +22611,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1110</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22307,7 +22619,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1111</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22315,7 +22627,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1112</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22323,7 +22635,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>1113</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22331,7 +22643,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1114</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22339,7 +22651,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>1115</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22347,7 +22659,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1116</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22355,7 +22667,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>1117</v>
+        <v>1129</v>
       </c>
     </row>
   </sheetData>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -7227,7 +7227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H238"/>
+  <dimension ref="A1:I238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7236,8 +7236,9 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7250,7 +7251,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>적이 낼 수 있는 모든 행동. 해금 턴이 비어 있으면 1턴부터 나온다.</t>
+          <t>발동 조건은 셋이다 — 해금 턴은 "이 턴부터 나올 수 있다", 쿨다운은 "쓰고 나서 몇 턴 쉰다", 연계는 "앞 행동을 쓰면 확률로 확정된다". 쿨다운 0은 제한 없음.</t>
         </is>
       </c>
     </row>
@@ -7287,10 +7288,15 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
+          <t>쿨다운</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>연계</t>
         </is>
@@ -7323,8 +7329,11 @@
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
+      <c r="G4" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -7355,8 +7364,11 @@
       <c r="F5" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -7385,8 +7397,11 @@
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="G6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>급강하 50%</t>
         </is>
@@ -7419,12 +7434,13 @@
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -7453,12 +7469,13 @@
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -7487,8 +7504,11 @@
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -7517,12 +7537,15 @@
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>불꽃 폭발 50%</t>
         </is>
@@ -7557,8 +7580,11 @@
       <c r="F11" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="8" t="inlineStr"/>
+      <c r="G11" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -7587,12 +7613,13 @@
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -7621,12 +7648,13 @@
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -7655,8 +7683,11 @@
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="8" t="inlineStr"/>
+      <c r="G14" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H14" s="8" t="inlineStr"/>
+      <c r="I14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -7685,8 +7716,11 @@
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr"/>
-      <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="G15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>기습 50%</t>
         </is>
@@ -7721,8 +7755,11 @@
       <c r="F16" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G16" s="8" t="inlineStr"/>
+      <c r="G16" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H16" s="8" t="inlineStr"/>
+      <c r="I16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -7751,12 +7788,13 @@
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -7785,12 +7823,13 @@
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="I18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -7819,8 +7858,11 @@
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="8" t="inlineStr"/>
+      <c r="G19" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H19" s="8" t="inlineStr"/>
+      <c r="I19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -7849,8 +7891,11 @@
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr"/>
-      <c r="G20" s="8" t="inlineStr"/>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="G20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8" t="inlineStr"/>
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>사냥 50%</t>
         </is>
@@ -7885,8 +7930,11 @@
       <c r="F21" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G21" s="8" t="inlineStr"/>
+      <c r="G21" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -7915,12 +7963,13 @@
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr"/>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -7949,12 +7998,13 @@
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr"/>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -7983,8 +8033,11 @@
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="8" t="inlineStr"/>
+      <c r="G24" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -8013,8 +8066,11 @@
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr"/>
-      <c r="G25" s="8" t="inlineStr"/>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="G25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>덩굴 채찍 50%</t>
         </is>
@@ -8049,8 +8105,11 @@
       <c r="F26" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G26" s="8" t="inlineStr"/>
+      <c r="G26" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -8079,12 +8138,13 @@
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr"/>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -8113,12 +8173,13 @@
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr"/>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr"/>
+      <c r="I28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -8147,8 +8208,11 @@
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr"/>
-      <c r="G29" s="8" t="inlineStr"/>
+      <c r="G29" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H29" s="8" t="inlineStr"/>
+      <c r="I29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -8177,8 +8241,11 @@
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr"/>
-      <c r="G30" s="8" t="inlineStr"/>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="G30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>짓뭉개기 50%</t>
         </is>
@@ -8213,8 +8280,11 @@
       <c r="F31" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G31" s="8" t="inlineStr"/>
+      <c r="G31" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H31" s="8" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -8243,8 +8313,11 @@
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr"/>
-      <c r="G32" s="8" t="inlineStr"/>
+      <c r="G32" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H32" s="8" t="inlineStr"/>
+      <c r="I32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -8273,12 +8346,13 @@
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr"/>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -8307,12 +8381,13 @@
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr"/>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr"/>
+      <c r="I34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -8341,8 +8416,11 @@
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr"/>
-      <c r="G35" s="8" t="inlineStr"/>
+      <c r="G35" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -8371,8 +8449,11 @@
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr"/>
-      <c r="G36" s="8" t="inlineStr"/>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="G36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="8" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>급류 50%</t>
         </is>
@@ -8407,8 +8488,11 @@
       <c r="F37" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G37" s="8" t="inlineStr"/>
+      <c r="G37" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -8437,12 +8521,13 @@
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr"/>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr"/>
+      <c r="I38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -8471,12 +8556,13 @@
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr"/>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -8505,8 +8591,11 @@
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr"/>
-      <c r="G40" s="8" t="inlineStr"/>
+      <c r="G40" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H40" s="8" t="inlineStr"/>
+      <c r="I40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -8537,8 +8626,11 @@
       <c r="F41" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G41" s="8" t="inlineStr"/>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="G41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="8" t="inlineStr"/>
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>부풀기 50%</t>
         </is>
@@ -8571,8 +8663,11 @@
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr"/>
-      <c r="G42" s="8" t="inlineStr"/>
+      <c r="G42" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H42" s="8" t="inlineStr"/>
+      <c r="I42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -8601,12 +8696,13 @@
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr"/>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr"/>
+      <c r="I43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -8635,12 +8731,13 @@
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr"/>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr"/>
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr"/>
+      <c r="I44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -8669,8 +8766,11 @@
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr"/>
-      <c r="G45" s="8" t="inlineStr"/>
+      <c r="G45" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H45" s="8" t="inlineStr"/>
+      <c r="I45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -8701,8 +8801,11 @@
       <c r="F46" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G46" s="8" t="inlineStr"/>
+      <c r="G46" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H46" s="8" t="inlineStr"/>
+      <c r="I46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -8731,8 +8834,11 @@
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr"/>
-      <c r="G47" s="8" t="inlineStr"/>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="G47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>몰려들기 50%</t>
         </is>
@@ -8765,12 +8871,13 @@
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr"/>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr"/>
+      <c r="I48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -8799,12 +8906,13 @@
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr"/>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr"/>
+      <c r="I49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -8835,8 +8943,11 @@
       <c r="F50" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G50" s="8" t="inlineStr"/>
+      <c r="G50" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H50" s="8" t="inlineStr"/>
+      <c r="I50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -8865,8 +8976,11 @@
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr"/>
-      <c r="G51" s="8" t="inlineStr"/>
+      <c r="G51" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H51" s="8" t="inlineStr"/>
+      <c r="I51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -8895,8 +9009,11 @@
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr"/>
-      <c r="G52" s="8" t="inlineStr"/>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="G52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="8" t="inlineStr"/>
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>쓸어내기 50%</t>
         </is>
@@ -8929,12 +9046,13 @@
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr"/>
-      <c r="G53" s="8" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr"/>
+      <c r="I53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -8963,12 +9081,13 @@
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr"/>
-      <c r="G54" s="8" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr"/>
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr"/>
+      <c r="I54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
@@ -8997,8 +9116,11 @@
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr"/>
-      <c r="G55" s="10" t="inlineStr"/>
+      <c r="G55" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H55" s="10" t="inlineStr"/>
+      <c r="I55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -9027,8 +9149,11 @@
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr"/>
-      <c r="G56" s="10" t="inlineStr"/>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="G56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="10" t="inlineStr"/>
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>광란 60%</t>
         </is>
@@ -9063,8 +9188,11 @@
       <c r="F57" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G57" s="10" t="inlineStr"/>
+      <c r="G57" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H57" s="10" t="inlineStr"/>
+      <c r="I57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -9093,12 +9221,13 @@
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr"/>
-      <c r="G58" s="10" t="inlineStr">
+      <c r="G58" s="10" t="inlineStr"/>
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H58" s="10" t="inlineStr"/>
+      <c r="I58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -9127,12 +9256,13 @@
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr"/>
-      <c r="G59" s="10" t="inlineStr">
+      <c r="G59" s="10" t="inlineStr"/>
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H59" s="10" t="inlineStr"/>
+      <c r="I59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
@@ -9161,8 +9291,11 @@
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr"/>
-      <c r="G60" s="10" t="inlineStr"/>
+      <c r="G60" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H60" s="10" t="inlineStr"/>
+      <c r="I60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
@@ -9191,12 +9324,15 @@
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr"/>
-      <c r="G61" s="10" t="inlineStr">
+      <c r="G61" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>요동 60%</t>
         </is>
@@ -9231,8 +9367,11 @@
       <c r="F62" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G62" s="10" t="inlineStr"/>
+      <c r="G62" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H62" s="10" t="inlineStr"/>
+      <c r="I62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
@@ -9261,12 +9400,13 @@
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr"/>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="G63" s="10" t="inlineStr"/>
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H63" s="10" t="inlineStr"/>
+      <c r="I63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -9295,12 +9435,13 @@
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr"/>
-      <c r="G64" s="10" t="inlineStr">
+      <c r="G64" s="10" t="inlineStr"/>
+      <c r="H64" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H64" s="10" t="inlineStr"/>
+      <c r="I64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
@@ -9329,8 +9470,11 @@
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr"/>
-      <c r="G65" s="10" t="inlineStr"/>
+      <c r="G65" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H65" s="10" t="inlineStr"/>
+      <c r="I65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -9359,12 +9503,15 @@
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr"/>
-      <c r="G66" s="10" t="inlineStr">
+      <c r="G66" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="I66" s="10" t="inlineStr">
         <is>
           <t>덮침 60%</t>
         </is>
@@ -9399,8 +9546,11 @@
       <c r="F67" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G67" s="10" t="inlineStr"/>
+      <c r="G67" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H67" s="10" t="inlineStr"/>
+      <c r="I67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
@@ -9429,12 +9579,13 @@
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr"/>
-      <c r="G68" s="10" t="inlineStr">
+      <c r="G68" s="10" t="inlineStr"/>
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H68" s="10" t="inlineStr"/>
+      <c r="I68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
@@ -9463,12 +9614,13 @@
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr"/>
-      <c r="G69" s="10" t="inlineStr">
+      <c r="G69" s="10" t="inlineStr"/>
+      <c r="H69" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H69" s="10" t="inlineStr"/>
+      <c r="I69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
@@ -9497,8 +9649,11 @@
         </is>
       </c>
       <c r="F70" s="16" t="inlineStr"/>
-      <c r="G70" s="16" t="inlineStr"/>
+      <c r="G70" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H70" s="16" t="inlineStr"/>
+      <c r="I70" s="16" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
@@ -9527,12 +9682,15 @@
         </is>
       </c>
       <c r="F71" s="16" t="inlineStr"/>
-      <c r="G71" s="16" t="inlineStr">
+      <c r="G71" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="16" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H71" s="16" t="inlineStr">
+      <c r="I71" s="16" t="inlineStr">
         <is>
           <t>덮치기 70%</t>
         </is>
@@ -9567,8 +9725,11 @@
       <c r="F72" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="G72" s="16" t="inlineStr"/>
+      <c r="G72" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H72" s="16" t="inlineStr"/>
+      <c r="I72" s="16" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
@@ -9597,8 +9758,11 @@
         </is>
       </c>
       <c r="F73" s="16" t="inlineStr"/>
-      <c r="G73" s="16" t="inlineStr"/>
+      <c r="G73" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H73" s="16" t="inlineStr"/>
+      <c r="I73" s="16" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
@@ -9627,8 +9791,11 @@
         </is>
       </c>
       <c r="F74" s="16" t="inlineStr"/>
-      <c r="G74" s="16" t="inlineStr"/>
+      <c r="G74" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H74" s="16" t="inlineStr"/>
+      <c r="I74" s="16" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
@@ -9657,8 +9824,11 @@
         </is>
       </c>
       <c r="F75" s="16" t="inlineStr"/>
-      <c r="G75" s="16" t="inlineStr"/>
+      <c r="G75" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H75" s="16" t="inlineStr"/>
+      <c r="I75" s="16" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
@@ -9687,12 +9857,13 @@
         </is>
       </c>
       <c r="F76" s="16" t="inlineStr"/>
-      <c r="G76" s="16" t="inlineStr">
+      <c r="G76" s="16" t="inlineStr"/>
+      <c r="H76" s="16" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H76" s="16" t="inlineStr"/>
+      <c r="I76" s="16" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
@@ -9721,12 +9892,13 @@
         </is>
       </c>
       <c r="F77" s="16" t="inlineStr"/>
-      <c r="G77" s="16" t="inlineStr">
+      <c r="G77" s="16" t="inlineStr"/>
+      <c r="H77" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H77" s="16" t="inlineStr"/>
+      <c r="I77" s="16" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
@@ -9755,8 +9927,11 @@
         </is>
       </c>
       <c r="F78" s="16" t="inlineStr"/>
-      <c r="G78" s="16" t="inlineStr"/>
+      <c r="G78" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H78" s="16" t="inlineStr"/>
+      <c r="I78" s="16" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
@@ -9785,8 +9960,11 @@
         </is>
       </c>
       <c r="F79" s="16" t="inlineStr"/>
-      <c r="G79" s="16" t="inlineStr"/>
-      <c r="H79" s="16" t="inlineStr">
+      <c r="G79" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="16" t="inlineStr"/>
+      <c r="I79" s="16" t="inlineStr">
         <is>
           <t>내려찍기 70%</t>
         </is>
@@ -9821,8 +9999,11 @@
       <c r="F80" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="G80" s="16" t="inlineStr"/>
+      <c r="G80" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H80" s="16" t="inlineStr"/>
+      <c r="I80" s="16" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
@@ -9851,8 +10032,11 @@
         </is>
       </c>
       <c r="F81" s="16" t="inlineStr"/>
-      <c r="G81" s="16" t="inlineStr"/>
+      <c r="G81" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H81" s="16" t="inlineStr"/>
+      <c r="I81" s="16" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
@@ -9881,12 +10065,13 @@
         </is>
       </c>
       <c r="F82" s="16" t="inlineStr"/>
-      <c r="G82" s="16" t="inlineStr">
+      <c r="G82" s="16" t="inlineStr"/>
+      <c r="H82" s="16" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H82" s="16" t="inlineStr"/>
+      <c r="I82" s="16" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
@@ -9915,12 +10100,13 @@
         </is>
       </c>
       <c r="F83" s="16" t="inlineStr"/>
-      <c r="G83" s="16" t="inlineStr">
+      <c r="G83" s="16" t="inlineStr"/>
+      <c r="H83" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H83" s="16" t="inlineStr"/>
+      <c r="I83" s="16" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
@@ -9949,8 +10135,11 @@
         </is>
       </c>
       <c r="F84" s="16" t="inlineStr"/>
-      <c r="G84" s="16" t="inlineStr"/>
+      <c r="G84" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H84" s="16" t="inlineStr"/>
+      <c r="I84" s="16" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
@@ -9979,12 +10168,15 @@
         </is>
       </c>
       <c r="F85" s="16" t="inlineStr"/>
-      <c r="G85" s="16" t="inlineStr">
+      <c r="G85" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="16" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H85" s="16" t="inlineStr">
+      <c r="I85" s="16" t="inlineStr">
         <is>
           <t>솔기 뜯기 70%</t>
         </is>
@@ -10019,8 +10211,11 @@
       <c r="F86" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="G86" s="16" t="inlineStr"/>
+      <c r="G86" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H86" s="16" t="inlineStr"/>
+      <c r="I86" s="16" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
@@ -10049,8 +10244,11 @@
         </is>
       </c>
       <c r="F87" s="16" t="inlineStr"/>
-      <c r="G87" s="16" t="inlineStr"/>
+      <c r="G87" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H87" s="16" t="inlineStr"/>
+      <c r="I87" s="16" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
@@ -10079,12 +10277,13 @@
         </is>
       </c>
       <c r="F88" s="16" t="inlineStr"/>
-      <c r="G88" s="16" t="inlineStr">
+      <c r="G88" s="16" t="inlineStr"/>
+      <c r="H88" s="16" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H88" s="16" t="inlineStr"/>
+      <c r="I88" s="16" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
@@ -10113,12 +10312,13 @@
         </is>
       </c>
       <c r="F89" s="16" t="inlineStr"/>
-      <c r="G89" s="16" t="inlineStr">
+      <c r="G89" s="16" t="inlineStr"/>
+      <c r="H89" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H89" s="16" t="inlineStr"/>
+      <c r="I89" s="16" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
@@ -10147,8 +10347,11 @@
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr"/>
-      <c r="G90" s="8" t="inlineStr"/>
+      <c r="G90" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H90" s="8" t="inlineStr"/>
+      <c r="I90" s="8" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -10177,8 +10380,11 @@
         </is>
       </c>
       <c r="F91" s="8" t="inlineStr"/>
-      <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="8" t="inlineStr">
+      <c r="G91" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="8" t="inlineStr"/>
+      <c r="I91" s="8" t="inlineStr">
         <is>
           <t>독침 뱉기 50%</t>
         </is>
@@ -10213,8 +10419,11 @@
       <c r="F92" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G92" s="8" t="inlineStr"/>
+      <c r="G92" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H92" s="8" t="inlineStr"/>
+      <c r="I92" s="8" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -10243,12 +10452,13 @@
         </is>
       </c>
       <c r="F93" s="8" t="inlineStr"/>
-      <c r="G93" s="8" t="inlineStr">
+      <c r="G93" s="8" t="inlineStr"/>
+      <c r="H93" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H93" s="8" t="inlineStr"/>
+      <c r="I93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
@@ -10277,12 +10487,13 @@
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr"/>
-      <c r="G94" s="8" t="inlineStr">
+      <c r="G94" s="8" t="inlineStr"/>
+      <c r="H94" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H94" s="8" t="inlineStr"/>
+      <c r="I94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -10313,8 +10524,11 @@
       <c r="F95" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G95" s="8" t="inlineStr"/>
+      <c r="G95" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H95" s="8" t="inlineStr"/>
+      <c r="I95" s="8" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
@@ -10343,8 +10557,11 @@
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr"/>
-      <c r="G96" s="8" t="inlineStr"/>
-      <c r="H96" s="8" t="inlineStr">
+      <c r="G96" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="8" t="inlineStr"/>
+      <c r="I96" s="8" t="inlineStr">
         <is>
           <t>흡혈 50%</t>
         </is>
@@ -10377,8 +10594,11 @@
         </is>
       </c>
       <c r="F97" s="8" t="inlineStr"/>
-      <c r="G97" s="8" t="inlineStr"/>
+      <c r="G97" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H97" s="8" t="inlineStr"/>
+      <c r="I97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
@@ -10407,12 +10627,13 @@
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr"/>
-      <c r="G98" s="8" t="inlineStr">
+      <c r="G98" s="8" t="inlineStr"/>
+      <c r="H98" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H98" s="8" t="inlineStr"/>
+      <c r="I98" s="8" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -10441,12 +10662,13 @@
         </is>
       </c>
       <c r="F99" s="8" t="inlineStr"/>
-      <c r="G99" s="8" t="inlineStr">
+      <c r="G99" s="8" t="inlineStr"/>
+      <c r="H99" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H99" s="8" t="inlineStr"/>
+      <c r="I99" s="8" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
@@ -10475,8 +10697,11 @@
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr"/>
-      <c r="G100" s="8" t="inlineStr"/>
+      <c r="G100" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H100" s="8" t="inlineStr"/>
+      <c r="I100" s="8" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
@@ -10505,12 +10730,15 @@
         </is>
       </c>
       <c r="F101" s="8" t="inlineStr"/>
-      <c r="G101" s="8" t="inlineStr">
+      <c r="G101" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H101" s="8" t="inlineStr">
+      <c r="I101" s="8" t="inlineStr">
         <is>
           <t>곡소리 50%</t>
         </is>
@@ -10545,8 +10773,11 @@
       <c r="F102" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G102" s="8" t="inlineStr"/>
+      <c r="G102" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H102" s="8" t="inlineStr"/>
+      <c r="I102" s="8" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
@@ -10575,12 +10806,13 @@
         </is>
       </c>
       <c r="F103" s="8" t="inlineStr"/>
-      <c r="G103" s="8" t="inlineStr">
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H103" s="8" t="inlineStr"/>
+      <c r="I103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
@@ -10609,12 +10841,13 @@
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr"/>
-      <c r="G104" s="8" t="inlineStr">
+      <c r="G104" s="8" t="inlineStr"/>
+      <c r="H104" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H104" s="8" t="inlineStr"/>
+      <c r="I104" s="8" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
@@ -10643,8 +10876,11 @@
         </is>
       </c>
       <c r="F105" s="8" t="inlineStr"/>
-      <c r="G105" s="8" t="inlineStr"/>
+      <c r="G105" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H105" s="8" t="inlineStr"/>
+      <c r="I105" s="8" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
@@ -10673,12 +10909,15 @@
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr"/>
-      <c r="G106" s="8" t="inlineStr">
+      <c r="G106" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="8" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H106" s="8" t="inlineStr">
+      <c r="I106" s="8" t="inlineStr">
         <is>
           <t>짓밟기 50%</t>
         </is>
@@ -10713,8 +10952,11 @@
       <c r="F107" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G107" s="8" t="inlineStr"/>
+      <c r="G107" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H107" s="8" t="inlineStr"/>
+      <c r="I107" s="8" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
@@ -10743,12 +10985,13 @@
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr"/>
-      <c r="G108" s="8" t="inlineStr">
+      <c r="G108" s="8" t="inlineStr"/>
+      <c r="H108" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H108" s="8" t="inlineStr"/>
+      <c r="I108" s="8" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
@@ -10777,12 +11020,13 @@
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr"/>
-      <c r="G109" s="8" t="inlineStr">
+      <c r="G109" s="8" t="inlineStr"/>
+      <c r="H109" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H109" s="8" t="inlineStr"/>
+      <c r="I109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
@@ -10811,8 +11055,11 @@
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr"/>
-      <c r="G110" s="8" t="inlineStr"/>
+      <c r="G110" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H110" s="8" t="inlineStr"/>
+      <c r="I110" s="8" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
@@ -10841,8 +11088,11 @@
         </is>
       </c>
       <c r="F111" s="8" t="inlineStr"/>
-      <c r="G111" s="8" t="inlineStr"/>
-      <c r="H111" s="8" t="inlineStr">
+      <c r="G111" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="8" t="inlineStr"/>
+      <c r="I111" s="8" t="inlineStr">
         <is>
           <t>뼈 던지기 50%</t>
         </is>
@@ -10877,8 +11127,11 @@
       <c r="F112" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G112" s="8" t="inlineStr"/>
+      <c r="G112" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H112" s="8" t="inlineStr"/>
+      <c r="I112" s="8" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
@@ -10907,12 +11160,13 @@
         </is>
       </c>
       <c r="F113" s="8" t="inlineStr"/>
-      <c r="G113" s="8" t="inlineStr">
+      <c r="G113" s="8" t="inlineStr"/>
+      <c r="H113" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H113" s="8" t="inlineStr"/>
+      <c r="I113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
@@ -10941,12 +11195,13 @@
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr"/>
-      <c r="G114" s="8" t="inlineStr">
+      <c r="G114" s="8" t="inlineStr"/>
+      <c r="H114" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H114" s="8" t="inlineStr"/>
+      <c r="I114" s="8" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
@@ -10975,8 +11230,11 @@
         </is>
       </c>
       <c r="F115" s="8" t="inlineStr"/>
-      <c r="G115" s="8" t="inlineStr"/>
+      <c r="G115" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H115" s="8" t="inlineStr"/>
+      <c r="I115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
@@ -11005,12 +11263,15 @@
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr"/>
-      <c r="G116" s="8" t="inlineStr">
+      <c r="G116" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="8" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H116" s="8" t="inlineStr">
+      <c r="I116" s="8" t="inlineStr">
         <is>
           <t>분출 50%</t>
         </is>
@@ -11045,8 +11306,11 @@
       <c r="F117" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G117" s="8" t="inlineStr"/>
+      <c r="G117" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H117" s="8" t="inlineStr"/>
+      <c r="I117" s="8" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
@@ -11075,12 +11339,13 @@
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr"/>
-      <c r="G118" s="8" t="inlineStr">
+      <c r="G118" s="8" t="inlineStr"/>
+      <c r="H118" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H118" s="8" t="inlineStr"/>
+      <c r="I118" s="8" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
@@ -11109,12 +11374,13 @@
         </is>
       </c>
       <c r="F119" s="8" t="inlineStr"/>
-      <c r="G119" s="8" t="inlineStr">
+      <c r="G119" s="8" t="inlineStr"/>
+      <c r="H119" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H119" s="8" t="inlineStr"/>
+      <c r="I119" s="8" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
@@ -11143,8 +11409,11 @@
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr"/>
-      <c r="G120" s="10" t="inlineStr"/>
+      <c r="G120" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H120" s="10" t="inlineStr"/>
+      <c r="I120" s="10" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
@@ -11173,8 +11442,11 @@
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr"/>
-      <c r="G121" s="10" t="inlineStr"/>
-      <c r="H121" s="10" t="inlineStr">
+      <c r="G121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="10" t="inlineStr"/>
+      <c r="I121" s="10" t="inlineStr">
         <is>
           <t>진동 60%</t>
         </is>
@@ -11209,8 +11481,11 @@
       <c r="F122" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G122" s="10" t="inlineStr"/>
+      <c r="G122" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H122" s="10" t="inlineStr"/>
+      <c r="I122" s="10" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
@@ -11239,12 +11514,13 @@
         </is>
       </c>
       <c r="F123" s="10" t="inlineStr"/>
-      <c r="G123" s="10" t="inlineStr">
+      <c r="G123" s="10" t="inlineStr"/>
+      <c r="H123" s="10" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H123" s="10" t="inlineStr"/>
+      <c r="I123" s="10" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
@@ -11273,12 +11549,13 @@
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr"/>
-      <c r="G124" s="10" t="inlineStr">
+      <c r="G124" s="10" t="inlineStr"/>
+      <c r="H124" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H124" s="10" t="inlineStr"/>
+      <c r="I124" s="10" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
@@ -11307,8 +11584,11 @@
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr"/>
-      <c r="G125" s="10" t="inlineStr"/>
+      <c r="G125" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H125" s="10" t="inlineStr"/>
+      <c r="I125" s="10" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
@@ -11337,8 +11617,11 @@
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr"/>
-      <c r="G126" s="10" t="inlineStr"/>
-      <c r="H126" s="10" t="inlineStr">
+      <c r="G126" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="10" t="inlineStr"/>
+      <c r="I126" s="10" t="inlineStr">
         <is>
           <t>참격 60%</t>
         </is>
@@ -11373,8 +11656,11 @@
       <c r="F127" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G127" s="10" t="inlineStr"/>
+      <c r="G127" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H127" s="10" t="inlineStr"/>
+      <c r="I127" s="10" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
@@ -11403,12 +11689,13 @@
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr"/>
-      <c r="G128" s="10" t="inlineStr">
+      <c r="G128" s="10" t="inlineStr"/>
+      <c r="H128" s="10" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H128" s="10" t="inlineStr"/>
+      <c r="I128" s="10" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
@@ -11437,12 +11724,13 @@
         </is>
       </c>
       <c r="F129" s="10" t="inlineStr"/>
-      <c r="G129" s="10" t="inlineStr">
+      <c r="G129" s="10" t="inlineStr"/>
+      <c r="H129" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H129" s="10" t="inlineStr"/>
+      <c r="I129" s="10" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
@@ -11471,8 +11759,11 @@
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr"/>
-      <c r="G130" s="10" t="inlineStr"/>
+      <c r="G130" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H130" s="10" t="inlineStr"/>
+      <c r="I130" s="10" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
@@ -11501,8 +11792,11 @@
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr"/>
-      <c r="G131" s="10" t="inlineStr"/>
-      <c r="H131" s="10" t="inlineStr">
+      <c r="G131" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="10" t="inlineStr"/>
+      <c r="I131" s="10" t="inlineStr">
         <is>
           <t>매장 60%</t>
         </is>
@@ -11537,8 +11831,11 @@
       <c r="F132" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G132" s="10" t="inlineStr"/>
+      <c r="G132" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H132" s="10" t="inlineStr"/>
+      <c r="I132" s="10" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
@@ -11567,12 +11864,13 @@
         </is>
       </c>
       <c r="F133" s="10" t="inlineStr"/>
-      <c r="G133" s="10" t="inlineStr">
+      <c r="G133" s="10" t="inlineStr"/>
+      <c r="H133" s="10" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H133" s="10" t="inlineStr"/>
+      <c r="I133" s="10" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
@@ -11601,12 +11899,13 @@
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr"/>
-      <c r="G134" s="10" t="inlineStr">
+      <c r="G134" s="10" t="inlineStr"/>
+      <c r="H134" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H134" s="10" t="inlineStr"/>
+      <c r="I134" s="10" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="16" t="inlineStr">
@@ -11635,8 +11934,11 @@
         </is>
       </c>
       <c r="F135" s="16" t="inlineStr"/>
-      <c r="G135" s="16" t="inlineStr"/>
+      <c r="G135" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H135" s="16" t="inlineStr"/>
+      <c r="I135" s="16" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="16" t="inlineStr">
@@ -11665,12 +11967,15 @@
         </is>
       </c>
       <c r="F136" s="16" t="inlineStr"/>
-      <c r="G136" s="16" t="inlineStr">
+      <c r="G136" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="16" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H136" s="16" t="inlineStr">
+      <c r="I136" s="16" t="inlineStr">
         <is>
           <t>죽음의 회전 70%</t>
         </is>
@@ -11705,8 +12010,11 @@
       <c r="F137" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="G137" s="16" t="inlineStr"/>
+      <c r="G137" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H137" s="16" t="inlineStr"/>
+      <c r="I137" s="16" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="16" t="inlineStr">
@@ -11735,8 +12043,11 @@
         </is>
       </c>
       <c r="F138" s="16" t="inlineStr"/>
-      <c r="G138" s="16" t="inlineStr"/>
+      <c r="G138" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H138" s="16" t="inlineStr"/>
+      <c r="I138" s="16" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="16" t="inlineStr">
@@ -11765,12 +12076,13 @@
         </is>
       </c>
       <c r="F139" s="16" t="inlineStr"/>
-      <c r="G139" s="16" t="inlineStr">
+      <c r="G139" s="16" t="inlineStr"/>
+      <c r="H139" s="16" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H139" s="16" t="inlineStr"/>
+      <c r="I139" s="16" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="16" t="inlineStr">
@@ -11799,12 +12111,13 @@
         </is>
       </c>
       <c r="F140" s="16" t="inlineStr"/>
-      <c r="G140" s="16" t="inlineStr">
+      <c r="G140" s="16" t="inlineStr"/>
+      <c r="H140" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H140" s="16" t="inlineStr"/>
+      <c r="I140" s="16" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="16" t="inlineStr">
@@ -11833,8 +12146,11 @@
         </is>
       </c>
       <c r="F141" s="16" t="inlineStr"/>
-      <c r="G141" s="16" t="inlineStr"/>
+      <c r="G141" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H141" s="16" t="inlineStr"/>
+      <c r="I141" s="16" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="16" t="inlineStr">
@@ -11863,8 +12179,11 @@
         </is>
       </c>
       <c r="F142" s="16" t="inlineStr"/>
-      <c r="G142" s="16" t="inlineStr"/>
-      <c r="H142" s="16" t="inlineStr">
+      <c r="G142" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" s="16" t="inlineStr"/>
+      <c r="I142" s="16" t="inlineStr">
         <is>
           <t>질식 70%</t>
         </is>
@@ -11899,8 +12218,11 @@
       <c r="F143" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="G143" s="16" t="inlineStr"/>
+      <c r="G143" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H143" s="16" t="inlineStr"/>
+      <c r="I143" s="16" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="16" t="inlineStr">
@@ -11929,8 +12251,11 @@
         </is>
       </c>
       <c r="F144" s="16" t="inlineStr"/>
-      <c r="G144" s="16" t="inlineStr"/>
+      <c r="G144" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H144" s="16" t="inlineStr"/>
+      <c r="I144" s="16" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="16" t="inlineStr">
@@ -11959,12 +12284,13 @@
         </is>
       </c>
       <c r="F145" s="16" t="inlineStr"/>
-      <c r="G145" s="16" t="inlineStr">
+      <c r="G145" s="16" t="inlineStr"/>
+      <c r="H145" s="16" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H145" s="16" t="inlineStr"/>
+      <c r="I145" s="16" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="16" t="inlineStr">
@@ -11993,12 +12319,13 @@
         </is>
       </c>
       <c r="F146" s="16" t="inlineStr"/>
-      <c r="G146" s="16" t="inlineStr">
+      <c r="G146" s="16" t="inlineStr"/>
+      <c r="H146" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H146" s="16" t="inlineStr"/>
+      <c r="I146" s="16" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="16" t="inlineStr">
@@ -12027,8 +12354,11 @@
         </is>
       </c>
       <c r="F147" s="16" t="inlineStr"/>
-      <c r="G147" s="16" t="inlineStr"/>
+      <c r="G147" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H147" s="16" t="inlineStr"/>
+      <c r="I147" s="16" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="16" t="inlineStr">
@@ -12057,8 +12387,11 @@
         </is>
       </c>
       <c r="F148" s="16" t="inlineStr"/>
-      <c r="G148" s="16" t="inlineStr"/>
-      <c r="H148" s="16" t="inlineStr">
+      <c r="G148" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="16" t="inlineStr"/>
+      <c r="I148" s="16" t="inlineStr">
         <is>
           <t>무덤의 부름 70%</t>
         </is>
@@ -12093,8 +12426,11 @@
       <c r="F149" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="G149" s="16" t="inlineStr"/>
+      <c r="G149" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H149" s="16" t="inlineStr"/>
+      <c r="I149" s="16" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="16" t="inlineStr">
@@ -12123,8 +12459,11 @@
         </is>
       </c>
       <c r="F150" s="16" t="inlineStr"/>
-      <c r="G150" s="16" t="inlineStr"/>
+      <c r="G150" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H150" s="16" t="inlineStr"/>
+      <c r="I150" s="16" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="16" t="inlineStr">
@@ -12153,12 +12492,13 @@
         </is>
       </c>
       <c r="F151" s="16" t="inlineStr"/>
-      <c r="G151" s="16" t="inlineStr">
+      <c r="G151" s="16" t="inlineStr"/>
+      <c r="H151" s="16" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H151" s="16" t="inlineStr"/>
+      <c r="I151" s="16" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="16" t="inlineStr">
@@ -12187,12 +12527,13 @@
         </is>
       </c>
       <c r="F152" s="16" t="inlineStr"/>
-      <c r="G152" s="16" t="inlineStr">
+      <c r="G152" s="16" t="inlineStr"/>
+      <c r="H152" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H152" s="16" t="inlineStr"/>
+      <c r="I152" s="16" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
@@ -12221,8 +12562,11 @@
         </is>
       </c>
       <c r="F153" s="8" t="inlineStr"/>
-      <c r="G153" s="8" t="inlineStr"/>
+      <c r="G153" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H153" s="8" t="inlineStr"/>
+      <c r="I153" s="8" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="8" t="inlineStr">
@@ -12251,8 +12595,11 @@
         </is>
       </c>
       <c r="F154" s="8" t="inlineStr"/>
-      <c r="G154" s="8" t="inlineStr"/>
-      <c r="H154" s="8" t="inlineStr">
+      <c r="G154" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" s="8" t="inlineStr"/>
+      <c r="I154" s="8" t="inlineStr">
         <is>
           <t>끽 소리 50%</t>
         </is>
@@ -12287,8 +12634,11 @@
       <c r="F155" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G155" s="8" t="inlineStr"/>
+      <c r="G155" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H155" s="8" t="inlineStr"/>
+      <c r="I155" s="8" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="8" t="inlineStr">
@@ -12317,12 +12667,13 @@
         </is>
       </c>
       <c r="F156" s="8" t="inlineStr"/>
-      <c r="G156" s="8" t="inlineStr">
+      <c r="G156" s="8" t="inlineStr"/>
+      <c r="H156" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H156" s="8" t="inlineStr"/>
+      <c r="I156" s="8" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
@@ -12351,12 +12702,13 @@
         </is>
       </c>
       <c r="F157" s="8" t="inlineStr"/>
-      <c r="G157" s="8" t="inlineStr">
+      <c r="G157" s="8" t="inlineStr"/>
+      <c r="H157" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H157" s="8" t="inlineStr"/>
+      <c r="I157" s="8" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="8" t="inlineStr">
@@ -12385,8 +12737,11 @@
         </is>
       </c>
       <c r="F158" s="8" t="inlineStr"/>
-      <c r="G158" s="8" t="inlineStr"/>
-      <c r="H158" s="8" t="inlineStr">
+      <c r="G158" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" s="8" t="inlineStr"/>
+      <c r="I158" s="8" t="inlineStr">
         <is>
           <t>시선 광선 50%</t>
         </is>
@@ -12421,8 +12776,11 @@
       <c r="F159" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G159" s="8" t="inlineStr"/>
+      <c r="G159" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H159" s="8" t="inlineStr"/>
+      <c r="I159" s="8" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="8" t="inlineStr">
@@ -12451,12 +12809,15 @@
         </is>
       </c>
       <c r="F160" s="8" t="inlineStr"/>
-      <c r="G160" s="8" t="inlineStr">
+      <c r="G160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="8" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H160" s="8" t="inlineStr"/>
+      <c r="I160" s="8" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
@@ -12485,12 +12846,13 @@
         </is>
       </c>
       <c r="F161" s="8" t="inlineStr"/>
-      <c r="G161" s="8" t="inlineStr">
+      <c r="G161" s="8" t="inlineStr"/>
+      <c r="H161" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H161" s="8" t="inlineStr"/>
+      <c r="I161" s="8" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="8" t="inlineStr">
@@ -12519,12 +12881,13 @@
         </is>
       </c>
       <c r="F162" s="8" t="inlineStr"/>
-      <c r="G162" s="8" t="inlineStr">
+      <c r="G162" s="8" t="inlineStr"/>
+      <c r="H162" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H162" s="8" t="inlineStr"/>
+      <c r="I162" s="8" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
@@ -12553,8 +12916,11 @@
         </is>
       </c>
       <c r="F163" s="8" t="inlineStr"/>
-      <c r="G163" s="8" t="inlineStr"/>
+      <c r="G163" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H163" s="8" t="inlineStr"/>
+      <c r="I163" s="8" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="8" t="inlineStr">
@@ -12585,8 +12951,11 @@
       <c r="F164" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G164" s="8" t="inlineStr"/>
-      <c r="H164" s="8" t="inlineStr">
+      <c r="G164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="8" t="inlineStr"/>
+      <c r="I164" s="8" t="inlineStr">
         <is>
           <t>고치 50%</t>
         </is>
@@ -12619,8 +12988,11 @@
         </is>
       </c>
       <c r="F165" s="8" t="inlineStr"/>
-      <c r="G165" s="8" t="inlineStr"/>
+      <c r="G165" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H165" s="8" t="inlineStr"/>
+      <c r="I165" s="8" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="8" t="inlineStr">
@@ -12649,12 +13021,13 @@
         </is>
       </c>
       <c r="F166" s="8" t="inlineStr"/>
-      <c r="G166" s="8" t="inlineStr">
+      <c r="G166" s="8" t="inlineStr"/>
+      <c r="H166" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H166" s="8" t="inlineStr"/>
+      <c r="I166" s="8" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
@@ -12683,12 +13056,13 @@
         </is>
       </c>
       <c r="F167" s="8" t="inlineStr"/>
-      <c r="G167" s="8" t="inlineStr">
+      <c r="G167" s="8" t="inlineStr"/>
+      <c r="H167" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H167" s="8" t="inlineStr"/>
+      <c r="I167" s="8" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="8" t="inlineStr">
@@ -12717,8 +13091,11 @@
         </is>
       </c>
       <c r="F168" s="8" t="inlineStr"/>
-      <c r="G168" s="8" t="inlineStr"/>
-      <c r="H168" s="8" t="inlineStr">
+      <c r="G168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" s="8" t="inlineStr"/>
+      <c r="I168" s="8" t="inlineStr">
         <is>
           <t>맥동 50%</t>
         </is>
@@ -12751,8 +13128,11 @@
         </is>
       </c>
       <c r="F169" s="8" t="inlineStr"/>
-      <c r="G169" s="8" t="inlineStr"/>
+      <c r="G169" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H169" s="8" t="inlineStr"/>
+      <c r="I169" s="8" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="8" t="inlineStr">
@@ -12783,8 +13163,11 @@
       <c r="F170" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G170" s="8" t="inlineStr"/>
+      <c r="G170" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H170" s="8" t="inlineStr"/>
+      <c r="I170" s="8" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="8" t="inlineStr">
@@ -12813,12 +13196,13 @@
         </is>
       </c>
       <c r="F171" s="8" t="inlineStr"/>
-      <c r="G171" s="8" t="inlineStr">
+      <c r="G171" s="8" t="inlineStr"/>
+      <c r="H171" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H171" s="8" t="inlineStr"/>
+      <c r="I171" s="8" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="8" t="inlineStr">
@@ -12847,12 +13231,13 @@
         </is>
       </c>
       <c r="F172" s="8" t="inlineStr"/>
-      <c r="G172" s="8" t="inlineStr">
+      <c r="G172" s="8" t="inlineStr"/>
+      <c r="H172" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H172" s="8" t="inlineStr"/>
+      <c r="I172" s="8" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="8" t="inlineStr">
@@ -12881,8 +13266,11 @@
         </is>
       </c>
       <c r="F173" s="8" t="inlineStr"/>
-      <c r="G173" s="8" t="inlineStr"/>
+      <c r="G173" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H173" s="8" t="inlineStr"/>
+      <c r="I173" s="8" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="8" t="inlineStr">
@@ -12911,12 +13299,15 @@
         </is>
       </c>
       <c r="F174" s="8" t="inlineStr"/>
-      <c r="G174" s="8" t="inlineStr">
+      <c r="G174" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" s="8" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H174" s="8" t="inlineStr">
+      <c r="I174" s="8" t="inlineStr">
         <is>
           <t>제물 50%</t>
         </is>
@@ -12951,8 +13342,11 @@
       <c r="F175" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G175" s="8" t="inlineStr"/>
+      <c r="G175" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H175" s="8" t="inlineStr"/>
+      <c r="I175" s="8" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="8" t="inlineStr">
@@ -12981,12 +13375,13 @@
         </is>
       </c>
       <c r="F176" s="8" t="inlineStr"/>
-      <c r="G176" s="8" t="inlineStr">
+      <c r="G176" s="8" t="inlineStr"/>
+      <c r="H176" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H176" s="8" t="inlineStr"/>
+      <c r="I176" s="8" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="8" t="inlineStr">
@@ -13015,12 +13410,13 @@
         </is>
       </c>
       <c r="F177" s="8" t="inlineStr"/>
-      <c r="G177" s="8" t="inlineStr">
+      <c r="G177" s="8" t="inlineStr"/>
+      <c r="H177" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H177" s="8" t="inlineStr"/>
+      <c r="I177" s="8" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="8" t="inlineStr">
@@ -13049,8 +13445,11 @@
         </is>
       </c>
       <c r="F178" s="8" t="inlineStr"/>
-      <c r="G178" s="8" t="inlineStr"/>
+      <c r="G178" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H178" s="8" t="inlineStr"/>
+      <c r="I178" s="8" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="8" t="inlineStr">
@@ -13079,8 +13478,11 @@
         </is>
       </c>
       <c r="F179" s="8" t="inlineStr"/>
-      <c r="G179" s="8" t="inlineStr"/>
-      <c r="H179" s="8" t="inlineStr">
+      <c r="G179" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" s="8" t="inlineStr"/>
+      <c r="I179" s="8" t="inlineStr">
         <is>
           <t>균열 50%</t>
         </is>
@@ -13115,8 +13517,11 @@
       <c r="F180" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G180" s="8" t="inlineStr"/>
+      <c r="G180" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H180" s="8" t="inlineStr"/>
+      <c r="I180" s="8" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="8" t="inlineStr">
@@ -13145,12 +13550,13 @@
         </is>
       </c>
       <c r="F181" s="8" t="inlineStr"/>
-      <c r="G181" s="8" t="inlineStr">
+      <c r="G181" s="8" t="inlineStr"/>
+      <c r="H181" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H181" s="8" t="inlineStr"/>
+      <c r="I181" s="8" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="8" t="inlineStr">
@@ -13179,12 +13585,13 @@
         </is>
       </c>
       <c r="F182" s="8" t="inlineStr"/>
-      <c r="G182" s="8" t="inlineStr">
+      <c r="G182" s="8" t="inlineStr"/>
+      <c r="H182" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H182" s="8" t="inlineStr"/>
+      <c r="I182" s="8" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="10" t="inlineStr">
@@ -13213,8 +13620,11 @@
         </is>
       </c>
       <c r="F183" s="10" t="inlineStr"/>
-      <c r="G183" s="10" t="inlineStr"/>
+      <c r="G183" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H183" s="10" t="inlineStr"/>
+      <c r="I183" s="10" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="10" t="inlineStr">
@@ -13243,8 +13653,11 @@
         </is>
       </c>
       <c r="F184" s="10" t="inlineStr"/>
-      <c r="G184" s="10" t="inlineStr"/>
+      <c r="G184" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H184" s="10" t="inlineStr"/>
+      <c r="I184" s="10" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="10" t="inlineStr">
@@ -13273,8 +13686,11 @@
         </is>
       </c>
       <c r="F185" s="10" t="inlineStr"/>
-      <c r="G185" s="10" t="inlineStr"/>
-      <c r="H185" s="10" t="inlineStr">
+      <c r="G185" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" s="10" t="inlineStr"/>
+      <c r="I185" s="10" t="inlineStr">
         <is>
           <t>붕괴 60%</t>
         </is>
@@ -13309,8 +13725,11 @@
       <c r="F186" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G186" s="10" t="inlineStr"/>
+      <c r="G186" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H186" s="10" t="inlineStr"/>
+      <c r="I186" s="10" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="10" t="inlineStr">
@@ -13339,12 +13758,13 @@
         </is>
       </c>
       <c r="F187" s="10" t="inlineStr"/>
-      <c r="G187" s="10" t="inlineStr">
+      <c r="G187" s="10" t="inlineStr"/>
+      <c r="H187" s="10" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H187" s="10" t="inlineStr"/>
+      <c r="I187" s="10" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="10" t="inlineStr">
@@ -13373,12 +13793,13 @@
         </is>
       </c>
       <c r="F188" s="10" t="inlineStr"/>
-      <c r="G188" s="10" t="inlineStr">
+      <c r="G188" s="10" t="inlineStr"/>
+      <c r="H188" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H188" s="10" t="inlineStr"/>
+      <c r="I188" s="10" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="10" t="inlineStr">
@@ -13407,8 +13828,11 @@
         </is>
       </c>
       <c r="F189" s="10" t="inlineStr"/>
-      <c r="G189" s="10" t="inlineStr"/>
+      <c r="G189" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H189" s="10" t="inlineStr"/>
+      <c r="I189" s="10" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="10" t="inlineStr">
@@ -13437,8 +13861,11 @@
         </is>
       </c>
       <c r="F190" s="10" t="inlineStr"/>
-      <c r="G190" s="10" t="inlineStr"/>
+      <c r="G190" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H190" s="10" t="inlineStr"/>
+      <c r="I190" s="10" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="10" t="inlineStr">
@@ -13467,8 +13894,11 @@
         </is>
       </c>
       <c r="F191" s="10" t="inlineStr"/>
-      <c r="G191" s="10" t="inlineStr"/>
-      <c r="H191" s="10" t="inlineStr">
+      <c r="G191" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" s="10" t="inlineStr"/>
+      <c r="I191" s="10" t="inlineStr">
         <is>
           <t>내려찍기 60%</t>
         </is>
@@ -13503,8 +13933,11 @@
       <c r="F192" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G192" s="10" t="inlineStr"/>
+      <c r="G192" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H192" s="10" t="inlineStr"/>
+      <c r="I192" s="10" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="10" t="inlineStr">
@@ -13533,12 +13966,13 @@
         </is>
       </c>
       <c r="F193" s="10" t="inlineStr"/>
-      <c r="G193" s="10" t="inlineStr">
+      <c r="G193" s="10" t="inlineStr"/>
+      <c r="H193" s="10" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H193" s="10" t="inlineStr"/>
+      <c r="I193" s="10" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="10" t="inlineStr">
@@ -13567,12 +14001,13 @@
         </is>
       </c>
       <c r="F194" s="10" t="inlineStr"/>
-      <c r="G194" s="10" t="inlineStr">
+      <c r="G194" s="10" t="inlineStr"/>
+      <c r="H194" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H194" s="10" t="inlineStr"/>
+      <c r="I194" s="10" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="10" t="inlineStr">
@@ -13601,8 +14036,11 @@
         </is>
       </c>
       <c r="F195" s="10" t="inlineStr"/>
-      <c r="G195" s="10" t="inlineStr"/>
+      <c r="G195" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H195" s="10" t="inlineStr"/>
+      <c r="I195" s="10" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="10" t="inlineStr">
@@ -13631,12 +14069,15 @@
         </is>
       </c>
       <c r="F196" s="10" t="inlineStr"/>
-      <c r="G196" s="10" t="inlineStr">
+      <c r="G196" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" s="10" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H196" s="10" t="inlineStr">
+      <c r="I196" s="10" t="inlineStr">
         <is>
           <t>큰 종소리 60%</t>
         </is>
@@ -13671,8 +14112,11 @@
       <c r="F197" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G197" s="10" t="inlineStr"/>
+      <c r="G197" s="10" t="n">
+        <v>0</v>
+      </c>
       <c r="H197" s="10" t="inlineStr"/>
+      <c r="I197" s="10" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="10" t="inlineStr">
@@ -13701,12 +14145,13 @@
         </is>
       </c>
       <c r="F198" s="10" t="inlineStr"/>
-      <c r="G198" s="10" t="inlineStr">
+      <c r="G198" s="10" t="inlineStr"/>
+      <c r="H198" s="10" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H198" s="10" t="inlineStr"/>
+      <c r="I198" s="10" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="10" t="inlineStr">
@@ -13735,12 +14180,13 @@
         </is>
       </c>
       <c r="F199" s="10" t="inlineStr"/>
-      <c r="G199" s="10" t="inlineStr">
+      <c r="G199" s="10" t="inlineStr"/>
+      <c r="H199" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H199" s="10" t="inlineStr"/>
+      <c r="I199" s="10" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="16" t="inlineStr">
@@ -13769,8 +14215,11 @@
         </is>
       </c>
       <c r="F200" s="16" t="inlineStr"/>
-      <c r="G200" s="16" t="inlineStr"/>
+      <c r="G200" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H200" s="16" t="inlineStr"/>
+      <c r="I200" s="16" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="16" t="inlineStr">
@@ -13799,12 +14248,15 @@
         </is>
       </c>
       <c r="F201" s="16" t="inlineStr"/>
-      <c r="G201" s="16" t="inlineStr">
+      <c r="G201" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" s="16" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H201" s="16" t="inlineStr">
+      <c r="I201" s="16" t="inlineStr">
         <is>
           <t>악몽 70%</t>
         </is>
@@ -13839,8 +14291,11 @@
       <c r="F202" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="G202" s="16" t="inlineStr"/>
+      <c r="G202" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H202" s="16" t="inlineStr"/>
+      <c r="I202" s="16" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="16" t="inlineStr">
@@ -13869,8 +14324,11 @@
         </is>
       </c>
       <c r="F203" s="16" t="inlineStr"/>
-      <c r="G203" s="16" t="inlineStr"/>
+      <c r="G203" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H203" s="16" t="inlineStr"/>
+      <c r="I203" s="16" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="16" t="inlineStr">
@@ -13899,12 +14357,13 @@
         </is>
       </c>
       <c r="F204" s="16" t="inlineStr"/>
-      <c r="G204" s="16" t="inlineStr">
+      <c r="G204" s="16" t="inlineStr"/>
+      <c r="H204" s="16" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H204" s="16" t="inlineStr"/>
+      <c r="I204" s="16" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="16" t="inlineStr">
@@ -13933,12 +14392,13 @@
         </is>
       </c>
       <c r="F205" s="16" t="inlineStr"/>
-      <c r="G205" s="16" t="inlineStr">
+      <c r="G205" s="16" t="inlineStr"/>
+      <c r="H205" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H205" s="16" t="inlineStr"/>
+      <c r="I205" s="16" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="16" t="inlineStr">
@@ -13967,8 +14427,11 @@
         </is>
       </c>
       <c r="F206" s="16" t="inlineStr"/>
-      <c r="G206" s="16" t="inlineStr"/>
+      <c r="G206" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H206" s="16" t="inlineStr"/>
+      <c r="I206" s="16" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="16" t="inlineStr">
@@ -13997,8 +14460,11 @@
         </is>
       </c>
       <c r="F207" s="16" t="inlineStr"/>
-      <c r="G207" s="16" t="inlineStr"/>
-      <c r="H207" s="16" t="inlineStr">
+      <c r="G207" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" s="16" t="inlineStr"/>
+      <c r="I207" s="16" t="inlineStr">
         <is>
           <t>빛 삼키기 70%</t>
         </is>
@@ -14031,8 +14497,11 @@
         </is>
       </c>
       <c r="F208" s="16" t="inlineStr"/>
-      <c r="G208" s="16" t="inlineStr"/>
+      <c r="G208" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H208" s="16" t="inlineStr"/>
+      <c r="I208" s="16" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="16" t="inlineStr">
@@ -14063,8 +14532,11 @@
       <c r="F209" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="G209" s="16" t="inlineStr"/>
+      <c r="G209" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H209" s="16" t="inlineStr"/>
+      <c r="I209" s="16" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="16" t="inlineStr">
@@ -14093,12 +14565,13 @@
         </is>
       </c>
       <c r="F210" s="16" t="inlineStr"/>
-      <c r="G210" s="16" t="inlineStr">
+      <c r="G210" s="16" t="inlineStr"/>
+      <c r="H210" s="16" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H210" s="16" t="inlineStr"/>
+      <c r="I210" s="16" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="16" t="inlineStr">
@@ -14127,12 +14600,13 @@
         </is>
       </c>
       <c r="F211" s="16" t="inlineStr"/>
-      <c r="G211" s="16" t="inlineStr">
+      <c r="G211" s="16" t="inlineStr"/>
+      <c r="H211" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H211" s="16" t="inlineStr"/>
+      <c r="I211" s="16" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="16" t="inlineStr">
@@ -14161,8 +14635,11 @@
         </is>
       </c>
       <c r="F212" s="16" t="inlineStr"/>
-      <c r="G212" s="16" t="inlineStr"/>
+      <c r="G212" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H212" s="16" t="inlineStr"/>
+      <c r="I212" s="16" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="16" t="inlineStr">
@@ -14191,8 +14668,11 @@
         </is>
       </c>
       <c r="F213" s="16" t="inlineStr"/>
-      <c r="G213" s="16" t="inlineStr"/>
+      <c r="G213" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H213" s="16" t="inlineStr"/>
+      <c r="I213" s="16" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="16" t="inlineStr">
@@ -14221,8 +14701,11 @@
         </is>
       </c>
       <c r="F214" s="16" t="inlineStr"/>
-      <c r="G214" s="16" t="inlineStr"/>
-      <c r="H214" s="16" t="inlineStr">
+      <c r="G214" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" s="16" t="inlineStr"/>
+      <c r="I214" s="16" t="inlineStr">
         <is>
           <t>심판 70%</t>
         </is>
@@ -14257,8 +14740,11 @@
       <c r="F215" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="G215" s="16" t="inlineStr"/>
+      <c r="G215" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H215" s="16" t="inlineStr"/>
+      <c r="I215" s="16" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="16" t="inlineStr">
@@ -14287,12 +14773,13 @@
         </is>
       </c>
       <c r="F216" s="16" t="inlineStr"/>
-      <c r="G216" s="16" t="inlineStr">
+      <c r="G216" s="16" t="inlineStr"/>
+      <c r="H216" s="16" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H216" s="16" t="inlineStr"/>
+      <c r="I216" s="16" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="16" t="inlineStr">
@@ -14321,12 +14808,13 @@
         </is>
       </c>
       <c r="F217" s="16" t="inlineStr"/>
-      <c r="G217" s="16" t="inlineStr">
+      <c r="G217" s="16" t="inlineStr"/>
+      <c r="H217" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H217" s="16" t="inlineStr"/>
+      <c r="I217" s="16" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="16" t="inlineStr">
@@ -14355,12 +14843,15 @@
         </is>
       </c>
       <c r="F218" s="16" t="inlineStr"/>
-      <c r="G218" s="16" t="inlineStr">
+      <c r="G218" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" s="16" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H218" s="16" t="inlineStr"/>
+      <c r="I218" s="16" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="16" t="inlineStr">
@@ -14389,8 +14880,11 @@
         </is>
       </c>
       <c r="F219" s="16" t="inlineStr"/>
-      <c r="G219" s="16" t="inlineStr"/>
+      <c r="G219" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H219" s="16" t="inlineStr"/>
+      <c r="I219" s="16" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="16" t="inlineStr">
@@ -14419,8 +14913,11 @@
         </is>
       </c>
       <c r="F220" s="16" t="inlineStr"/>
-      <c r="G220" s="16" t="inlineStr"/>
-      <c r="H220" s="16" t="inlineStr">
+      <c r="G220" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" s="16" t="inlineStr"/>
+      <c r="I220" s="16" t="inlineStr">
         <is>
           <t>지운다 70%</t>
         </is>
@@ -14455,8 +14952,11 @@
       <c r="F221" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="G221" s="16" t="inlineStr"/>
+      <c r="G221" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="H221" s="16" t="inlineStr"/>
+      <c r="I221" s="16" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="16" t="inlineStr">
@@ -14485,12 +14985,13 @@
         </is>
       </c>
       <c r="F222" s="16" t="inlineStr"/>
-      <c r="G222" s="16" t="inlineStr">
+      <c r="G222" s="16" t="inlineStr"/>
+      <c r="H222" s="16" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H222" s="16" t="inlineStr"/>
+      <c r="I222" s="16" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="16" t="inlineStr">
@@ -14519,12 +15020,13 @@
         </is>
       </c>
       <c r="F223" s="16" t="inlineStr"/>
-      <c r="G223" s="16" t="inlineStr">
+      <c r="G223" s="16" t="inlineStr"/>
+      <c r="H223" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H223" s="16" t="inlineStr"/>
+      <c r="I223" s="16" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="8" t="inlineStr">
@@ -14553,8 +15055,11 @@
         </is>
       </c>
       <c r="F224" s="8" t="inlineStr"/>
-      <c r="G224" s="8" t="inlineStr"/>
-      <c r="H224" s="8" t="inlineStr">
+      <c r="G224" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" s="8" t="inlineStr"/>
+      <c r="I224" s="8" t="inlineStr">
         <is>
           <t>지팡이 내리치기 50%</t>
         </is>
@@ -14589,8 +15094,11 @@
       <c r="F225" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G225" s="8" t="inlineStr"/>
+      <c r="G225" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H225" s="8" t="inlineStr"/>
+      <c r="I225" s="8" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="8" t="inlineStr">
@@ -14619,8 +15127,11 @@
         </is>
       </c>
       <c r="F226" s="8" t="inlineStr"/>
-      <c r="G226" s="8" t="inlineStr"/>
+      <c r="G226" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H226" s="8" t="inlineStr"/>
+      <c r="I226" s="8" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="8" t="inlineStr">
@@ -14649,12 +15160,13 @@
         </is>
       </c>
       <c r="F227" s="8" t="inlineStr"/>
-      <c r="G227" s="8" t="inlineStr">
+      <c r="G227" s="8" t="inlineStr"/>
+      <c r="H227" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H227" s="8" t="inlineStr"/>
+      <c r="I227" s="8" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="8" t="inlineStr">
@@ -14683,12 +15195,13 @@
         </is>
       </c>
       <c r="F228" s="8" t="inlineStr"/>
-      <c r="G228" s="8" t="inlineStr">
+      <c r="G228" s="8" t="inlineStr"/>
+      <c r="H228" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H228" s="8" t="inlineStr"/>
+      <c r="I228" s="8" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="8" t="inlineStr">
@@ -14717,8 +15230,11 @@
         </is>
       </c>
       <c r="F229" s="8" t="inlineStr"/>
-      <c r="G229" s="8" t="inlineStr"/>
+      <c r="G229" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H229" s="8" t="inlineStr"/>
+      <c r="I229" s="8" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="8" t="inlineStr">
@@ -14749,8 +15265,11 @@
       <c r="F230" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G230" s="8" t="inlineStr"/>
-      <c r="H230" s="8" t="inlineStr">
+      <c r="G230" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" s="8" t="inlineStr"/>
+      <c r="I230" s="8" t="inlineStr">
         <is>
           <t>어긋난 화음 50%</t>
         </is>
@@ -14783,12 +15302,15 @@
         </is>
       </c>
       <c r="F231" s="8" t="inlineStr"/>
-      <c r="G231" s="8" t="inlineStr">
+      <c r="G231" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" s="8" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="H231" s="8" t="inlineStr"/>
+      <c r="I231" s="8" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="8" t="inlineStr">
@@ -14817,12 +15339,13 @@
         </is>
       </c>
       <c r="F232" s="8" t="inlineStr"/>
-      <c r="G232" s="8" t="inlineStr">
+      <c r="G232" s="8" t="inlineStr"/>
+      <c r="H232" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H232" s="8" t="inlineStr"/>
+      <c r="I232" s="8" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="8" t="inlineStr">
@@ -14851,12 +15374,13 @@
         </is>
       </c>
       <c r="F233" s="8" t="inlineStr"/>
-      <c r="G233" s="8" t="inlineStr">
+      <c r="G233" s="8" t="inlineStr"/>
+      <c r="H233" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H233" s="8" t="inlineStr"/>
+      <c r="I233" s="8" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="8" t="inlineStr">
@@ -14885,8 +15409,11 @@
         </is>
       </c>
       <c r="F234" s="8" t="inlineStr"/>
-      <c r="G234" s="8" t="inlineStr"/>
+      <c r="G234" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H234" s="8" t="inlineStr"/>
+      <c r="I234" s="8" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="8" t="inlineStr">
@@ -14915,8 +15442,11 @@
         </is>
       </c>
       <c r="F235" s="8" t="inlineStr"/>
-      <c r="G235" s="8" t="inlineStr"/>
-      <c r="H235" s="8" t="inlineStr">
+      <c r="G235" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" s="8" t="inlineStr"/>
+      <c r="I235" s="8" t="inlineStr">
         <is>
           <t>확 타오르기 50%</t>
         </is>
@@ -14951,8 +15481,11 @@
       <c r="F236" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G236" s="8" t="inlineStr"/>
+      <c r="G236" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H236" s="8" t="inlineStr"/>
+      <c r="I236" s="8" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="8" t="inlineStr">
@@ -14981,12 +15514,13 @@
         </is>
       </c>
       <c r="F237" s="8" t="inlineStr"/>
-      <c r="G237" s="8" t="inlineStr">
+      <c r="G237" s="8" t="inlineStr"/>
+      <c r="H237" s="8" t="inlineStr">
         <is>
           <t>강화(4~6턴 주기)</t>
         </is>
       </c>
-      <c r="H237" s="8" t="inlineStr"/>
+      <c r="I237" s="8" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="8" t="inlineStr">
@@ -15015,12 +15549,13 @@
         </is>
       </c>
       <c r="F238" s="8" t="inlineStr"/>
-      <c r="G238" s="8" t="inlineStr">
+      <c r="G238" s="8" t="inlineStr"/>
+      <c r="H238" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="H238" s="8" t="inlineStr"/>
+      <c r="I238" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>각 적의 'surge' 행동 — 해금 턴 4, 쿨다운 4. 4턴 이후 주기적으로 힘을 올린다</t>
+          <t>각 적의 'surge' 행동 — 해금 턴 4, 쿨다운 3. 4턴 이후 5턴 안팎마다 힘을 올린다</t>
         </is>
       </c>
     </row>
@@ -7267,7 +7267,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>발동 조건 네 가지 — 가중치는 뽑힐 확률(0이면 추첨에서 빠지고 연계로만 나온다), 해금 턴은 "이 턴부터", 쿨다운은 "쓰고 나서 몇 턴 쉰다"(0=제한 없음), 연계는 "앞 행동 다음에 확률로 확정".</t>
+          <t>발동 조건 네 가지 — 가중치는 뽑힐 확률(0이면 추첨에서 빠지고 연계로만 나온다), 해금 턴은 "이 턴부터", 쿨다운은 "쓰고 나서 몇 턴 쉰다"(0=제한 없음, 2면 한 칸 걸러 나온다), 연계는 "앞 행동 다음에 확률로 확정".</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I7" s="8" t="inlineStr"/>
       <c r="J7" s="8" t="inlineStr"/>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" s="8" t="inlineStr"/>
       <c r="J9" s="8" t="inlineStr"/>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr"/>
       <c r="H10" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>5</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I11" s="8" t="inlineStr"/>
       <c r="J11" s="8" t="inlineStr"/>
@@ -7682,7 +7682,7 @@
         <v>4</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12" s="8" t="inlineStr"/>
       <c r="J12" s="8" t="inlineStr"/>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr"/>
       <c r="H14" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14" s="8" t="inlineStr"/>
       <c r="J14" s="8" t="inlineStr"/>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr"/>
       <c r="H15" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15" s="8" t="inlineStr"/>
       <c r="J15" s="8" t="inlineStr">
@@ -7842,7 +7842,7 @@
         <v>5</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16" s="8" t="inlineStr"/>
       <c r="J16" s="8" t="inlineStr"/>
@@ -7882,7 +7882,7 @@
         <v>4</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I17" s="8" t="inlineStr"/>
       <c r="J17" s="8" t="inlineStr"/>
@@ -8082,7 +8082,7 @@
         <v>4</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I22" s="8" t="inlineStr"/>
       <c r="J22" s="8" t="inlineStr"/>
@@ -8160,7 +8160,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr"/>
       <c r="H24" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" s="8" t="inlineStr"/>
       <c r="J24" s="8" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr"/>
       <c r="H25" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25" s="8" t="inlineStr"/>
       <c r="J25" s="8" t="inlineStr">
@@ -8242,7 +8242,7 @@
         <v>5</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" s="8" t="inlineStr"/>
       <c r="J26" s="8" t="inlineStr"/>
@@ -8282,7 +8282,7 @@
         <v>4</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27" s="8" t="inlineStr"/>
       <c r="J27" s="8" t="inlineStr"/>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr"/>
       <c r="H29" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I29" s="8" t="inlineStr"/>
       <c r="J29" s="8" t="inlineStr"/>
@@ -8398,7 +8398,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr"/>
       <c r="H30" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I30" s="8" t="inlineStr"/>
       <c r="J30" s="8" t="inlineStr">
@@ -8442,7 +8442,7 @@
         <v>5</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I31" s="8" t="inlineStr"/>
       <c r="J31" s="8" t="inlineStr"/>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="G32" s="8" t="inlineStr"/>
       <c r="H32" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I32" s="8" t="inlineStr"/>
       <c r="J32" s="8" t="inlineStr"/>
@@ -8520,7 +8520,7 @@
         <v>4</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I33" s="8" t="inlineStr"/>
       <c r="J33" s="8" t="inlineStr"/>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr"/>
       <c r="H35" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35" s="8" t="inlineStr"/>
       <c r="J35" s="8" t="inlineStr"/>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr"/>
       <c r="H36" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I36" s="8" t="inlineStr"/>
       <c r="J36" s="8" t="inlineStr">
@@ -8680,7 +8680,7 @@
         <v>5</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I37" s="8" t="inlineStr"/>
       <c r="J37" s="8" t="inlineStr"/>
@@ -8720,7 +8720,7 @@
         <v>4</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I38" s="8" t="inlineStr"/>
       <c r="J38" s="8" t="inlineStr"/>
@@ -8920,7 +8920,7 @@
         <v>4</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I43" s="8" t="inlineStr"/>
       <c r="J43" s="8" t="inlineStr"/>
@@ -9120,7 +9120,7 @@
         <v>4</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I48" s="8" t="inlineStr"/>
       <c r="J48" s="8" t="inlineStr"/>
@@ -9200,7 +9200,7 @@
         <v>5</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" s="8" t="inlineStr"/>
       <c r="J50" s="8" t="inlineStr"/>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr"/>
       <c r="H51" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I51" s="8" t="inlineStr"/>
       <c r="J51" s="8" t="inlineStr"/>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr"/>
       <c r="H52" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I52" s="8" t="inlineStr"/>
       <c r="J52" s="8" t="inlineStr">
@@ -9320,7 +9320,7 @@
         <v>4</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I53" s="8" t="inlineStr"/>
       <c r="J53" s="8" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="G55" s="10" t="inlineStr"/>
       <c r="H55" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" s="10" t="inlineStr"/>
       <c r="J55" s="10" t="inlineStr"/>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="G56" s="10" t="inlineStr"/>
       <c r="H56" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I56" s="10" t="inlineStr"/>
       <c r="J56" s="10" t="inlineStr">
@@ -9480,7 +9480,7 @@
         <v>6</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I57" s="10" t="inlineStr"/>
       <c r="J57" s="10" t="inlineStr"/>
@@ -9520,7 +9520,7 @@
         <v>4</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I58" s="10" t="inlineStr"/>
       <c r="J58" s="10" t="inlineStr"/>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="G60" s="10" t="inlineStr"/>
       <c r="H60" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I60" s="10" t="inlineStr"/>
       <c r="J60" s="10" t="inlineStr"/>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G61" s="10" t="inlineStr"/>
       <c r="H61" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I61" s="10" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>6</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I62" s="10" t="inlineStr"/>
       <c r="J62" s="10" t="inlineStr"/>
@@ -9724,7 +9724,7 @@
         <v>4</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I63" s="10" t="inlineStr"/>
       <c r="J63" s="10" t="inlineStr"/>
@@ -9802,7 +9802,7 @@
       </c>
       <c r="G65" s="10" t="inlineStr"/>
       <c r="H65" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I65" s="10" t="inlineStr"/>
       <c r="J65" s="10" t="inlineStr"/>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="G66" s="10" t="inlineStr"/>
       <c r="H66" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>6</v>
       </c>
       <c r="H67" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I67" s="10" t="inlineStr"/>
       <c r="J67" s="10" t="inlineStr"/>
@@ -9928,7 +9928,7 @@
         <v>4</v>
       </c>
       <c r="H68" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I68" s="10" t="inlineStr"/>
       <c r="J68" s="10" t="inlineStr"/>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="G70" s="16" t="inlineStr"/>
       <c r="H70" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I70" s="16" t="inlineStr"/>
       <c r="J70" s="16" t="inlineStr"/>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="G71" s="16" t="inlineStr"/>
       <c r="H71" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         <v>6</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I72" s="16" t="inlineStr"/>
       <c r="J72" s="16" t="inlineStr"/>
@@ -10246,7 +10246,7 @@
         <v>4</v>
       </c>
       <c r="H76" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I76" s="16" t="inlineStr"/>
       <c r="J76" s="16" t="inlineStr"/>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="G78" s="16" t="inlineStr"/>
       <c r="H78" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I78" s="16" t="inlineStr"/>
       <c r="J78" s="16" t="inlineStr"/>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="G79" s="16" t="inlineStr"/>
       <c r="H79" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I79" s="16" t="inlineStr"/>
       <c r="J79" s="16" t="inlineStr">
@@ -10406,7 +10406,7 @@
         <v>6</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I80" s="16" t="inlineStr"/>
       <c r="J80" s="16" t="inlineStr"/>
@@ -10484,7 +10484,7 @@
         <v>4</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I82" s="16" t="inlineStr"/>
       <c r="J82" s="16" t="inlineStr"/>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="G84" s="16" t="inlineStr"/>
       <c r="H84" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I84" s="16" t="inlineStr"/>
       <c r="J84" s="16" t="inlineStr"/>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="G85" s="16" t="inlineStr"/>
       <c r="H85" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>6</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I86" s="16" t="inlineStr"/>
       <c r="J86" s="16" t="inlineStr"/>
@@ -10726,7 +10726,7 @@
         <v>4</v>
       </c>
       <c r="H88" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I88" s="16" t="inlineStr"/>
       <c r="J88" s="16" t="inlineStr"/>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="G90" s="8" t="inlineStr"/>
       <c r="H90" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I90" s="8" t="inlineStr"/>
       <c r="J90" s="8" t="inlineStr"/>
@@ -10842,7 +10842,7 @@
       </c>
       <c r="G91" s="8" t="inlineStr"/>
       <c r="H91" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I91" s="8" t="inlineStr"/>
       <c r="J91" s="8" t="inlineStr">
@@ -10886,7 +10886,7 @@
         <v>5</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I92" s="8" t="inlineStr"/>
       <c r="J92" s="8" t="inlineStr"/>
@@ -10926,7 +10926,7 @@
         <v>4</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I93" s="8" t="inlineStr"/>
       <c r="J93" s="8" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
         <v>4</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I98" s="8" t="inlineStr"/>
       <c r="J98" s="8" t="inlineStr"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="G100" s="8" t="inlineStr"/>
       <c r="H100" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I100" s="8" t="inlineStr"/>
       <c r="J100" s="8" t="inlineStr"/>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="G101" s="8" t="inlineStr"/>
       <c r="H101" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I101" s="8" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>5</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I102" s="8" t="inlineStr"/>
       <c r="J102" s="8" t="inlineStr"/>
@@ -11330,7 +11330,7 @@
         <v>4</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I103" s="8" t="inlineStr"/>
       <c r="J103" s="8" t="inlineStr"/>
@@ -11534,7 +11534,7 @@
         <v>4</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I108" s="8" t="inlineStr"/>
       <c r="J108" s="8" t="inlineStr"/>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr"/>
       <c r="H110" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I110" s="8" t="inlineStr"/>
       <c r="J110" s="8" t="inlineStr"/>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="G111" s="8" t="inlineStr"/>
       <c r="H111" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I111" s="8" t="inlineStr"/>
       <c r="J111" s="8" t="inlineStr">
@@ -11694,7 +11694,7 @@
         <v>5</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I112" s="8" t="inlineStr"/>
       <c r="J112" s="8" t="inlineStr"/>
@@ -11734,7 +11734,7 @@
         <v>4</v>
       </c>
       <c r="H113" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I113" s="8" t="inlineStr"/>
       <c r="J113" s="8" t="inlineStr"/>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr"/>
       <c r="H115" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I115" s="8" t="inlineStr"/>
       <c r="J115" s="8" t="inlineStr"/>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr"/>
       <c r="H116" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I116" s="8" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>5</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I117" s="8" t="inlineStr"/>
       <c r="J117" s="8" t="inlineStr"/>
@@ -11938,7 +11938,7 @@
         <v>4</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I118" s="8" t="inlineStr"/>
       <c r="J118" s="8" t="inlineStr"/>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="G120" s="10" t="inlineStr"/>
       <c r="H120" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I120" s="10" t="inlineStr"/>
       <c r="J120" s="10" t="inlineStr"/>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="G121" s="10" t="inlineStr"/>
       <c r="H121" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I121" s="10" t="inlineStr"/>
       <c r="J121" s="10" t="inlineStr">
@@ -12098,7 +12098,7 @@
         <v>6</v>
       </c>
       <c r="H122" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I122" s="10" t="inlineStr"/>
       <c r="J122" s="10" t="inlineStr"/>
@@ -12138,7 +12138,7 @@
         <v>4</v>
       </c>
       <c r="H123" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I123" s="10" t="inlineStr"/>
       <c r="J123" s="10" t="inlineStr"/>
@@ -12216,7 +12216,7 @@
       </c>
       <c r="G125" s="10" t="inlineStr"/>
       <c r="H125" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I125" s="10" t="inlineStr"/>
       <c r="J125" s="10" t="inlineStr"/>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="G126" s="10" t="inlineStr"/>
       <c r="H126" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I126" s="10" t="inlineStr"/>
       <c r="J126" s="10" t="inlineStr">
@@ -12298,7 +12298,7 @@
         <v>6</v>
       </c>
       <c r="H127" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I127" s="10" t="inlineStr"/>
       <c r="J127" s="10" t="inlineStr"/>
@@ -12338,7 +12338,7 @@
         <v>4</v>
       </c>
       <c r="H128" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I128" s="10" t="inlineStr"/>
       <c r="J128" s="10" t="inlineStr"/>
@@ -12416,7 +12416,7 @@
       </c>
       <c r="G130" s="10" t="inlineStr"/>
       <c r="H130" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I130" s="10" t="inlineStr"/>
       <c r="J130" s="10" t="inlineStr"/>
@@ -12454,7 +12454,7 @@
       </c>
       <c r="G131" s="10" t="inlineStr"/>
       <c r="H131" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I131" s="10" t="inlineStr"/>
       <c r="J131" s="10" t="inlineStr">
@@ -12498,7 +12498,7 @@
         <v>6</v>
       </c>
       <c r="H132" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I132" s="10" t="inlineStr"/>
       <c r="J132" s="10" t="inlineStr"/>
@@ -12538,7 +12538,7 @@
         <v>4</v>
       </c>
       <c r="H133" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I133" s="10" t="inlineStr"/>
       <c r="J133" s="10" t="inlineStr"/>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="G135" s="16" t="inlineStr"/>
       <c r="H135" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I135" s="16" t="inlineStr"/>
       <c r="J135" s="16" t="inlineStr"/>
@@ -12654,7 +12654,7 @@
       </c>
       <c r="G136" s="16" t="inlineStr"/>
       <c r="H136" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I136" s="16" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>6</v>
       </c>
       <c r="H137" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I137" s="16" t="inlineStr"/>
       <c r="J137" s="16" t="inlineStr"/>
@@ -12780,7 +12780,7 @@
         <v>4</v>
       </c>
       <c r="H139" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I139" s="16" t="inlineStr"/>
       <c r="J139" s="16" t="inlineStr"/>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="G141" s="16" t="inlineStr"/>
       <c r="H141" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I141" s="16" t="inlineStr"/>
       <c r="J141" s="16" t="inlineStr"/>
@@ -12896,7 +12896,7 @@
       </c>
       <c r="G142" s="16" t="inlineStr"/>
       <c r="H142" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I142" s="16" t="inlineStr"/>
       <c r="J142" s="16" t="inlineStr">
@@ -12940,7 +12940,7 @@
         <v>6</v>
       </c>
       <c r="H143" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I143" s="16" t="inlineStr"/>
       <c r="J143" s="16" t="inlineStr"/>
@@ -13018,7 +13018,7 @@
         <v>4</v>
       </c>
       <c r="H145" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I145" s="16" t="inlineStr"/>
       <c r="J145" s="16" t="inlineStr"/>
@@ -13096,7 +13096,7 @@
       </c>
       <c r="G147" s="16" t="inlineStr"/>
       <c r="H147" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I147" s="16" t="inlineStr"/>
       <c r="J147" s="16" t="inlineStr"/>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="G148" s="16" t="inlineStr"/>
       <c r="H148" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I148" s="16" t="inlineStr"/>
       <c r="J148" s="16" t="inlineStr">
@@ -13178,7 +13178,7 @@
         <v>6</v>
       </c>
       <c r="H149" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I149" s="16" t="inlineStr"/>
       <c r="J149" s="16" t="inlineStr"/>
@@ -13256,7 +13256,7 @@
         <v>4</v>
       </c>
       <c r="H151" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I151" s="16" t="inlineStr"/>
       <c r="J151" s="16" t="inlineStr"/>
@@ -13456,7 +13456,7 @@
         <v>4</v>
       </c>
       <c r="H156" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I156" s="8" t="inlineStr"/>
       <c r="J156" s="8" t="inlineStr"/>
@@ -13534,7 +13534,7 @@
       </c>
       <c r="G158" s="8" t="inlineStr"/>
       <c r="H158" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I158" s="8" t="inlineStr"/>
       <c r="J158" s="8" t="inlineStr">
@@ -13578,7 +13578,7 @@
         <v>5</v>
       </c>
       <c r="H159" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I159" s="8" t="inlineStr"/>
       <c r="J159" s="8" t="inlineStr"/>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G160" s="8" t="inlineStr"/>
       <c r="H160" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I160" s="8" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>4</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I161" s="8" t="inlineStr"/>
       <c r="J161" s="8" t="inlineStr"/>
@@ -13860,7 +13860,7 @@
         <v>4</v>
       </c>
       <c r="H166" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I166" s="8" t="inlineStr"/>
       <c r="J166" s="8" t="inlineStr"/>
@@ -13938,7 +13938,7 @@
       </c>
       <c r="G168" s="8" t="inlineStr"/>
       <c r="H168" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I168" s="8" t="inlineStr"/>
       <c r="J168" s="8" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="G169" s="8" t="inlineStr"/>
       <c r="H169" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I169" s="8" t="inlineStr"/>
       <c r="J169" s="8" t="inlineStr">
@@ -14024,7 +14024,7 @@
         <v>5</v>
       </c>
       <c r="H170" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I170" s="8" t="inlineStr"/>
       <c r="J170" s="8" t="inlineStr"/>
@@ -14064,7 +14064,7 @@
         <v>4</v>
       </c>
       <c r="H171" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I171" s="8" t="inlineStr"/>
       <c r="J171" s="8" t="inlineStr"/>
@@ -14268,7 +14268,7 @@
         <v>4</v>
       </c>
       <c r="H176" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I176" s="8" t="inlineStr"/>
       <c r="J176" s="8" t="inlineStr"/>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="G178" s="8" t="inlineStr"/>
       <c r="H178" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I178" s="8" t="inlineStr"/>
       <c r="J178" s="8" t="inlineStr"/>
@@ -14384,7 +14384,7 @@
       </c>
       <c r="G179" s="8" t="inlineStr"/>
       <c r="H179" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I179" s="8" t="inlineStr"/>
       <c r="J179" s="8" t="inlineStr">
@@ -14428,7 +14428,7 @@
         <v>5</v>
       </c>
       <c r="H180" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I180" s="8" t="inlineStr"/>
       <c r="J180" s="8" t="inlineStr"/>
@@ -14468,7 +14468,7 @@
         <v>4</v>
       </c>
       <c r="H181" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I181" s="8" t="inlineStr"/>
       <c r="J181" s="8" t="inlineStr"/>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="G183" s="10" t="inlineStr"/>
       <c r="H183" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I183" s="10" t="inlineStr"/>
       <c r="J183" s="10" t="inlineStr"/>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="G184" s="10" t="inlineStr"/>
       <c r="H184" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I184" s="10" t="inlineStr"/>
       <c r="J184" s="10" t="inlineStr"/>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="G185" s="10" t="inlineStr"/>
       <c r="H185" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I185" s="10" t="inlineStr"/>
       <c r="J185" s="10" t="inlineStr">
@@ -14666,7 +14666,7 @@
         <v>6</v>
       </c>
       <c r="H186" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I186" s="10" t="inlineStr"/>
       <c r="J186" s="10" t="inlineStr"/>
@@ -14706,7 +14706,7 @@
         <v>4</v>
       </c>
       <c r="H187" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I187" s="10" t="inlineStr"/>
       <c r="J187" s="10" t="inlineStr"/>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="G189" s="10" t="inlineStr"/>
       <c r="H189" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I189" s="10" t="inlineStr"/>
       <c r="J189" s="10" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="G190" s="10" t="inlineStr"/>
       <c r="H190" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I190" s="10" t="inlineStr"/>
       <c r="J190" s="10" t="inlineStr"/>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="G191" s="10" t="inlineStr"/>
       <c r="H191" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I191" s="10" t="inlineStr"/>
       <c r="J191" s="10" t="inlineStr">
@@ -14904,7 +14904,7 @@
         <v>6</v>
       </c>
       <c r="H192" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I192" s="10" t="inlineStr"/>
       <c r="J192" s="10" t="inlineStr"/>
@@ -14944,7 +14944,7 @@
         <v>4</v>
       </c>
       <c r="H193" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I193" s="10" t="inlineStr"/>
       <c r="J193" s="10" t="inlineStr"/>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="G195" s="10" t="inlineStr"/>
       <c r="H195" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I195" s="10" t="inlineStr"/>
       <c r="J195" s="10" t="inlineStr"/>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="G196" s="10" t="inlineStr"/>
       <c r="H196" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I196" s="10" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>6</v>
       </c>
       <c r="H197" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I197" s="10" t="inlineStr"/>
       <c r="J197" s="10" t="inlineStr"/>
@@ -15148,7 +15148,7 @@
         <v>4</v>
       </c>
       <c r="H198" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I198" s="10" t="inlineStr"/>
       <c r="J198" s="10" t="inlineStr"/>
@@ -15226,7 +15226,7 @@
       </c>
       <c r="G200" s="16" t="inlineStr"/>
       <c r="H200" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I200" s="16" t="inlineStr"/>
       <c r="J200" s="16" t="inlineStr"/>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="G201" s="16" t="inlineStr"/>
       <c r="H201" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I201" s="16" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>6</v>
       </c>
       <c r="H202" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I202" s="16" t="inlineStr"/>
       <c r="J202" s="16" t="inlineStr"/>
@@ -15390,7 +15390,7 @@
         <v>4</v>
       </c>
       <c r="H204" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I204" s="16" t="inlineStr"/>
       <c r="J204" s="16" t="inlineStr"/>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="G206" s="16" t="inlineStr"/>
       <c r="H206" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I206" s="16" t="inlineStr"/>
       <c r="J206" s="16" t="inlineStr"/>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="G207" s="16" t="inlineStr"/>
       <c r="H207" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I207" s="16" t="inlineStr"/>
       <c r="J207" s="16" t="inlineStr">
@@ -15588,7 +15588,7 @@
         <v>6</v>
       </c>
       <c r="H209" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I209" s="16" t="inlineStr"/>
       <c r="J209" s="16" t="inlineStr"/>
@@ -15628,7 +15628,7 @@
         <v>4</v>
       </c>
       <c r="H210" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I210" s="16" t="inlineStr"/>
       <c r="J210" s="16" t="inlineStr"/>
@@ -15706,7 +15706,7 @@
       </c>
       <c r="G212" s="16" t="inlineStr"/>
       <c r="H212" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I212" s="16" t="inlineStr"/>
       <c r="J212" s="16" t="inlineStr"/>
@@ -15744,7 +15744,7 @@
       </c>
       <c r="G213" s="16" t="inlineStr"/>
       <c r="H213" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I213" s="16" t="inlineStr"/>
       <c r="J213" s="16" t="inlineStr">
@@ -15830,7 +15830,7 @@
         <v>6</v>
       </c>
       <c r="H215" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I215" s="16" t="inlineStr"/>
       <c r="J215" s="16" t="inlineStr"/>
@@ -15870,7 +15870,7 @@
         <v>4</v>
       </c>
       <c r="H216" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I216" s="16" t="inlineStr"/>
       <c r="J216" s="16" t="inlineStr"/>
@@ -15948,7 +15948,7 @@
       </c>
       <c r="G218" s="16" t="inlineStr"/>
       <c r="H218" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I218" s="16" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
       </c>
       <c r="G219" s="16" t="inlineStr"/>
       <c r="H219" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I219" s="16" t="inlineStr"/>
       <c r="J219" s="16" t="inlineStr"/>
@@ -16028,7 +16028,7 @@
       </c>
       <c r="G220" s="16" t="inlineStr"/>
       <c r="H220" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I220" s="16" t="inlineStr"/>
       <c r="J220" s="16" t="inlineStr">
@@ -16072,7 +16072,7 @@
         <v>6</v>
       </c>
       <c r="H221" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I221" s="16" t="inlineStr"/>
       <c r="J221" s="16" t="inlineStr"/>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="G223" s="8" t="inlineStr"/>
       <c r="H223" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I223" s="8" t="inlineStr"/>
       <c r="J223" s="8" t="inlineStr">
@@ -16194,7 +16194,7 @@
         <v>5</v>
       </c>
       <c r="H224" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I224" s="8" t="inlineStr"/>
       <c r="J224" s="8" t="inlineStr"/>
@@ -16232,7 +16232,7 @@
       </c>
       <c r="G225" s="8" t="inlineStr"/>
       <c r="H225" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I225" s="8" t="inlineStr"/>
       <c r="J225" s="8" t="inlineStr"/>
@@ -16272,7 +16272,7 @@
         <v>4</v>
       </c>
       <c r="H226" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I226" s="8" t="inlineStr"/>
       <c r="J226" s="8" t="inlineStr"/>
@@ -16476,7 +16476,7 @@
         <v>4</v>
       </c>
       <c r="H231" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I231" s="8" t="inlineStr"/>
       <c r="J231" s="8" t="inlineStr"/>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="G233" s="8" t="inlineStr"/>
       <c r="H233" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I233" s="8" t="inlineStr"/>
       <c r="J233" s="8" t="inlineStr"/>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="G234" s="8" t="inlineStr"/>
       <c r="H234" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I234" s="8" t="inlineStr"/>
       <c r="J234" s="8" t="inlineStr">
@@ -16636,7 +16636,7 @@
         <v>5</v>
       </c>
       <c r="H235" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I235" s="8" t="inlineStr"/>
       <c r="J235" s="8" t="inlineStr"/>
@@ -16676,7 +16676,7 @@
         <v>4</v>
       </c>
       <c r="H236" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I236" s="8" t="inlineStr"/>
       <c r="J236" s="8" t="inlineStr"/>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
@@ -699,7 +699,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>최대 HP의 50%</t>
+          <t>최대 HP의 30%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>급강하 (5턴부터)</t>
+          <t>깃털을 곤두세운다 (5턴부터)</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>어지러운 날갯짓 → 급강하 (50%)</t>
+          <t>어지러운 날갯짓 → 급강하 (100%)</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr"/>
       <c r="H4" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
@@ -7384,19 +7384,17 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>피해 8</t>
+          <t>피해 15</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>5</v>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
@@ -7424,12 +7422,12 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>피해 4 · 혼란 1</t>
+          <t>혼란 2</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr"/>
@@ -7439,7 +7437,7 @@
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>급강하 50%</t>
+          <t>급강하 100%</t>
         </is>
       </c>
     </row>
@@ -7471,14 +7469,14 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>99</t>
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I7" s="8" t="inlineStr"/>
       <c r="J7" s="8" t="inlineStr"/>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -4584,22 +4584,22 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>깃털을 곤두세운다</t>
+          <t>마구 쪼기</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>피해 5</t>
         </is>
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>깃털을 곤두세운다 (5턴부터)</t>
+          <t>날개쉬기 (2턴부터)</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>어지러운 날갯짓 → 급강하 (100%)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr">
@@ -7379,22 +7379,24 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>급강하</t>
+          <t>날개쉬기</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>피해 15</t>
+          <t>힘 2</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="H5" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
@@ -7417,7 +7419,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>어지러운 날갯짓</t>
+          <t>흉내내기</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -7432,14 +7434,10 @@
       </c>
       <c r="G6" s="8" t="inlineStr"/>
       <c r="H6" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>급강하 100%</t>
-        </is>
-      </c>
+      <c r="J6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -7459,12 +7457,12 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>깃털을 곤두세운다</t>
+          <t>마구 쪼기</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>피해 5</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -4459,8 +4459,8 @@
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
@@ -4523,12 +4523,12 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>강화 행동</t>
+          <t>기본 행동</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>강화 효과</t>
+          <t>유니크 행동</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -4584,12 +4584,12 @@
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>마구 쪼기</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>피해 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K4" s="8" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>심지를 태운다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>다리를 곧추세운다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>송곳니를 드러낸다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>가시를 세운다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>옹이가 굵어진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>물살이 거세진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>몸을 부풀린다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>무리가 불어난다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>빗자루가 뻣뻣해진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>무리를 부른다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>힘 6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K14" s="10" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>지느러미를 곧추세운다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>힘 6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K15" s="10" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>어둠을 삼킨다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>힘 6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K16" s="10" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
-          <t>털이 곤두선다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>힘 7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K17" s="16" t="inlineStr">
@@ -5438,12 +5438,12 @@
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
-          <t>바위를 움켜쥔다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>힘 7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K18" s="16" t="inlineStr">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
-          <t>솜이 팽팽해진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>힘 7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K19" s="16" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>목이 부푼다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>날갯소리가 높아진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>안개가 짙어진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
@@ -5743,12 +5743,12 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>뿔이 자란다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>뼈를 맞춘다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>마디가 굵어진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>진흙을 더 끌어모은다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
         <is>
-          <t>힘 6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K26" s="10" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>창을 고쳐 쥔다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
         <is>
-          <t>힘 6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K27" s="10" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="I28" s="10" t="inlineStr">
         <is>
-          <t>삽자루를 고쳐 쥔다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
         <is>
-          <t>힘 6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K28" s="10" t="inlineStr">
@@ -6109,12 +6109,12 @@
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
-          <t>늪이 끓어오른다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>힘 7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K29" s="16" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="I30" s="16" t="inlineStr">
         <is>
-          <t>숨을 깊이 들이쉰다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>힘 7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K30" s="16" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
-          <t>흙을 밀어낸다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>힘 7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K31" s="16" t="inlineStr">
@@ -6292,12 +6292,12 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>귀를 세운다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>동공이 벌어진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
@@ -6414,12 +6414,12 @@
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>비늘가루를 모은다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
-          <t>속삭임이 커진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>기도를 삼킨다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="I37" s="8" t="inlineStr">
         <is>
-          <t>금이 갈라진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>모래를 끌어모은다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J38" s="10" t="inlineStr">
         <is>
-          <t>힘 6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K38" s="10" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>촉수가 굵어진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J39" s="10" t="inlineStr">
         <is>
-          <t>힘 6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K39" s="10" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>줄을 힘껏 당긴다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J40" s="10" t="inlineStr">
         <is>
-          <t>힘 6</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K40" s="10" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="I41" s="16" t="inlineStr">
         <is>
-          <t>꿈을 고쳐 쓴다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>힘 7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K41" s="16" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
-          <t>아가리가 더 벌어진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>힘 7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K42" s="16" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="I43" s="16" t="inlineStr">
         <is>
-          <t>후광이 짙어진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>힘 7</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K43" s="16" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>설교가 빨라진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>음이 높아진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>심지가 길어진다</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
@@ -7242,7 +7242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J237"/>
+  <dimension ref="A1:L237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7253,8 +7253,10 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7309,15 +7311,25 @@
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
+          <t>락 턴</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
           <t>쿨다운</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>파쇄</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>연계</t>
         </is>
@@ -7355,11 +7367,13 @@
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -7395,11 +7409,13 @@
       <c r="G5" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -7433,11 +7449,13 @@
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="n">
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -7462,7 +7480,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>피해 5</t>
+          <t>피해 2 ×5타</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -7473,11 +7491,13 @@
       <c r="G7" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="J7" s="8" t="inlineStr"/>
+      <c r="K7" s="8" t="inlineStr"/>
+      <c r="L7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -7512,12 +7532,14 @@
       </c>
       <c r="G8" s="8" t="inlineStr"/>
       <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr"/>
+      <c r="J8" s="8" t="inlineStr"/>
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="L8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -7537,12 +7559,12 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>지지기</t>
+          <t>웅크리기</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>피해 5</t>
+          <t>방어 5</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -7551,11 +7573,13 @@
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="8" t="inlineStr"/>
+      <c r="L9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -7580,7 +7604,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>힘 2</t>
+          <t>휴식</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -7589,15 +7613,17 @@
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr"/>
+      <c r="I10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8" t="inlineStr"/>
+      <c r="K10" s="8" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="L10" s="8" t="inlineStr">
         <is>
           <t>불꽃 폭발 100%</t>
         </is>
@@ -7626,7 +7652,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>피해 10</t>
+          <t>피해 15</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
@@ -7637,11 +7663,13 @@
       <c r="G11" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="8" t="inlineStr"/>
       <c r="J11" s="8" t="inlineStr"/>
+      <c r="K11" s="8" t="inlineStr"/>
+      <c r="L11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -7677,11 +7705,13 @@
       <c r="G12" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="8" t="inlineStr"/>
+      <c r="I12" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I12" s="8" t="inlineStr"/>
       <c r="J12" s="8" t="inlineStr"/>
+      <c r="K12" s="8" t="inlineStr"/>
+      <c r="L12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -7716,12 +7746,14 @@
       </c>
       <c r="G13" s="8" t="inlineStr"/>
       <c r="H13" s="8" t="inlineStr"/>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr"/>
+      <c r="J13" s="8" t="inlineStr"/>
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr"/>
+      <c r="L13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -7755,11 +7787,13 @@
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr"/>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="8" t="inlineStr"/>
+      <c r="I14" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="8" t="inlineStr"/>
       <c r="J14" s="8" t="inlineStr"/>
+      <c r="K14" s="8" t="inlineStr"/>
+      <c r="L14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -7793,11 +7827,13 @@
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr"/>
-      <c r="H15" s="8" t="n">
+      <c r="H15" s="8" t="inlineStr"/>
+      <c r="I15" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="8" t="inlineStr"/>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr"/>
+      <c r="L15" s="8" t="inlineStr">
         <is>
           <t>기습 100%</t>
         </is>
@@ -7837,11 +7873,13 @@
       <c r="G16" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H16" s="8" t="n">
+      <c r="H16" s="8" t="inlineStr"/>
+      <c r="I16" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="8" t="inlineStr"/>
       <c r="J16" s="8" t="inlineStr"/>
+      <c r="K16" s="8" t="inlineStr"/>
+      <c r="L16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -7877,11 +7915,13 @@
       <c r="G17" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I17" s="8" t="inlineStr"/>
       <c r="J17" s="8" t="inlineStr"/>
+      <c r="K17" s="8" t="inlineStr"/>
+      <c r="L17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -7916,12 +7956,14 @@
       </c>
       <c r="G18" s="8" t="inlineStr"/>
       <c r="H18" s="8" t="inlineStr"/>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr"/>
+      <c r="J18" s="8" t="inlineStr"/>
+      <c r="K18" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr"/>
+      <c r="L18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -7955,11 +7997,13 @@
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr"/>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="8" t="inlineStr"/>
+      <c r="I19" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="8" t="inlineStr"/>
       <c r="J19" s="8" t="inlineStr"/>
+      <c r="K19" s="8" t="inlineStr"/>
+      <c r="L19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -7993,11 +8037,13 @@
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr"/>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="8" t="inlineStr"/>
+      <c r="I20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="8" t="inlineStr"/>
-      <c r="J20" s="8" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr"/>
+      <c r="K20" s="8" t="inlineStr"/>
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>사냥 50%</t>
         </is>
@@ -8037,11 +8083,13 @@
       <c r="G21" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="8" t="inlineStr"/>
       <c r="J21" s="8" t="inlineStr"/>
+      <c r="K21" s="8" t="inlineStr"/>
+      <c r="L21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -8077,11 +8125,13 @@
       <c r="G22" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="8" t="inlineStr"/>
       <c r="J22" s="8" t="inlineStr"/>
+      <c r="K22" s="8" t="inlineStr"/>
+      <c r="L22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -8116,12 +8166,14 @@
       </c>
       <c r="G23" s="8" t="inlineStr"/>
       <c r="H23" s="8" t="inlineStr"/>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr"/>
+      <c r="J23" s="8" t="inlineStr"/>
+      <c r="K23" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J23" s="8" t="inlineStr"/>
+      <c r="L23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -8155,11 +8207,13 @@
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr"/>
-      <c r="H24" s="8" t="n">
+      <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="8" t="inlineStr"/>
       <c r="J24" s="8" t="inlineStr"/>
+      <c r="K24" s="8" t="inlineStr"/>
+      <c r="L24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -8193,11 +8247,13 @@
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr"/>
-      <c r="H25" s="8" t="n">
+      <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="8" t="inlineStr"/>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr"/>
+      <c r="K25" s="8" t="inlineStr"/>
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t>덩굴 채찍 100%</t>
         </is>
@@ -8237,11 +8293,13 @@
       <c r="G26" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="8" t="inlineStr"/>
       <c r="J26" s="8" t="inlineStr"/>
+      <c r="K26" s="8" t="inlineStr"/>
+      <c r="L26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -8277,11 +8335,13 @@
       <c r="G27" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I27" s="8" t="inlineStr"/>
       <c r="J27" s="8" t="inlineStr"/>
+      <c r="K27" s="8" t="inlineStr"/>
+      <c r="L27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -8316,12 +8376,14 @@
       </c>
       <c r="G28" s="8" t="inlineStr"/>
       <c r="H28" s="8" t="inlineStr"/>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr"/>
+      <c r="J28" s="8" t="inlineStr"/>
+      <c r="K28" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J28" s="8" t="inlineStr"/>
+      <c r="L28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -8355,11 +8417,13 @@
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr"/>
-      <c r="H29" s="8" t="n">
+      <c r="H29" s="8" t="inlineStr"/>
+      <c r="I29" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I29" s="8" t="inlineStr"/>
       <c r="J29" s="8" t="inlineStr"/>
+      <c r="K29" s="8" t="inlineStr"/>
+      <c r="L29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -8393,11 +8457,13 @@
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr"/>
-      <c r="H30" s="8" t="n">
+      <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I30" s="8" t="inlineStr"/>
-      <c r="J30" s="8" t="inlineStr">
+      <c r="J30" s="8" t="inlineStr"/>
+      <c r="K30" s="8" t="inlineStr"/>
+      <c r="L30" s="8" t="inlineStr">
         <is>
           <t>짓뭉개기 100%</t>
         </is>
@@ -8437,11 +8503,13 @@
       <c r="G31" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="8" t="inlineStr"/>
+      <c r="I31" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I31" s="8" t="inlineStr"/>
       <c r="J31" s="8" t="inlineStr"/>
+      <c r="K31" s="8" t="inlineStr"/>
+      <c r="L31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -8475,11 +8543,13 @@
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr"/>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="8" t="inlineStr"/>
+      <c r="I32" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I32" s="8" t="inlineStr"/>
       <c r="J32" s="8" t="inlineStr"/>
+      <c r="K32" s="8" t="inlineStr"/>
+      <c r="L32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -8515,11 +8585,13 @@
       <c r="G33" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H33" s="8" t="n">
+      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I33" s="8" t="inlineStr"/>
       <c r="J33" s="8" t="inlineStr"/>
+      <c r="K33" s="8" t="inlineStr"/>
+      <c r="L33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -8554,12 +8626,14 @@
       </c>
       <c r="G34" s="8" t="inlineStr"/>
       <c r="H34" s="8" t="inlineStr"/>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr"/>
+      <c r="J34" s="8" t="inlineStr"/>
+      <c r="K34" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J34" s="8" t="inlineStr"/>
+      <c r="L34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -8593,11 +8667,13 @@
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr"/>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I35" s="8" t="inlineStr"/>
       <c r="J35" s="8" t="inlineStr"/>
+      <c r="K35" s="8" t="inlineStr"/>
+      <c r="L35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -8631,11 +8707,13 @@
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr"/>
-      <c r="H36" s="8" t="n">
+      <c r="H36" s="8" t="inlineStr"/>
+      <c r="I36" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I36" s="8" t="inlineStr"/>
-      <c r="J36" s="8" t="inlineStr">
+      <c r="J36" s="8" t="inlineStr"/>
+      <c r="K36" s="8" t="inlineStr"/>
+      <c r="L36" s="8" t="inlineStr">
         <is>
           <t>급류 100%</t>
         </is>
@@ -8675,11 +8753,13 @@
       <c r="G37" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H37" s="8" t="n">
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="8" t="inlineStr"/>
       <c r="J37" s="8" t="inlineStr"/>
+      <c r="K37" s="8" t="inlineStr"/>
+      <c r="L37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -8715,11 +8795,13 @@
       <c r="G38" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H38" s="8" t="n">
+      <c r="H38" s="8" t="inlineStr"/>
+      <c r="I38" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I38" s="8" t="inlineStr"/>
       <c r="J38" s="8" t="inlineStr"/>
+      <c r="K38" s="8" t="inlineStr"/>
+      <c r="L38" s="8" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
@@ -8754,12 +8836,14 @@
       </c>
       <c r="G39" s="8" t="inlineStr"/>
       <c r="H39" s="8" t="inlineStr"/>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr"/>
+      <c r="J39" s="8" t="inlineStr"/>
+      <c r="K39" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J39" s="8" t="inlineStr"/>
+      <c r="L39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -8793,11 +8877,13 @@
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr"/>
-      <c r="H40" s="8" t="n">
+      <c r="H40" s="8" t="inlineStr"/>
+      <c r="I40" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I40" s="8" t="inlineStr"/>
       <c r="J40" s="8" t="inlineStr"/>
+      <c r="K40" s="8" t="inlineStr"/>
+      <c r="L40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
@@ -8833,11 +8919,13 @@
       <c r="G41" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H41" s="8" t="n">
+      <c r="H41" s="8" t="inlineStr"/>
+      <c r="I41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="8" t="inlineStr"/>
-      <c r="J41" s="8" t="inlineStr">
+      <c r="J41" s="8" t="inlineStr"/>
+      <c r="K41" s="8" t="inlineStr"/>
+      <c r="L41" s="8" t="inlineStr">
         <is>
           <t>부풀기 50%</t>
         </is>
@@ -8875,11 +8963,13 @@
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr"/>
-      <c r="H42" s="8" t="n">
+      <c r="H42" s="8" t="inlineStr"/>
+      <c r="I42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I42" s="8" t="inlineStr"/>
       <c r="J42" s="8" t="inlineStr"/>
+      <c r="K42" s="8" t="inlineStr"/>
+      <c r="L42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
@@ -8915,11 +9005,13 @@
       <c r="G43" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="8" t="inlineStr"/>
+      <c r="I43" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I43" s="8" t="inlineStr"/>
       <c r="J43" s="8" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -8954,12 +9046,14 @@
       </c>
       <c r="G44" s="8" t="inlineStr"/>
       <c r="H44" s="8" t="inlineStr"/>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr"/>
+      <c r="J44" s="8" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J44" s="8" t="inlineStr"/>
+      <c r="L44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -8993,11 +9087,13 @@
         </is>
       </c>
       <c r="G45" s="8" t="inlineStr"/>
-      <c r="H45" s="8" t="n">
+      <c r="H45" s="8" t="inlineStr"/>
+      <c r="I45" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I45" s="8" t="inlineStr"/>
       <c r="J45" s="8" t="inlineStr"/>
+      <c r="K45" s="8" t="inlineStr"/>
+      <c r="L45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -9033,11 +9129,13 @@
       <c r="G46" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="8" t="inlineStr"/>
+      <c r="I46" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="8" t="inlineStr"/>
       <c r="J46" s="8" t="inlineStr"/>
+      <c r="K46" s="8" t="inlineStr"/>
+      <c r="L46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -9071,11 +9169,13 @@
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr"/>
-      <c r="H47" s="8" t="n">
+      <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="8" t="inlineStr"/>
-      <c r="J47" s="8" t="inlineStr">
+      <c r="J47" s="8" t="inlineStr"/>
+      <c r="K47" s="8" t="inlineStr"/>
+      <c r="L47" s="8" t="inlineStr">
         <is>
           <t>몰려들기 50%</t>
         </is>
@@ -9115,11 +9215,13 @@
       <c r="G48" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H48" s="8" t="n">
+      <c r="H48" s="8" t="inlineStr"/>
+      <c r="I48" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I48" s="8" t="inlineStr"/>
       <c r="J48" s="8" t="inlineStr"/>
+      <c r="K48" s="8" t="inlineStr"/>
+      <c r="L48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -9154,12 +9256,14 @@
       </c>
       <c r="G49" s="8" t="inlineStr"/>
       <c r="H49" s="8" t="inlineStr"/>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr"/>
+      <c r="J49" s="8" t="inlineStr"/>
+      <c r="K49" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J49" s="8" t="inlineStr"/>
+      <c r="L49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -9195,11 +9299,13 @@
       <c r="G50" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H50" s="8" t="n">
+      <c r="H50" s="8" t="inlineStr"/>
+      <c r="I50" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="8" t="inlineStr"/>
       <c r="J50" s="8" t="inlineStr"/>
+      <c r="K50" s="8" t="inlineStr"/>
+      <c r="L50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -9233,11 +9339,13 @@
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr"/>
-      <c r="H51" s="8" t="n">
+      <c r="H51" s="8" t="inlineStr"/>
+      <c r="I51" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I51" s="8" t="inlineStr"/>
       <c r="J51" s="8" t="inlineStr"/>
+      <c r="K51" s="8" t="inlineStr"/>
+      <c r="L51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -9271,11 +9379,13 @@
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr"/>
-      <c r="H52" s="8" t="n">
+      <c r="H52" s="8" t="inlineStr"/>
+      <c r="I52" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I52" s="8" t="inlineStr"/>
-      <c r="J52" s="8" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr"/>
+      <c r="K52" s="8" t="inlineStr"/>
+      <c r="L52" s="8" t="inlineStr">
         <is>
           <t>쓸어내기 100%</t>
         </is>
@@ -9315,11 +9425,13 @@
       <c r="G53" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H53" s="8" t="n">
+      <c r="H53" s="8" t="inlineStr"/>
+      <c r="I53" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I53" s="8" t="inlineStr"/>
       <c r="J53" s="8" t="inlineStr"/>
+      <c r="K53" s="8" t="inlineStr"/>
+      <c r="L53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -9354,12 +9466,14 @@
       </c>
       <c r="G54" s="8" t="inlineStr"/>
       <c r="H54" s="8" t="inlineStr"/>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr"/>
+      <c r="J54" s="8" t="inlineStr"/>
+      <c r="K54" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J54" s="8" t="inlineStr"/>
+      <c r="L54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
@@ -9393,11 +9507,13 @@
         </is>
       </c>
       <c r="G55" s="10" t="inlineStr"/>
-      <c r="H55" s="10" t="n">
+      <c r="H55" s="10" t="inlineStr"/>
+      <c r="I55" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I55" s="10" t="inlineStr"/>
       <c r="J55" s="10" t="inlineStr"/>
+      <c r="K55" s="10" t="inlineStr"/>
+      <c r="L55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -9431,11 +9547,13 @@
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr"/>
-      <c r="H56" s="10" t="n">
+      <c r="H56" s="10" t="inlineStr"/>
+      <c r="I56" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I56" s="10" t="inlineStr"/>
-      <c r="J56" s="10" t="inlineStr">
+      <c r="J56" s="10" t="inlineStr"/>
+      <c r="K56" s="10" t="inlineStr"/>
+      <c r="L56" s="10" t="inlineStr">
         <is>
           <t>광란 60%</t>
         </is>
@@ -9475,11 +9593,13 @@
       <c r="G57" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H57" s="10" t="n">
+      <c r="H57" s="10" t="inlineStr"/>
+      <c r="I57" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I57" s="10" t="inlineStr"/>
       <c r="J57" s="10" t="inlineStr"/>
+      <c r="K57" s="10" t="inlineStr"/>
+      <c r="L57" s="10" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -9515,11 +9635,13 @@
       <c r="G58" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H58" s="10" t="n">
+      <c r="H58" s="10" t="inlineStr"/>
+      <c r="I58" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I58" s="10" t="inlineStr"/>
       <c r="J58" s="10" t="inlineStr"/>
+      <c r="K58" s="10" t="inlineStr"/>
+      <c r="L58" s="10" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
@@ -9554,12 +9676,14 @@
       </c>
       <c r="G59" s="10" t="inlineStr"/>
       <c r="H59" s="10" t="inlineStr"/>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr"/>
+      <c r="J59" s="10" t="inlineStr"/>
+      <c r="K59" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J59" s="10" t="inlineStr"/>
+      <c r="L59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
@@ -9593,11 +9717,13 @@
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr"/>
-      <c r="H60" s="10" t="n">
+      <c r="H60" s="10" t="inlineStr"/>
+      <c r="I60" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I60" s="10" t="inlineStr"/>
       <c r="J60" s="10" t="inlineStr"/>
+      <c r="K60" s="10" t="inlineStr"/>
+      <c r="L60" s="10" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
@@ -9631,15 +9757,17 @@
         </is>
       </c>
       <c r="G61" s="10" t="inlineStr"/>
-      <c r="H61" s="10" t="n">
+      <c r="H61" s="10" t="inlineStr"/>
+      <c r="I61" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I61" s="10" t="inlineStr">
+      <c r="J61" s="10" t="inlineStr"/>
+      <c r="K61" s="10" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J61" s="10" t="inlineStr">
+      <c r="L61" s="10" t="inlineStr">
         <is>
           <t>요동 100%</t>
         </is>
@@ -9679,11 +9807,13 @@
       <c r="G62" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H62" s="10" t="n">
+      <c r="H62" s="10" t="inlineStr"/>
+      <c r="I62" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I62" s="10" t="inlineStr"/>
       <c r="J62" s="10" t="inlineStr"/>
+      <c r="K62" s="10" t="inlineStr"/>
+      <c r="L62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
@@ -9719,11 +9849,13 @@
       <c r="G63" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H63" s="10" t="n">
+      <c r="H63" s="10" t="inlineStr"/>
+      <c r="I63" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I63" s="10" t="inlineStr"/>
       <c r="J63" s="10" t="inlineStr"/>
+      <c r="K63" s="10" t="inlineStr"/>
+      <c r="L63" s="10" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -9758,12 +9890,14 @@
       </c>
       <c r="G64" s="10" t="inlineStr"/>
       <c r="H64" s="10" t="inlineStr"/>
-      <c r="I64" s="10" t="inlineStr">
+      <c r="I64" s="10" t="inlineStr"/>
+      <c r="J64" s="10" t="inlineStr"/>
+      <c r="K64" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J64" s="10" t="inlineStr"/>
+      <c r="L64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
@@ -9797,11 +9931,13 @@
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr"/>
-      <c r="H65" s="10" t="n">
+      <c r="H65" s="10" t="inlineStr"/>
+      <c r="I65" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I65" s="10" t="inlineStr"/>
       <c r="J65" s="10" t="inlineStr"/>
+      <c r="K65" s="10" t="inlineStr"/>
+      <c r="L65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
@@ -9835,15 +9971,17 @@
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr"/>
-      <c r="H66" s="10" t="n">
+      <c r="H66" s="10" t="inlineStr"/>
+      <c r="I66" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I66" s="10" t="inlineStr">
+      <c r="J66" s="10" t="inlineStr"/>
+      <c r="K66" s="10" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J66" s="10" t="inlineStr">
+      <c r="L66" s="10" t="inlineStr">
         <is>
           <t>덮침 100%</t>
         </is>
@@ -9883,11 +10021,13 @@
       <c r="G67" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H67" s="10" t="n">
+      <c r="H67" s="10" t="inlineStr"/>
+      <c r="I67" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I67" s="10" t="inlineStr"/>
       <c r="J67" s="10" t="inlineStr"/>
+      <c r="K67" s="10" t="inlineStr"/>
+      <c r="L67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
@@ -9923,11 +10063,13 @@
       <c r="G68" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H68" s="10" t="n">
+      <c r="H68" s="10" t="inlineStr"/>
+      <c r="I68" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I68" s="10" t="inlineStr"/>
       <c r="J68" s="10" t="inlineStr"/>
+      <c r="K68" s="10" t="inlineStr"/>
+      <c r="L68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
@@ -9962,12 +10104,14 @@
       </c>
       <c r="G69" s="10" t="inlineStr"/>
       <c r="H69" s="10" t="inlineStr"/>
-      <c r="I69" s="10" t="inlineStr">
+      <c r="I69" s="10" t="inlineStr"/>
+      <c r="J69" s="10" t="inlineStr"/>
+      <c r="K69" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J69" s="10" t="inlineStr"/>
+      <c r="L69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
@@ -10001,11 +10145,13 @@
         </is>
       </c>
       <c r="G70" s="16" t="inlineStr"/>
-      <c r="H70" s="16" t="n">
+      <c r="H70" s="16" t="inlineStr"/>
+      <c r="I70" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I70" s="16" t="inlineStr"/>
       <c r="J70" s="16" t="inlineStr"/>
+      <c r="K70" s="16" t="inlineStr"/>
+      <c r="L70" s="16" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
@@ -10039,15 +10185,17 @@
         </is>
       </c>
       <c r="G71" s="16" t="inlineStr"/>
-      <c r="H71" s="16" t="n">
+      <c r="H71" s="16" t="inlineStr"/>
+      <c r="I71" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I71" s="16" t="inlineStr">
+      <c r="J71" s="16" t="inlineStr"/>
+      <c r="K71" s="16" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J71" s="16" t="inlineStr">
+      <c r="L71" s="16" t="inlineStr">
         <is>
           <t>덮치기 100%</t>
         </is>
@@ -10087,11 +10235,13 @@
       <c r="G72" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="H72" s="16" t="n">
+      <c r="H72" s="16" t="inlineStr"/>
+      <c r="I72" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I72" s="16" t="inlineStr"/>
       <c r="J72" s="16" t="inlineStr"/>
+      <c r="K72" s="16" t="inlineStr"/>
+      <c r="L72" s="16" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
@@ -10125,11 +10275,13 @@
         </is>
       </c>
       <c r="G73" s="16" t="inlineStr"/>
-      <c r="H73" s="16" t="n">
+      <c r="H73" s="16" t="inlineStr"/>
+      <c r="I73" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I73" s="16" t="inlineStr"/>
       <c r="J73" s="16" t="inlineStr"/>
+      <c r="K73" s="16" t="inlineStr"/>
+      <c r="L73" s="16" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
@@ -10163,11 +10315,13 @@
         </is>
       </c>
       <c r="G74" s="16" t="inlineStr"/>
-      <c r="H74" s="16" t="n">
+      <c r="H74" s="16" t="inlineStr"/>
+      <c r="I74" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I74" s="16" t="inlineStr"/>
       <c r="J74" s="16" t="inlineStr"/>
+      <c r="K74" s="16" t="inlineStr"/>
+      <c r="L74" s="16" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
@@ -10201,11 +10355,13 @@
         </is>
       </c>
       <c r="G75" s="16" t="inlineStr"/>
-      <c r="H75" s="16" t="n">
+      <c r="H75" s="16" t="inlineStr"/>
+      <c r="I75" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I75" s="16" t="inlineStr"/>
       <c r="J75" s="16" t="inlineStr"/>
+      <c r="K75" s="16" t="inlineStr"/>
+      <c r="L75" s="16" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
@@ -10241,11 +10397,13 @@
       <c r="G76" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="H76" s="16" t="n">
+      <c r="H76" s="16" t="inlineStr"/>
+      <c r="I76" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I76" s="16" t="inlineStr"/>
       <c r="J76" s="16" t="inlineStr"/>
+      <c r="K76" s="16" t="inlineStr"/>
+      <c r="L76" s="16" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
@@ -10280,12 +10438,14 @@
       </c>
       <c r="G77" s="16" t="inlineStr"/>
       <c r="H77" s="16" t="inlineStr"/>
-      <c r="I77" s="16" t="inlineStr">
+      <c r="I77" s="16" t="inlineStr"/>
+      <c r="J77" s="16" t="inlineStr"/>
+      <c r="K77" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J77" s="16" t="inlineStr"/>
+      <c r="L77" s="16" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
@@ -10319,11 +10479,13 @@
         </is>
       </c>
       <c r="G78" s="16" t="inlineStr"/>
-      <c r="H78" s="16" t="n">
+      <c r="H78" s="16" t="inlineStr"/>
+      <c r="I78" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I78" s="16" t="inlineStr"/>
       <c r="J78" s="16" t="inlineStr"/>
+      <c r="K78" s="16" t="inlineStr"/>
+      <c r="L78" s="16" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
@@ -10357,11 +10519,13 @@
         </is>
       </c>
       <c r="G79" s="16" t="inlineStr"/>
-      <c r="H79" s="16" t="n">
+      <c r="H79" s="16" t="inlineStr"/>
+      <c r="I79" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I79" s="16" t="inlineStr"/>
-      <c r="J79" s="16" t="inlineStr">
+      <c r="J79" s="16" t="inlineStr"/>
+      <c r="K79" s="16" t="inlineStr"/>
+      <c r="L79" s="16" t="inlineStr">
         <is>
           <t>내려찍기 100%</t>
         </is>
@@ -10401,11 +10565,13 @@
       <c r="G80" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="H80" s="16" t="n">
+      <c r="H80" s="16" t="inlineStr"/>
+      <c r="I80" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I80" s="16" t="inlineStr"/>
       <c r="J80" s="16" t="inlineStr"/>
+      <c r="K80" s="16" t="inlineStr"/>
+      <c r="L80" s="16" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
@@ -10439,11 +10605,13 @@
         </is>
       </c>
       <c r="G81" s="16" t="inlineStr"/>
-      <c r="H81" s="16" t="n">
+      <c r="H81" s="16" t="inlineStr"/>
+      <c r="I81" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I81" s="16" t="inlineStr"/>
       <c r="J81" s="16" t="inlineStr"/>
+      <c r="K81" s="16" t="inlineStr"/>
+      <c r="L81" s="16" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
@@ -10479,11 +10647,13 @@
       <c r="G82" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="H82" s="16" t="n">
+      <c r="H82" s="16" t="inlineStr"/>
+      <c r="I82" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I82" s="16" t="inlineStr"/>
       <c r="J82" s="16" t="inlineStr"/>
+      <c r="K82" s="16" t="inlineStr"/>
+      <c r="L82" s="16" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
@@ -10518,12 +10688,14 @@
       </c>
       <c r="G83" s="16" t="inlineStr"/>
       <c r="H83" s="16" t="inlineStr"/>
-      <c r="I83" s="16" t="inlineStr">
+      <c r="I83" s="16" t="inlineStr"/>
+      <c r="J83" s="16" t="inlineStr"/>
+      <c r="K83" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J83" s="16" t="inlineStr"/>
+      <c r="L83" s="16" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
@@ -10557,11 +10729,13 @@
         </is>
       </c>
       <c r="G84" s="16" t="inlineStr"/>
-      <c r="H84" s="16" t="n">
+      <c r="H84" s="16" t="inlineStr"/>
+      <c r="I84" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I84" s="16" t="inlineStr"/>
       <c r="J84" s="16" t="inlineStr"/>
+      <c r="K84" s="16" t="inlineStr"/>
+      <c r="L84" s="16" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
@@ -10595,15 +10769,17 @@
         </is>
       </c>
       <c r="G85" s="16" t="inlineStr"/>
-      <c r="H85" s="16" t="n">
+      <c r="H85" s="16" t="inlineStr"/>
+      <c r="I85" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I85" s="16" t="inlineStr">
+      <c r="J85" s="16" t="inlineStr"/>
+      <c r="K85" s="16" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J85" s="16" t="inlineStr">
+      <c r="L85" s="16" t="inlineStr">
         <is>
           <t>솔기 뜯기 100%</t>
         </is>
@@ -10643,11 +10819,13 @@
       <c r="G86" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="H86" s="16" t="n">
+      <c r="H86" s="16" t="inlineStr"/>
+      <c r="I86" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I86" s="16" t="inlineStr"/>
       <c r="J86" s="16" t="inlineStr"/>
+      <c r="K86" s="16" t="inlineStr"/>
+      <c r="L86" s="16" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
@@ -10681,11 +10859,13 @@
         </is>
       </c>
       <c r="G87" s="16" t="inlineStr"/>
-      <c r="H87" s="16" t="n">
+      <c r="H87" s="16" t="inlineStr"/>
+      <c r="I87" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I87" s="16" t="inlineStr"/>
       <c r="J87" s="16" t="inlineStr"/>
+      <c r="K87" s="16" t="inlineStr"/>
+      <c r="L87" s="16" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
@@ -10721,11 +10901,13 @@
       <c r="G88" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="H88" s="16" t="n">
+      <c r="H88" s="16" t="inlineStr"/>
+      <c r="I88" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I88" s="16" t="inlineStr"/>
       <c r="J88" s="16" t="inlineStr"/>
+      <c r="K88" s="16" t="inlineStr"/>
+      <c r="L88" s="16" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
@@ -10760,12 +10942,14 @@
       </c>
       <c r="G89" s="16" t="inlineStr"/>
       <c r="H89" s="16" t="inlineStr"/>
-      <c r="I89" s="16" t="inlineStr">
+      <c r="I89" s="16" t="inlineStr"/>
+      <c r="J89" s="16" t="inlineStr"/>
+      <c r="K89" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J89" s="16" t="inlineStr"/>
+      <c r="L89" s="16" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
@@ -10799,11 +10983,13 @@
         </is>
       </c>
       <c r="G90" s="8" t="inlineStr"/>
-      <c r="H90" s="8" t="n">
+      <c r="H90" s="8" t="inlineStr"/>
+      <c r="I90" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I90" s="8" t="inlineStr"/>
       <c r="J90" s="8" t="inlineStr"/>
+      <c r="K90" s="8" t="inlineStr"/>
+      <c r="L90" s="8" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="8" t="inlineStr">
@@ -10837,11 +11023,13 @@
         </is>
       </c>
       <c r="G91" s="8" t="inlineStr"/>
-      <c r="H91" s="8" t="n">
+      <c r="H91" s="8" t="inlineStr"/>
+      <c r="I91" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I91" s="8" t="inlineStr"/>
-      <c r="J91" s="8" t="inlineStr">
+      <c r="J91" s="8" t="inlineStr"/>
+      <c r="K91" s="8" t="inlineStr"/>
+      <c r="L91" s="8" t="inlineStr">
         <is>
           <t>독침 뱉기 100%</t>
         </is>
@@ -10881,11 +11069,13 @@
       <c r="G92" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H92" s="8" t="n">
+      <c r="H92" s="8" t="inlineStr"/>
+      <c r="I92" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I92" s="8" t="inlineStr"/>
       <c r="J92" s="8" t="inlineStr"/>
+      <c r="K92" s="8" t="inlineStr"/>
+      <c r="L92" s="8" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="8" t="inlineStr">
@@ -10921,11 +11111,13 @@
       <c r="G93" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H93" s="8" t="n">
+      <c r="H93" s="8" t="inlineStr"/>
+      <c r="I93" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I93" s="8" t="inlineStr"/>
       <c r="J93" s="8" t="inlineStr"/>
+      <c r="K93" s="8" t="inlineStr"/>
+      <c r="L93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
@@ -10960,12 +11152,14 @@
       </c>
       <c r="G94" s="8" t="inlineStr"/>
       <c r="H94" s="8" t="inlineStr"/>
-      <c r="I94" s="8" t="inlineStr">
+      <c r="I94" s="8" t="inlineStr"/>
+      <c r="J94" s="8" t="inlineStr"/>
+      <c r="K94" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J94" s="8" t="inlineStr"/>
+      <c r="L94" s="8" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="inlineStr">
@@ -11001,11 +11195,13 @@
       <c r="G95" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H95" s="8" t="n">
+      <c r="H95" s="8" t="inlineStr"/>
+      <c r="I95" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I95" s="8" t="inlineStr"/>
       <c r="J95" s="8" t="inlineStr"/>
+      <c r="K95" s="8" t="inlineStr"/>
+      <c r="L95" s="8" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
@@ -11039,11 +11235,13 @@
         </is>
       </c>
       <c r="G96" s="8" t="inlineStr"/>
-      <c r="H96" s="8" t="n">
+      <c r="H96" s="8" t="inlineStr"/>
+      <c r="I96" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I96" s="8" t="inlineStr"/>
-      <c r="J96" s="8" t="inlineStr">
+      <c r="J96" s="8" t="inlineStr"/>
+      <c r="K96" s="8" t="inlineStr"/>
+      <c r="L96" s="8" t="inlineStr">
         <is>
           <t>흡혈 50%</t>
         </is>
@@ -11081,11 +11279,13 @@
         </is>
       </c>
       <c r="G97" s="8" t="inlineStr"/>
-      <c r="H97" s="8" t="n">
+      <c r="H97" s="8" t="inlineStr"/>
+      <c r="I97" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I97" s="8" t="inlineStr"/>
       <c r="J97" s="8" t="inlineStr"/>
+      <c r="K97" s="8" t="inlineStr"/>
+      <c r="L97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
@@ -11121,11 +11321,13 @@
       <c r="G98" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H98" s="8" t="n">
+      <c r="H98" s="8" t="inlineStr"/>
+      <c r="I98" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I98" s="8" t="inlineStr"/>
       <c r="J98" s="8" t="inlineStr"/>
+      <c r="K98" s="8" t="inlineStr"/>
+      <c r="L98" s="8" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="8" t="inlineStr">
@@ -11160,12 +11362,14 @@
       </c>
       <c r="G99" s="8" t="inlineStr"/>
       <c r="H99" s="8" t="inlineStr"/>
-      <c r="I99" s="8" t="inlineStr">
+      <c r="I99" s="8" t="inlineStr"/>
+      <c r="J99" s="8" t="inlineStr"/>
+      <c r="K99" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J99" s="8" t="inlineStr"/>
+      <c r="L99" s="8" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
@@ -11199,11 +11403,13 @@
         </is>
       </c>
       <c r="G100" s="8" t="inlineStr"/>
-      <c r="H100" s="8" t="n">
+      <c r="H100" s="8" t="inlineStr"/>
+      <c r="I100" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I100" s="8" t="inlineStr"/>
       <c r="J100" s="8" t="inlineStr"/>
+      <c r="K100" s="8" t="inlineStr"/>
+      <c r="L100" s="8" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
@@ -11237,15 +11443,17 @@
         </is>
       </c>
       <c r="G101" s="8" t="inlineStr"/>
-      <c r="H101" s="8" t="n">
+      <c r="H101" s="8" t="inlineStr"/>
+      <c r="I101" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I101" s="8" t="inlineStr">
+      <c r="J101" s="8" t="inlineStr"/>
+      <c r="K101" s="8" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J101" s="8" t="inlineStr">
+      <c r="L101" s="8" t="inlineStr">
         <is>
           <t>곡소리 100%</t>
         </is>
@@ -11285,11 +11493,13 @@
       <c r="G102" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H102" s="8" t="n">
+      <c r="H102" s="8" t="inlineStr"/>
+      <c r="I102" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I102" s="8" t="inlineStr"/>
       <c r="J102" s="8" t="inlineStr"/>
+      <c r="K102" s="8" t="inlineStr"/>
+      <c r="L102" s="8" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
@@ -11325,11 +11535,13 @@
       <c r="G103" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H103" s="8" t="n">
+      <c r="H103" s="8" t="inlineStr"/>
+      <c r="I103" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I103" s="8" t="inlineStr"/>
       <c r="J103" s="8" t="inlineStr"/>
+      <c r="K103" s="8" t="inlineStr"/>
+      <c r="L103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
@@ -11364,12 +11576,14 @@
       </c>
       <c r="G104" s="8" t="inlineStr"/>
       <c r="H104" s="8" t="inlineStr"/>
-      <c r="I104" s="8" t="inlineStr">
+      <c r="I104" s="8" t="inlineStr"/>
+      <c r="J104" s="8" t="inlineStr"/>
+      <c r="K104" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J104" s="8" t="inlineStr"/>
+      <c r="L104" s="8" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
@@ -11403,11 +11617,13 @@
         </is>
       </c>
       <c r="G105" s="8" t="inlineStr"/>
-      <c r="H105" s="8" t="n">
+      <c r="H105" s="8" t="inlineStr"/>
+      <c r="I105" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I105" s="8" t="inlineStr"/>
       <c r="J105" s="8" t="inlineStr"/>
+      <c r="K105" s="8" t="inlineStr"/>
+      <c r="L105" s="8" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
@@ -11441,15 +11657,17 @@
         </is>
       </c>
       <c r="G106" s="8" t="inlineStr"/>
-      <c r="H106" s="8" t="n">
+      <c r="H106" s="8" t="inlineStr"/>
+      <c r="I106" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I106" s="8" t="inlineStr">
+      <c r="J106" s="8" t="inlineStr"/>
+      <c r="K106" s="8" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J106" s="8" t="inlineStr">
+      <c r="L106" s="8" t="inlineStr">
         <is>
           <t>짓밟기 50%</t>
         </is>
@@ -11489,11 +11707,13 @@
       <c r="G107" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H107" s="8" t="n">
+      <c r="H107" s="8" t="inlineStr"/>
+      <c r="I107" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I107" s="8" t="inlineStr"/>
       <c r="J107" s="8" t="inlineStr"/>
+      <c r="K107" s="8" t="inlineStr"/>
+      <c r="L107" s="8" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
@@ -11529,11 +11749,13 @@
       <c r="G108" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H108" s="8" t="n">
+      <c r="H108" s="8" t="inlineStr"/>
+      <c r="I108" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I108" s="8" t="inlineStr"/>
       <c r="J108" s="8" t="inlineStr"/>
+      <c r="K108" s="8" t="inlineStr"/>
+      <c r="L108" s="8" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
@@ -11568,12 +11790,14 @@
       </c>
       <c r="G109" s="8" t="inlineStr"/>
       <c r="H109" s="8" t="inlineStr"/>
-      <c r="I109" s="8" t="inlineStr">
+      <c r="I109" s="8" t="inlineStr"/>
+      <c r="J109" s="8" t="inlineStr"/>
+      <c r="K109" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J109" s="8" t="inlineStr"/>
+      <c r="L109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
@@ -11607,11 +11831,13 @@
         </is>
       </c>
       <c r="G110" s="8" t="inlineStr"/>
-      <c r="H110" s="8" t="n">
+      <c r="H110" s="8" t="inlineStr"/>
+      <c r="I110" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I110" s="8" t="inlineStr"/>
       <c r="J110" s="8" t="inlineStr"/>
+      <c r="K110" s="8" t="inlineStr"/>
+      <c r="L110" s="8" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
@@ -11645,11 +11871,13 @@
         </is>
       </c>
       <c r="G111" s="8" t="inlineStr"/>
-      <c r="H111" s="8" t="n">
+      <c r="H111" s="8" t="inlineStr"/>
+      <c r="I111" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I111" s="8" t="inlineStr"/>
-      <c r="J111" s="8" t="inlineStr">
+      <c r="J111" s="8" t="inlineStr"/>
+      <c r="K111" s="8" t="inlineStr"/>
+      <c r="L111" s="8" t="inlineStr">
         <is>
           <t>뼈 던지기 100%</t>
         </is>
@@ -11689,11 +11917,13 @@
       <c r="G112" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H112" s="8" t="n">
+      <c r="H112" s="8" t="inlineStr"/>
+      <c r="I112" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I112" s="8" t="inlineStr"/>
       <c r="J112" s="8" t="inlineStr"/>
+      <c r="K112" s="8" t="inlineStr"/>
+      <c r="L112" s="8" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="8" t="inlineStr">
@@ -11729,11 +11959,13 @@
       <c r="G113" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H113" s="8" t="n">
+      <c r="H113" s="8" t="inlineStr"/>
+      <c r="I113" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I113" s="8" t="inlineStr"/>
       <c r="J113" s="8" t="inlineStr"/>
+      <c r="K113" s="8" t="inlineStr"/>
+      <c r="L113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
@@ -11768,12 +12000,14 @@
       </c>
       <c r="G114" s="8" t="inlineStr"/>
       <c r="H114" s="8" t="inlineStr"/>
-      <c r="I114" s="8" t="inlineStr">
+      <c r="I114" s="8" t="inlineStr"/>
+      <c r="J114" s="8" t="inlineStr"/>
+      <c r="K114" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J114" s="8" t="inlineStr"/>
+      <c r="L114" s="8" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="8" t="inlineStr">
@@ -11807,11 +12041,13 @@
         </is>
       </c>
       <c r="G115" s="8" t="inlineStr"/>
-      <c r="H115" s="8" t="n">
+      <c r="H115" s="8" t="inlineStr"/>
+      <c r="I115" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I115" s="8" t="inlineStr"/>
       <c r="J115" s="8" t="inlineStr"/>
+      <c r="K115" s="8" t="inlineStr"/>
+      <c r="L115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
@@ -11845,15 +12081,17 @@
         </is>
       </c>
       <c r="G116" s="8" t="inlineStr"/>
-      <c r="H116" s="8" t="n">
+      <c r="H116" s="8" t="inlineStr"/>
+      <c r="I116" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I116" s="8" t="inlineStr">
+      <c r="J116" s="8" t="inlineStr"/>
+      <c r="K116" s="8" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J116" s="8" t="inlineStr">
+      <c r="L116" s="8" t="inlineStr">
         <is>
           <t>분출 100%</t>
         </is>
@@ -11893,11 +12131,13 @@
       <c r="G117" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H117" s="8" t="n">
+      <c r="H117" s="8" t="inlineStr"/>
+      <c r="I117" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I117" s="8" t="inlineStr"/>
       <c r="J117" s="8" t="inlineStr"/>
+      <c r="K117" s="8" t="inlineStr"/>
+      <c r="L117" s="8" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
@@ -11933,11 +12173,13 @@
       <c r="G118" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H118" s="8" t="n">
+      <c r="H118" s="8" t="inlineStr"/>
+      <c r="I118" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I118" s="8" t="inlineStr"/>
       <c r="J118" s="8" t="inlineStr"/>
+      <c r="K118" s="8" t="inlineStr"/>
+      <c r="L118" s="8" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="8" t="inlineStr">
@@ -11972,12 +12214,14 @@
       </c>
       <c r="G119" s="8" t="inlineStr"/>
       <c r="H119" s="8" t="inlineStr"/>
-      <c r="I119" s="8" t="inlineStr">
+      <c r="I119" s="8" t="inlineStr"/>
+      <c r="J119" s="8" t="inlineStr"/>
+      <c r="K119" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J119" s="8" t="inlineStr"/>
+      <c r="L119" s="8" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
@@ -12011,11 +12255,13 @@
         </is>
       </c>
       <c r="G120" s="10" t="inlineStr"/>
-      <c r="H120" s="10" t="n">
+      <c r="H120" s="10" t="inlineStr"/>
+      <c r="I120" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I120" s="10" t="inlineStr"/>
       <c r="J120" s="10" t="inlineStr"/>
+      <c r="K120" s="10" t="inlineStr"/>
+      <c r="L120" s="10" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
@@ -12049,11 +12295,13 @@
         </is>
       </c>
       <c r="G121" s="10" t="inlineStr"/>
-      <c r="H121" s="10" t="n">
+      <c r="H121" s="10" t="inlineStr"/>
+      <c r="I121" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I121" s="10" t="inlineStr"/>
-      <c r="J121" s="10" t="inlineStr">
+      <c r="J121" s="10" t="inlineStr"/>
+      <c r="K121" s="10" t="inlineStr"/>
+      <c r="L121" s="10" t="inlineStr">
         <is>
           <t>진동 100%</t>
         </is>
@@ -12093,11 +12341,13 @@
       <c r="G122" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H122" s="10" t="n">
+      <c r="H122" s="10" t="inlineStr"/>
+      <c r="I122" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I122" s="10" t="inlineStr"/>
       <c r="J122" s="10" t="inlineStr"/>
+      <c r="K122" s="10" t="inlineStr"/>
+      <c r="L122" s="10" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
@@ -12133,11 +12383,13 @@
       <c r="G123" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H123" s="10" t="n">
+      <c r="H123" s="10" t="inlineStr"/>
+      <c r="I123" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I123" s="10" t="inlineStr"/>
       <c r="J123" s="10" t="inlineStr"/>
+      <c r="K123" s="10" t="inlineStr"/>
+      <c r="L123" s="10" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="10" t="inlineStr">
@@ -12172,12 +12424,14 @@
       </c>
       <c r="G124" s="10" t="inlineStr"/>
       <c r="H124" s="10" t="inlineStr"/>
-      <c r="I124" s="10" t="inlineStr">
+      <c r="I124" s="10" t="inlineStr"/>
+      <c r="J124" s="10" t="inlineStr"/>
+      <c r="K124" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J124" s="10" t="inlineStr"/>
+      <c r="L124" s="10" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
@@ -12211,11 +12465,13 @@
         </is>
       </c>
       <c r="G125" s="10" t="inlineStr"/>
-      <c r="H125" s="10" t="n">
+      <c r="H125" s="10" t="inlineStr"/>
+      <c r="I125" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I125" s="10" t="inlineStr"/>
       <c r="J125" s="10" t="inlineStr"/>
+      <c r="K125" s="10" t="inlineStr"/>
+      <c r="L125" s="10" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
@@ -12249,11 +12505,13 @@
         </is>
       </c>
       <c r="G126" s="10" t="inlineStr"/>
-      <c r="H126" s="10" t="n">
+      <c r="H126" s="10" t="inlineStr"/>
+      <c r="I126" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I126" s="10" t="inlineStr"/>
-      <c r="J126" s="10" t="inlineStr">
+      <c r="J126" s="10" t="inlineStr"/>
+      <c r="K126" s="10" t="inlineStr"/>
+      <c r="L126" s="10" t="inlineStr">
         <is>
           <t>참격 100%</t>
         </is>
@@ -12293,11 +12551,13 @@
       <c r="G127" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H127" s="10" t="n">
+      <c r="H127" s="10" t="inlineStr"/>
+      <c r="I127" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I127" s="10" t="inlineStr"/>
       <c r="J127" s="10" t="inlineStr"/>
+      <c r="K127" s="10" t="inlineStr"/>
+      <c r="L127" s="10" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
@@ -12333,11 +12593,13 @@
       <c r="G128" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H128" s="10" t="n">
+      <c r="H128" s="10" t="inlineStr"/>
+      <c r="I128" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I128" s="10" t="inlineStr"/>
       <c r="J128" s="10" t="inlineStr"/>
+      <c r="K128" s="10" t="inlineStr"/>
+      <c r="L128" s="10" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
@@ -12372,12 +12634,14 @@
       </c>
       <c r="G129" s="10" t="inlineStr"/>
       <c r="H129" s="10" t="inlineStr"/>
-      <c r="I129" s="10" t="inlineStr">
+      <c r="I129" s="10" t="inlineStr"/>
+      <c r="J129" s="10" t="inlineStr"/>
+      <c r="K129" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J129" s="10" t="inlineStr"/>
+      <c r="L129" s="10" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
@@ -12411,11 +12675,13 @@
         </is>
       </c>
       <c r="G130" s="10" t="inlineStr"/>
-      <c r="H130" s="10" t="n">
+      <c r="H130" s="10" t="inlineStr"/>
+      <c r="I130" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I130" s="10" t="inlineStr"/>
       <c r="J130" s="10" t="inlineStr"/>
+      <c r="K130" s="10" t="inlineStr"/>
+      <c r="L130" s="10" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
@@ -12449,11 +12715,13 @@
         </is>
       </c>
       <c r="G131" s="10" t="inlineStr"/>
-      <c r="H131" s="10" t="n">
+      <c r="H131" s="10" t="inlineStr"/>
+      <c r="I131" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I131" s="10" t="inlineStr"/>
-      <c r="J131" s="10" t="inlineStr">
+      <c r="J131" s="10" t="inlineStr"/>
+      <c r="K131" s="10" t="inlineStr"/>
+      <c r="L131" s="10" t="inlineStr">
         <is>
           <t>매장 100%</t>
         </is>
@@ -12493,11 +12761,13 @@
       <c r="G132" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H132" s="10" t="n">
+      <c r="H132" s="10" t="inlineStr"/>
+      <c r="I132" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I132" s="10" t="inlineStr"/>
       <c r="J132" s="10" t="inlineStr"/>
+      <c r="K132" s="10" t="inlineStr"/>
+      <c r="L132" s="10" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
@@ -12533,11 +12803,13 @@
       <c r="G133" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H133" s="10" t="n">
+      <c r="H133" s="10" t="inlineStr"/>
+      <c r="I133" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I133" s="10" t="inlineStr"/>
       <c r="J133" s="10" t="inlineStr"/>
+      <c r="K133" s="10" t="inlineStr"/>
+      <c r="L133" s="10" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
@@ -12572,12 +12844,14 @@
       </c>
       <c r="G134" s="10" t="inlineStr"/>
       <c r="H134" s="10" t="inlineStr"/>
-      <c r="I134" s="10" t="inlineStr">
+      <c r="I134" s="10" t="inlineStr"/>
+      <c r="J134" s="10" t="inlineStr"/>
+      <c r="K134" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J134" s="10" t="inlineStr"/>
+      <c r="L134" s="10" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="16" t="inlineStr">
@@ -12611,11 +12885,13 @@
         </is>
       </c>
       <c r="G135" s="16" t="inlineStr"/>
-      <c r="H135" s="16" t="n">
+      <c r="H135" s="16" t="inlineStr"/>
+      <c r="I135" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I135" s="16" t="inlineStr"/>
       <c r="J135" s="16" t="inlineStr"/>
+      <c r="K135" s="16" t="inlineStr"/>
+      <c r="L135" s="16" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="16" t="inlineStr">
@@ -12649,15 +12925,17 @@
         </is>
       </c>
       <c r="G136" s="16" t="inlineStr"/>
-      <c r="H136" s="16" t="n">
+      <c r="H136" s="16" t="inlineStr"/>
+      <c r="I136" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I136" s="16" t="inlineStr">
+      <c r="J136" s="16" t="inlineStr"/>
+      <c r="K136" s="16" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J136" s="16" t="inlineStr">
+      <c r="L136" s="16" t="inlineStr">
         <is>
           <t>죽음의 회전 100%</t>
         </is>
@@ -12697,11 +12975,13 @@
       <c r="G137" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="H137" s="16" t="n">
+      <c r="H137" s="16" t="inlineStr"/>
+      <c r="I137" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I137" s="16" t="inlineStr"/>
       <c r="J137" s="16" t="inlineStr"/>
+      <c r="K137" s="16" t="inlineStr"/>
+      <c r="L137" s="16" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="16" t="inlineStr">
@@ -12735,11 +13015,13 @@
         </is>
       </c>
       <c r="G138" s="16" t="inlineStr"/>
-      <c r="H138" s="16" t="n">
+      <c r="H138" s="16" t="inlineStr"/>
+      <c r="I138" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I138" s="16" t="inlineStr"/>
       <c r="J138" s="16" t="inlineStr"/>
+      <c r="K138" s="16" t="inlineStr"/>
+      <c r="L138" s="16" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="16" t="inlineStr">
@@ -12775,11 +13057,13 @@
       <c r="G139" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="H139" s="16" t="n">
+      <c r="H139" s="16" t="inlineStr"/>
+      <c r="I139" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I139" s="16" t="inlineStr"/>
       <c r="J139" s="16" t="inlineStr"/>
+      <c r="K139" s="16" t="inlineStr"/>
+      <c r="L139" s="16" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="16" t="inlineStr">
@@ -12814,12 +13098,14 @@
       </c>
       <c r="G140" s="16" t="inlineStr"/>
       <c r="H140" s="16" t="inlineStr"/>
-      <c r="I140" s="16" t="inlineStr">
+      <c r="I140" s="16" t="inlineStr"/>
+      <c r="J140" s="16" t="inlineStr"/>
+      <c r="K140" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J140" s="16" t="inlineStr"/>
+      <c r="L140" s="16" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="16" t="inlineStr">
@@ -12853,11 +13139,13 @@
         </is>
       </c>
       <c r="G141" s="16" t="inlineStr"/>
-      <c r="H141" s="16" t="n">
+      <c r="H141" s="16" t="inlineStr"/>
+      <c r="I141" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I141" s="16" t="inlineStr"/>
       <c r="J141" s="16" t="inlineStr"/>
+      <c r="K141" s="16" t="inlineStr"/>
+      <c r="L141" s="16" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="16" t="inlineStr">
@@ -12891,11 +13179,13 @@
         </is>
       </c>
       <c r="G142" s="16" t="inlineStr"/>
-      <c r="H142" s="16" t="n">
+      <c r="H142" s="16" t="inlineStr"/>
+      <c r="I142" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I142" s="16" t="inlineStr"/>
-      <c r="J142" s="16" t="inlineStr">
+      <c r="J142" s="16" t="inlineStr"/>
+      <c r="K142" s="16" t="inlineStr"/>
+      <c r="L142" s="16" t="inlineStr">
         <is>
           <t>질식 100%</t>
         </is>
@@ -12935,11 +13225,13 @@
       <c r="G143" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="H143" s="16" t="n">
+      <c r="H143" s="16" t="inlineStr"/>
+      <c r="I143" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I143" s="16" t="inlineStr"/>
       <c r="J143" s="16" t="inlineStr"/>
+      <c r="K143" s="16" t="inlineStr"/>
+      <c r="L143" s="16" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="16" t="inlineStr">
@@ -12973,11 +13265,13 @@
         </is>
       </c>
       <c r="G144" s="16" t="inlineStr"/>
-      <c r="H144" s="16" t="n">
+      <c r="H144" s="16" t="inlineStr"/>
+      <c r="I144" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I144" s="16" t="inlineStr"/>
       <c r="J144" s="16" t="inlineStr"/>
+      <c r="K144" s="16" t="inlineStr"/>
+      <c r="L144" s="16" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="16" t="inlineStr">
@@ -13013,11 +13307,13 @@
       <c r="G145" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="H145" s="16" t="n">
+      <c r="H145" s="16" t="inlineStr"/>
+      <c r="I145" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I145" s="16" t="inlineStr"/>
       <c r="J145" s="16" t="inlineStr"/>
+      <c r="K145" s="16" t="inlineStr"/>
+      <c r="L145" s="16" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="16" t="inlineStr">
@@ -13052,12 +13348,14 @@
       </c>
       <c r="G146" s="16" t="inlineStr"/>
       <c r="H146" s="16" t="inlineStr"/>
-      <c r="I146" s="16" t="inlineStr">
+      <c r="I146" s="16" t="inlineStr"/>
+      <c r="J146" s="16" t="inlineStr"/>
+      <c r="K146" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J146" s="16" t="inlineStr"/>
+      <c r="L146" s="16" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="16" t="inlineStr">
@@ -13091,11 +13389,13 @@
         </is>
       </c>
       <c r="G147" s="16" t="inlineStr"/>
-      <c r="H147" s="16" t="n">
+      <c r="H147" s="16" t="inlineStr"/>
+      <c r="I147" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I147" s="16" t="inlineStr"/>
       <c r="J147" s="16" t="inlineStr"/>
+      <c r="K147" s="16" t="inlineStr"/>
+      <c r="L147" s="16" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="16" t="inlineStr">
@@ -13129,11 +13429,13 @@
         </is>
       </c>
       <c r="G148" s="16" t="inlineStr"/>
-      <c r="H148" s="16" t="n">
+      <c r="H148" s="16" t="inlineStr"/>
+      <c r="I148" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I148" s="16" t="inlineStr"/>
-      <c r="J148" s="16" t="inlineStr">
+      <c r="J148" s="16" t="inlineStr"/>
+      <c r="K148" s="16" t="inlineStr"/>
+      <c r="L148" s="16" t="inlineStr">
         <is>
           <t>무덤의 부름 100%</t>
         </is>
@@ -13173,11 +13475,13 @@
       <c r="G149" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="H149" s="16" t="n">
+      <c r="H149" s="16" t="inlineStr"/>
+      <c r="I149" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I149" s="16" t="inlineStr"/>
       <c r="J149" s="16" t="inlineStr"/>
+      <c r="K149" s="16" t="inlineStr"/>
+      <c r="L149" s="16" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="16" t="inlineStr">
@@ -13211,11 +13515,13 @@
         </is>
       </c>
       <c r="G150" s="16" t="inlineStr"/>
-      <c r="H150" s="16" t="n">
+      <c r="H150" s="16" t="inlineStr"/>
+      <c r="I150" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I150" s="16" t="inlineStr"/>
       <c r="J150" s="16" t="inlineStr"/>
+      <c r="K150" s="16" t="inlineStr"/>
+      <c r="L150" s="16" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="16" t="inlineStr">
@@ -13251,11 +13557,13 @@
       <c r="G151" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="H151" s="16" t="n">
+      <c r="H151" s="16" t="inlineStr"/>
+      <c r="I151" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I151" s="16" t="inlineStr"/>
       <c r="J151" s="16" t="inlineStr"/>
+      <c r="K151" s="16" t="inlineStr"/>
+      <c r="L151" s="16" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="16" t="inlineStr">
@@ -13290,12 +13598,14 @@
       </c>
       <c r="G152" s="16" t="inlineStr"/>
       <c r="H152" s="16" t="inlineStr"/>
-      <c r="I152" s="16" t="inlineStr">
+      <c r="I152" s="16" t="inlineStr"/>
+      <c r="J152" s="16" t="inlineStr"/>
+      <c r="K152" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J152" s="16" t="inlineStr"/>
+      <c r="L152" s="16" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="8" t="inlineStr">
@@ -13329,11 +13639,13 @@
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr"/>
-      <c r="H153" s="8" t="n">
+      <c r="H153" s="8" t="inlineStr"/>
+      <c r="I153" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I153" s="8" t="inlineStr"/>
       <c r="J153" s="8" t="inlineStr"/>
+      <c r="K153" s="8" t="inlineStr"/>
+      <c r="L153" s="8" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="8" t="inlineStr">
@@ -13367,11 +13679,13 @@
         </is>
       </c>
       <c r="G154" s="8" t="inlineStr"/>
-      <c r="H154" s="8" t="n">
+      <c r="H154" s="8" t="inlineStr"/>
+      <c r="I154" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I154" s="8" t="inlineStr"/>
-      <c r="J154" s="8" t="inlineStr">
+      <c r="J154" s="8" t="inlineStr"/>
+      <c r="K154" s="8" t="inlineStr"/>
+      <c r="L154" s="8" t="inlineStr">
         <is>
           <t>끽 소리 50%</t>
         </is>
@@ -13411,11 +13725,13 @@
       <c r="G155" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H155" s="8" t="n">
+      <c r="H155" s="8" t="inlineStr"/>
+      <c r="I155" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I155" s="8" t="inlineStr"/>
       <c r="J155" s="8" t="inlineStr"/>
+      <c r="K155" s="8" t="inlineStr"/>
+      <c r="L155" s="8" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="8" t="inlineStr">
@@ -13451,11 +13767,13 @@
       <c r="G156" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H156" s="8" t="n">
+      <c r="H156" s="8" t="inlineStr"/>
+      <c r="I156" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I156" s="8" t="inlineStr"/>
       <c r="J156" s="8" t="inlineStr"/>
+      <c r="K156" s="8" t="inlineStr"/>
+      <c r="L156" s="8" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
@@ -13490,12 +13808,14 @@
       </c>
       <c r="G157" s="8" t="inlineStr"/>
       <c r="H157" s="8" t="inlineStr"/>
-      <c r="I157" s="8" t="inlineStr">
+      <c r="I157" s="8" t="inlineStr"/>
+      <c r="J157" s="8" t="inlineStr"/>
+      <c r="K157" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J157" s="8" t="inlineStr"/>
+      <c r="L157" s="8" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="8" t="inlineStr">
@@ -13529,11 +13849,13 @@
         </is>
       </c>
       <c r="G158" s="8" t="inlineStr"/>
-      <c r="H158" s="8" t="n">
+      <c r="H158" s="8" t="inlineStr"/>
+      <c r="I158" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I158" s="8" t="inlineStr"/>
-      <c r="J158" s="8" t="inlineStr">
+      <c r="J158" s="8" t="inlineStr"/>
+      <c r="K158" s="8" t="inlineStr"/>
+      <c r="L158" s="8" t="inlineStr">
         <is>
           <t>시선 광선 100%</t>
         </is>
@@ -13573,11 +13895,13 @@
       <c r="G159" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H159" s="8" t="n">
+      <c r="H159" s="8" t="inlineStr"/>
+      <c r="I159" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I159" s="8" t="inlineStr"/>
       <c r="J159" s="8" t="inlineStr"/>
+      <c r="K159" s="8" t="inlineStr"/>
+      <c r="L159" s="8" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="8" t="inlineStr">
@@ -13611,15 +13935,17 @@
         </is>
       </c>
       <c r="G160" s="8" t="inlineStr"/>
-      <c r="H160" s="8" t="n">
+      <c r="H160" s="8" t="inlineStr"/>
+      <c r="I160" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I160" s="8" t="inlineStr">
+      <c r="J160" s="8" t="inlineStr"/>
+      <c r="K160" s="8" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J160" s="8" t="inlineStr"/>
+      <c r="L160" s="8" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="8" t="inlineStr">
@@ -13655,11 +13981,13 @@
       <c r="G161" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H161" s="8" t="n">
+      <c r="H161" s="8" t="inlineStr"/>
+      <c r="I161" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I161" s="8" t="inlineStr"/>
       <c r="J161" s="8" t="inlineStr"/>
+      <c r="K161" s="8" t="inlineStr"/>
+      <c r="L161" s="8" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="8" t="inlineStr">
@@ -13694,12 +14022,14 @@
       </c>
       <c r="G162" s="8" t="inlineStr"/>
       <c r="H162" s="8" t="inlineStr"/>
-      <c r="I162" s="8" t="inlineStr">
+      <c r="I162" s="8" t="inlineStr"/>
+      <c r="J162" s="8" t="inlineStr"/>
+      <c r="K162" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J162" s="8" t="inlineStr"/>
+      <c r="L162" s="8" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="8" t="inlineStr">
@@ -13733,11 +14063,13 @@
         </is>
       </c>
       <c r="G163" s="8" t="inlineStr"/>
-      <c r="H163" s="8" t="n">
+      <c r="H163" s="8" t="inlineStr"/>
+      <c r="I163" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I163" s="8" t="inlineStr"/>
       <c r="J163" s="8" t="inlineStr"/>
+      <c r="K163" s="8" t="inlineStr"/>
+      <c r="L163" s="8" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="8" t="inlineStr">
@@ -13773,11 +14105,13 @@
       <c r="G164" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H164" s="8" t="n">
+      <c r="H164" s="8" t="inlineStr"/>
+      <c r="I164" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I164" s="8" t="inlineStr"/>
-      <c r="J164" s="8" t="inlineStr">
+      <c r="J164" s="8" t="inlineStr"/>
+      <c r="K164" s="8" t="inlineStr"/>
+      <c r="L164" s="8" t="inlineStr">
         <is>
           <t>고치 50%</t>
         </is>
@@ -13815,11 +14149,13 @@
         </is>
       </c>
       <c r="G165" s="8" t="inlineStr"/>
-      <c r="H165" s="8" t="n">
+      <c r="H165" s="8" t="inlineStr"/>
+      <c r="I165" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I165" s="8" t="inlineStr"/>
       <c r="J165" s="8" t="inlineStr"/>
+      <c r="K165" s="8" t="inlineStr"/>
+      <c r="L165" s="8" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="8" t="inlineStr">
@@ -13855,11 +14191,13 @@
       <c r="G166" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H166" s="8" t="n">
+      <c r="H166" s="8" t="inlineStr"/>
+      <c r="I166" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I166" s="8" t="inlineStr"/>
       <c r="J166" s="8" t="inlineStr"/>
+      <c r="K166" s="8" t="inlineStr"/>
+      <c r="L166" s="8" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
@@ -13894,12 +14232,14 @@
       </c>
       <c r="G167" s="8" t="inlineStr"/>
       <c r="H167" s="8" t="inlineStr"/>
-      <c r="I167" s="8" t="inlineStr">
+      <c r="I167" s="8" t="inlineStr"/>
+      <c r="J167" s="8" t="inlineStr"/>
+      <c r="K167" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J167" s="8" t="inlineStr"/>
+      <c r="L167" s="8" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="8" t="inlineStr">
@@ -13933,11 +14273,13 @@
         </is>
       </c>
       <c r="G168" s="8" t="inlineStr"/>
-      <c r="H168" s="8" t="n">
+      <c r="H168" s="8" t="inlineStr"/>
+      <c r="I168" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I168" s="8" t="inlineStr"/>
-      <c r="J168" s="8" t="inlineStr">
+      <c r="J168" s="8" t="inlineStr"/>
+      <c r="K168" s="8" t="inlineStr"/>
+      <c r="L168" s="8" t="inlineStr">
         <is>
           <t>맥동 50%</t>
         </is>
@@ -13975,11 +14317,13 @@
         </is>
       </c>
       <c r="G169" s="8" t="inlineStr"/>
-      <c r="H169" s="8" t="n">
+      <c r="H169" s="8" t="inlineStr"/>
+      <c r="I169" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I169" s="8" t="inlineStr"/>
-      <c r="J169" s="8" t="inlineStr">
+      <c r="J169" s="8" t="inlineStr"/>
+      <c r="K169" s="8" t="inlineStr"/>
+      <c r="L169" s="8" t="inlineStr">
         <is>
           <t>맥동 100%</t>
         </is>
@@ -14019,11 +14363,13 @@
       <c r="G170" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H170" s="8" t="n">
+      <c r="H170" s="8" t="inlineStr"/>
+      <c r="I170" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I170" s="8" t="inlineStr"/>
       <c r="J170" s="8" t="inlineStr"/>
+      <c r="K170" s="8" t="inlineStr"/>
+      <c r="L170" s="8" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="8" t="inlineStr">
@@ -14059,11 +14405,13 @@
       <c r="G171" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H171" s="8" t="n">
+      <c r="H171" s="8" t="inlineStr"/>
+      <c r="I171" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I171" s="8" t="inlineStr"/>
       <c r="J171" s="8" t="inlineStr"/>
+      <c r="K171" s="8" t="inlineStr"/>
+      <c r="L171" s="8" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="8" t="inlineStr">
@@ -14098,12 +14446,14 @@
       </c>
       <c r="G172" s="8" t="inlineStr"/>
       <c r="H172" s="8" t="inlineStr"/>
-      <c r="I172" s="8" t="inlineStr">
+      <c r="I172" s="8" t="inlineStr"/>
+      <c r="J172" s="8" t="inlineStr"/>
+      <c r="K172" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J172" s="8" t="inlineStr"/>
+      <c r="L172" s="8" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="8" t="inlineStr">
@@ -14137,11 +14487,13 @@
         </is>
       </c>
       <c r="G173" s="8" t="inlineStr"/>
-      <c r="H173" s="8" t="n">
+      <c r="H173" s="8" t="inlineStr"/>
+      <c r="I173" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I173" s="8" t="inlineStr"/>
       <c r="J173" s="8" t="inlineStr"/>
+      <c r="K173" s="8" t="inlineStr"/>
+      <c r="L173" s="8" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="8" t="inlineStr">
@@ -14175,15 +14527,17 @@
         </is>
       </c>
       <c r="G174" s="8" t="inlineStr"/>
-      <c r="H174" s="8" t="n">
+      <c r="H174" s="8" t="inlineStr"/>
+      <c r="I174" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I174" s="8" t="inlineStr">
+      <c r="J174" s="8" t="inlineStr"/>
+      <c r="K174" s="8" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J174" s="8" t="inlineStr">
+      <c r="L174" s="8" t="inlineStr">
         <is>
           <t>제물 50%</t>
         </is>
@@ -14223,11 +14577,13 @@
       <c r="G175" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H175" s="8" t="n">
+      <c r="H175" s="8" t="inlineStr"/>
+      <c r="I175" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I175" s="8" t="inlineStr"/>
       <c r="J175" s="8" t="inlineStr"/>
+      <c r="K175" s="8" t="inlineStr"/>
+      <c r="L175" s="8" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="8" t="inlineStr">
@@ -14263,11 +14619,13 @@
       <c r="G176" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H176" s="8" t="n">
+      <c r="H176" s="8" t="inlineStr"/>
+      <c r="I176" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I176" s="8" t="inlineStr"/>
       <c r="J176" s="8" t="inlineStr"/>
+      <c r="K176" s="8" t="inlineStr"/>
+      <c r="L176" s="8" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="8" t="inlineStr">
@@ -14302,12 +14660,14 @@
       </c>
       <c r="G177" s="8" t="inlineStr"/>
       <c r="H177" s="8" t="inlineStr"/>
-      <c r="I177" s="8" t="inlineStr">
+      <c r="I177" s="8" t="inlineStr"/>
+      <c r="J177" s="8" t="inlineStr"/>
+      <c r="K177" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J177" s="8" t="inlineStr"/>
+      <c r="L177" s="8" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="8" t="inlineStr">
@@ -14341,11 +14701,13 @@
         </is>
       </c>
       <c r="G178" s="8" t="inlineStr"/>
-      <c r="H178" s="8" t="n">
+      <c r="H178" s="8" t="inlineStr"/>
+      <c r="I178" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I178" s="8" t="inlineStr"/>
       <c r="J178" s="8" t="inlineStr"/>
+      <c r="K178" s="8" t="inlineStr"/>
+      <c r="L178" s="8" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="8" t="inlineStr">
@@ -14379,11 +14741,13 @@
         </is>
       </c>
       <c r="G179" s="8" t="inlineStr"/>
-      <c r="H179" s="8" t="n">
+      <c r="H179" s="8" t="inlineStr"/>
+      <c r="I179" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I179" s="8" t="inlineStr"/>
-      <c r="J179" s="8" t="inlineStr">
+      <c r="J179" s="8" t="inlineStr"/>
+      <c r="K179" s="8" t="inlineStr"/>
+      <c r="L179" s="8" t="inlineStr">
         <is>
           <t>균열 100%</t>
         </is>
@@ -14423,11 +14787,13 @@
       <c r="G180" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H180" s="8" t="n">
+      <c r="H180" s="8" t="inlineStr"/>
+      <c r="I180" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I180" s="8" t="inlineStr"/>
       <c r="J180" s="8" t="inlineStr"/>
+      <c r="K180" s="8" t="inlineStr"/>
+      <c r="L180" s="8" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="8" t="inlineStr">
@@ -14463,11 +14829,13 @@
       <c r="G181" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H181" s="8" t="n">
+      <c r="H181" s="8" t="inlineStr"/>
+      <c r="I181" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I181" s="8" t="inlineStr"/>
       <c r="J181" s="8" t="inlineStr"/>
+      <c r="K181" s="8" t="inlineStr"/>
+      <c r="L181" s="8" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="8" t="inlineStr">
@@ -14502,12 +14870,14 @@
       </c>
       <c r="G182" s="8" t="inlineStr"/>
       <c r="H182" s="8" t="inlineStr"/>
-      <c r="I182" s="8" t="inlineStr">
+      <c r="I182" s="8" t="inlineStr"/>
+      <c r="J182" s="8" t="inlineStr"/>
+      <c r="K182" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J182" s="8" t="inlineStr"/>
+      <c r="L182" s="8" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="10" t="inlineStr">
@@ -14541,11 +14911,13 @@
         </is>
       </c>
       <c r="G183" s="10" t="inlineStr"/>
-      <c r="H183" s="10" t="n">
+      <c r="H183" s="10" t="inlineStr"/>
+      <c r="I183" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I183" s="10" t="inlineStr"/>
       <c r="J183" s="10" t="inlineStr"/>
+      <c r="K183" s="10" t="inlineStr"/>
+      <c r="L183" s="10" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="10" t="inlineStr">
@@ -14579,11 +14951,13 @@
         </is>
       </c>
       <c r="G184" s="10" t="inlineStr"/>
-      <c r="H184" s="10" t="n">
+      <c r="H184" s="10" t="inlineStr"/>
+      <c r="I184" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I184" s="10" t="inlineStr"/>
       <c r="J184" s="10" t="inlineStr"/>
+      <c r="K184" s="10" t="inlineStr"/>
+      <c r="L184" s="10" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="10" t="inlineStr">
@@ -14617,11 +14991,13 @@
         </is>
       </c>
       <c r="G185" s="10" t="inlineStr"/>
-      <c r="H185" s="10" t="n">
+      <c r="H185" s="10" t="inlineStr"/>
+      <c r="I185" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I185" s="10" t="inlineStr"/>
-      <c r="J185" s="10" t="inlineStr">
+      <c r="J185" s="10" t="inlineStr"/>
+      <c r="K185" s="10" t="inlineStr"/>
+      <c r="L185" s="10" t="inlineStr">
         <is>
           <t>붕괴 100%</t>
         </is>
@@ -14661,11 +15037,13 @@
       <c r="G186" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H186" s="10" t="n">
+      <c r="H186" s="10" t="inlineStr"/>
+      <c r="I186" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I186" s="10" t="inlineStr"/>
       <c r="J186" s="10" t="inlineStr"/>
+      <c r="K186" s="10" t="inlineStr"/>
+      <c r="L186" s="10" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="10" t="inlineStr">
@@ -14701,11 +15079,13 @@
       <c r="G187" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H187" s="10" t="n">
+      <c r="H187" s="10" t="inlineStr"/>
+      <c r="I187" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I187" s="10" t="inlineStr"/>
       <c r="J187" s="10" t="inlineStr"/>
+      <c r="K187" s="10" t="inlineStr"/>
+      <c r="L187" s="10" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="10" t="inlineStr">
@@ -14740,12 +15120,14 @@
       </c>
       <c r="G188" s="10" t="inlineStr"/>
       <c r="H188" s="10" t="inlineStr"/>
-      <c r="I188" s="10" t="inlineStr">
+      <c r="I188" s="10" t="inlineStr"/>
+      <c r="J188" s="10" t="inlineStr"/>
+      <c r="K188" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J188" s="10" t="inlineStr"/>
+      <c r="L188" s="10" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="10" t="inlineStr">
@@ -14779,11 +15161,13 @@
         </is>
       </c>
       <c r="G189" s="10" t="inlineStr"/>
-      <c r="H189" s="10" t="n">
+      <c r="H189" s="10" t="inlineStr"/>
+      <c r="I189" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I189" s="10" t="inlineStr"/>
       <c r="J189" s="10" t="inlineStr"/>
+      <c r="K189" s="10" t="inlineStr"/>
+      <c r="L189" s="10" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="10" t="inlineStr">
@@ -14817,11 +15201,13 @@
         </is>
       </c>
       <c r="G190" s="10" t="inlineStr"/>
-      <c r="H190" s="10" t="n">
+      <c r="H190" s="10" t="inlineStr"/>
+      <c r="I190" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I190" s="10" t="inlineStr"/>
       <c r="J190" s="10" t="inlineStr"/>
+      <c r="K190" s="10" t="inlineStr"/>
+      <c r="L190" s="10" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="10" t="inlineStr">
@@ -14855,11 +15241,13 @@
         </is>
       </c>
       <c r="G191" s="10" t="inlineStr"/>
-      <c r="H191" s="10" t="n">
+      <c r="H191" s="10" t="inlineStr"/>
+      <c r="I191" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I191" s="10" t="inlineStr"/>
-      <c r="J191" s="10" t="inlineStr">
+      <c r="J191" s="10" t="inlineStr"/>
+      <c r="K191" s="10" t="inlineStr"/>
+      <c r="L191" s="10" t="inlineStr">
         <is>
           <t>내려찍기 100%</t>
         </is>
@@ -14899,11 +15287,13 @@
       <c r="G192" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H192" s="10" t="n">
+      <c r="H192" s="10" t="inlineStr"/>
+      <c r="I192" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I192" s="10" t="inlineStr"/>
       <c r="J192" s="10" t="inlineStr"/>
+      <c r="K192" s="10" t="inlineStr"/>
+      <c r="L192" s="10" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="10" t="inlineStr">
@@ -14939,11 +15329,13 @@
       <c r="G193" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H193" s="10" t="n">
+      <c r="H193" s="10" t="inlineStr"/>
+      <c r="I193" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I193" s="10" t="inlineStr"/>
       <c r="J193" s="10" t="inlineStr"/>
+      <c r="K193" s="10" t="inlineStr"/>
+      <c r="L193" s="10" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="10" t="inlineStr">
@@ -14978,12 +15370,14 @@
       </c>
       <c r="G194" s="10" t="inlineStr"/>
       <c r="H194" s="10" t="inlineStr"/>
-      <c r="I194" s="10" t="inlineStr">
+      <c r="I194" s="10" t="inlineStr"/>
+      <c r="J194" s="10" t="inlineStr"/>
+      <c r="K194" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J194" s="10" t="inlineStr"/>
+      <c r="L194" s="10" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="10" t="inlineStr">
@@ -15017,11 +15411,13 @@
         </is>
       </c>
       <c r="G195" s="10" t="inlineStr"/>
-      <c r="H195" s="10" t="n">
+      <c r="H195" s="10" t="inlineStr"/>
+      <c r="I195" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I195" s="10" t="inlineStr"/>
       <c r="J195" s="10" t="inlineStr"/>
+      <c r="K195" s="10" t="inlineStr"/>
+      <c r="L195" s="10" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="10" t="inlineStr">
@@ -15055,15 +15451,17 @@
         </is>
       </c>
       <c r="G196" s="10" t="inlineStr"/>
-      <c r="H196" s="10" t="n">
+      <c r="H196" s="10" t="inlineStr"/>
+      <c r="I196" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I196" s="10" t="inlineStr">
+      <c r="J196" s="10" t="inlineStr"/>
+      <c r="K196" s="10" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J196" s="10" t="inlineStr">
+      <c r="L196" s="10" t="inlineStr">
         <is>
           <t>큰 종소리 100%</t>
         </is>
@@ -15103,11 +15501,13 @@
       <c r="G197" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H197" s="10" t="n">
+      <c r="H197" s="10" t="inlineStr"/>
+      <c r="I197" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I197" s="10" t="inlineStr"/>
       <c r="J197" s="10" t="inlineStr"/>
+      <c r="K197" s="10" t="inlineStr"/>
+      <c r="L197" s="10" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="10" t="inlineStr">
@@ -15143,11 +15543,13 @@
       <c r="G198" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="H198" s="10" t="n">
+      <c r="H198" s="10" t="inlineStr"/>
+      <c r="I198" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I198" s="10" t="inlineStr"/>
       <c r="J198" s="10" t="inlineStr"/>
+      <c r="K198" s="10" t="inlineStr"/>
+      <c r="L198" s="10" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="10" t="inlineStr">
@@ -15182,12 +15584,14 @@
       </c>
       <c r="G199" s="10" t="inlineStr"/>
       <c r="H199" s="10" t="inlineStr"/>
-      <c r="I199" s="10" t="inlineStr">
+      <c r="I199" s="10" t="inlineStr"/>
+      <c r="J199" s="10" t="inlineStr"/>
+      <c r="K199" s="10" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J199" s="10" t="inlineStr"/>
+      <c r="L199" s="10" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="16" t="inlineStr">
@@ -15221,11 +15625,13 @@
         </is>
       </c>
       <c r="G200" s="16" t="inlineStr"/>
-      <c r="H200" s="16" t="n">
+      <c r="H200" s="16" t="inlineStr"/>
+      <c r="I200" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I200" s="16" t="inlineStr"/>
       <c r="J200" s="16" t="inlineStr"/>
+      <c r="K200" s="16" t="inlineStr"/>
+      <c r="L200" s="16" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="16" t="inlineStr">
@@ -15259,15 +15665,17 @@
         </is>
       </c>
       <c r="G201" s="16" t="inlineStr"/>
-      <c r="H201" s="16" t="n">
+      <c r="H201" s="16" t="inlineStr"/>
+      <c r="I201" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I201" s="16" t="inlineStr">
+      <c r="J201" s="16" t="inlineStr"/>
+      <c r="K201" s="16" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J201" s="16" t="inlineStr">
+      <c r="L201" s="16" t="inlineStr">
         <is>
           <t>악몽 100%</t>
         </is>
@@ -15307,11 +15715,13 @@
       <c r="G202" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="H202" s="16" t="n">
+      <c r="H202" s="16" t="inlineStr"/>
+      <c r="I202" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I202" s="16" t="inlineStr"/>
       <c r="J202" s="16" t="inlineStr"/>
+      <c r="K202" s="16" t="inlineStr"/>
+      <c r="L202" s="16" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="16" t="inlineStr">
@@ -15345,11 +15755,13 @@
         </is>
       </c>
       <c r="G203" s="16" t="inlineStr"/>
-      <c r="H203" s="16" t="n">
+      <c r="H203" s="16" t="inlineStr"/>
+      <c r="I203" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I203" s="16" t="inlineStr"/>
       <c r="J203" s="16" t="inlineStr"/>
+      <c r="K203" s="16" t="inlineStr"/>
+      <c r="L203" s="16" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="16" t="inlineStr">
@@ -15385,11 +15797,13 @@
       <c r="G204" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="H204" s="16" t="n">
+      <c r="H204" s="16" t="inlineStr"/>
+      <c r="I204" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I204" s="16" t="inlineStr"/>
       <c r="J204" s="16" t="inlineStr"/>
+      <c r="K204" s="16" t="inlineStr"/>
+      <c r="L204" s="16" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="16" t="inlineStr">
@@ -15424,12 +15838,14 @@
       </c>
       <c r="G205" s="16" t="inlineStr"/>
       <c r="H205" s="16" t="inlineStr"/>
-      <c r="I205" s="16" t="inlineStr">
+      <c r="I205" s="16" t="inlineStr"/>
+      <c r="J205" s="16" t="inlineStr"/>
+      <c r="K205" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J205" s="16" t="inlineStr"/>
+      <c r="L205" s="16" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="16" t="inlineStr">
@@ -15463,11 +15879,13 @@
         </is>
       </c>
       <c r="G206" s="16" t="inlineStr"/>
-      <c r="H206" s="16" t="n">
+      <c r="H206" s="16" t="inlineStr"/>
+      <c r="I206" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I206" s="16" t="inlineStr"/>
       <c r="J206" s="16" t="inlineStr"/>
+      <c r="K206" s="16" t="inlineStr"/>
+      <c r="L206" s="16" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="16" t="inlineStr">
@@ -15501,11 +15919,13 @@
         </is>
       </c>
       <c r="G207" s="16" t="inlineStr"/>
-      <c r="H207" s="16" t="n">
+      <c r="H207" s="16" t="inlineStr"/>
+      <c r="I207" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I207" s="16" t="inlineStr"/>
-      <c r="J207" s="16" t="inlineStr">
+      <c r="J207" s="16" t="inlineStr"/>
+      <c r="K207" s="16" t="inlineStr"/>
+      <c r="L207" s="16" t="inlineStr">
         <is>
           <t>짓씹기 100%</t>
         </is>
@@ -15543,11 +15963,13 @@
         </is>
       </c>
       <c r="G208" s="16" t="inlineStr"/>
-      <c r="H208" s="16" t="n">
+      <c r="H208" s="16" t="inlineStr"/>
+      <c r="I208" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I208" s="16" t="inlineStr"/>
       <c r="J208" s="16" t="inlineStr"/>
+      <c r="K208" s="16" t="inlineStr"/>
+      <c r="L208" s="16" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="16" t="inlineStr">
@@ -15583,11 +16005,13 @@
       <c r="G209" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="H209" s="16" t="n">
+      <c r="H209" s="16" t="inlineStr"/>
+      <c r="I209" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I209" s="16" t="inlineStr"/>
       <c r="J209" s="16" t="inlineStr"/>
+      <c r="K209" s="16" t="inlineStr"/>
+      <c r="L209" s="16" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="16" t="inlineStr">
@@ -15623,11 +16047,13 @@
       <c r="G210" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="H210" s="16" t="n">
+      <c r="H210" s="16" t="inlineStr"/>
+      <c r="I210" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I210" s="16" t="inlineStr"/>
       <c r="J210" s="16" t="inlineStr"/>
+      <c r="K210" s="16" t="inlineStr"/>
+      <c r="L210" s="16" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="16" t="inlineStr">
@@ -15662,12 +16088,14 @@
       </c>
       <c r="G211" s="16" t="inlineStr"/>
       <c r="H211" s="16" t="inlineStr"/>
-      <c r="I211" s="16" t="inlineStr">
+      <c r="I211" s="16" t="inlineStr"/>
+      <c r="J211" s="16" t="inlineStr"/>
+      <c r="K211" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J211" s="16" t="inlineStr"/>
+      <c r="L211" s="16" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="16" t="inlineStr">
@@ -15701,11 +16129,13 @@
         </is>
       </c>
       <c r="G212" s="16" t="inlineStr"/>
-      <c r="H212" s="16" t="n">
+      <c r="H212" s="16" t="inlineStr"/>
+      <c r="I212" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I212" s="16" t="inlineStr"/>
       <c r="J212" s="16" t="inlineStr"/>
+      <c r="K212" s="16" t="inlineStr"/>
+      <c r="L212" s="16" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="16" t="inlineStr">
@@ -15739,11 +16169,13 @@
         </is>
       </c>
       <c r="G213" s="16" t="inlineStr"/>
-      <c r="H213" s="16" t="n">
+      <c r="H213" s="16" t="inlineStr"/>
+      <c r="I213" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I213" s="16" t="inlineStr"/>
-      <c r="J213" s="16" t="inlineStr">
+      <c r="J213" s="16" t="inlineStr"/>
+      <c r="K213" s="16" t="inlineStr"/>
+      <c r="L213" s="16" t="inlineStr">
         <is>
           <t>심판 100%</t>
         </is>
@@ -15781,11 +16213,13 @@
         </is>
       </c>
       <c r="G214" s="16" t="inlineStr"/>
-      <c r="H214" s="16" t="n">
+      <c r="H214" s="16" t="inlineStr"/>
+      <c r="I214" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I214" s="16" t="inlineStr"/>
-      <c r="J214" s="16" t="inlineStr">
+      <c r="J214" s="16" t="inlineStr"/>
+      <c r="K214" s="16" t="inlineStr"/>
+      <c r="L214" s="16" t="inlineStr">
         <is>
           <t>심판 70%</t>
         </is>
@@ -15825,11 +16259,13 @@
       <c r="G215" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="H215" s="16" t="n">
+      <c r="H215" s="16" t="inlineStr"/>
+      <c r="I215" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="I215" s="16" t="inlineStr"/>
       <c r="J215" s="16" t="inlineStr"/>
+      <c r="K215" s="16" t="inlineStr"/>
+      <c r="L215" s="16" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="16" t="inlineStr">
@@ -15865,11 +16301,13 @@
       <c r="G216" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="H216" s="16" t="n">
+      <c r="H216" s="16" t="inlineStr"/>
+      <c r="I216" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I216" s="16" t="inlineStr"/>
       <c r="J216" s="16" t="inlineStr"/>
+      <c r="K216" s="16" t="inlineStr"/>
+      <c r="L216" s="16" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="16" t="inlineStr">
@@ -15904,12 +16342,14 @@
       </c>
       <c r="G217" s="16" t="inlineStr"/>
       <c r="H217" s="16" t="inlineStr"/>
-      <c r="I217" s="16" t="inlineStr">
+      <c r="I217" s="16" t="inlineStr"/>
+      <c r="J217" s="16" t="inlineStr"/>
+      <c r="K217" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J217" s="16" t="inlineStr"/>
+      <c r="L217" s="16" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="16" t="inlineStr">
@@ -15943,15 +16383,17 @@
         </is>
       </c>
       <c r="G218" s="16" t="inlineStr"/>
-      <c r="H218" s="16" t="n">
+      <c r="H218" s="16" t="inlineStr"/>
+      <c r="I218" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I218" s="16" t="inlineStr">
+      <c r="J218" s="16" t="inlineStr"/>
+      <c r="K218" s="16" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J218" s="16" t="inlineStr"/>
+      <c r="L218" s="16" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="16" t="inlineStr">
@@ -15985,11 +16427,13 @@
         </is>
       </c>
       <c r="G219" s="16" t="inlineStr"/>
-      <c r="H219" s="16" t="n">
+      <c r="H219" s="16" t="inlineStr"/>
+      <c r="I219" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I219" s="16" t="inlineStr"/>
       <c r="J219" s="16" t="inlineStr"/>
+      <c r="K219" s="16" t="inlineStr"/>
+      <c r="L219" s="16" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="16" t="inlineStr">
@@ -16023,11 +16467,13 @@
         </is>
       </c>
       <c r="G220" s="16" t="inlineStr"/>
-      <c r="H220" s="16" t="n">
+      <c r="H220" s="16" t="inlineStr"/>
+      <c r="I220" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I220" s="16" t="inlineStr"/>
-      <c r="J220" s="16" t="inlineStr">
+      <c r="J220" s="16" t="inlineStr"/>
+      <c r="K220" s="16" t="inlineStr"/>
+      <c r="L220" s="16" t="inlineStr">
         <is>
           <t>지운다 100%</t>
         </is>
@@ -16067,11 +16513,13 @@
       <c r="G221" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="H221" s="16" t="n">
+      <c r="H221" s="16" t="inlineStr"/>
+      <c r="I221" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="I221" s="16" t="inlineStr"/>
       <c r="J221" s="16" t="inlineStr"/>
+      <c r="K221" s="16" t="inlineStr"/>
+      <c r="L221" s="16" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="16" t="inlineStr">
@@ -16106,12 +16554,14 @@
       </c>
       <c r="G222" s="16" t="inlineStr"/>
       <c r="H222" s="16" t="inlineStr"/>
-      <c r="I222" s="16" t="inlineStr">
+      <c r="I222" s="16" t="inlineStr"/>
+      <c r="J222" s="16" t="inlineStr"/>
+      <c r="K222" s="16" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J222" s="16" t="inlineStr"/>
+      <c r="L222" s="16" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="8" t="inlineStr">
@@ -16145,11 +16595,13 @@
         </is>
       </c>
       <c r="G223" s="8" t="inlineStr"/>
-      <c r="H223" s="8" t="n">
+      <c r="H223" s="8" t="inlineStr"/>
+      <c r="I223" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I223" s="8" t="inlineStr"/>
-      <c r="J223" s="8" t="inlineStr">
+      <c r="J223" s="8" t="inlineStr"/>
+      <c r="K223" s="8" t="inlineStr"/>
+      <c r="L223" s="8" t="inlineStr">
         <is>
           <t>지팡이 내리치기 100%</t>
         </is>
@@ -16189,11 +16641,13 @@
       <c r="G224" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H224" s="8" t="n">
+      <c r="H224" s="8" t="inlineStr"/>
+      <c r="I224" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I224" s="8" t="inlineStr"/>
       <c r="J224" s="8" t="inlineStr"/>
+      <c r="K224" s="8" t="inlineStr"/>
+      <c r="L224" s="8" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="8" t="inlineStr">
@@ -16227,11 +16681,13 @@
         </is>
       </c>
       <c r="G225" s="8" t="inlineStr"/>
-      <c r="H225" s="8" t="n">
+      <c r="H225" s="8" t="inlineStr"/>
+      <c r="I225" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I225" s="8" t="inlineStr"/>
       <c r="J225" s="8" t="inlineStr"/>
+      <c r="K225" s="8" t="inlineStr"/>
+      <c r="L225" s="8" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="8" t="inlineStr">
@@ -16267,11 +16723,13 @@
       <c r="G226" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H226" s="8" t="n">
+      <c r="H226" s="8" t="inlineStr"/>
+      <c r="I226" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I226" s="8" t="inlineStr"/>
       <c r="J226" s="8" t="inlineStr"/>
+      <c r="K226" s="8" t="inlineStr"/>
+      <c r="L226" s="8" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="8" t="inlineStr">
@@ -16306,12 +16764,14 @@
       </c>
       <c r="G227" s="8" t="inlineStr"/>
       <c r="H227" s="8" t="inlineStr"/>
-      <c r="I227" s="8" t="inlineStr">
+      <c r="I227" s="8" t="inlineStr"/>
+      <c r="J227" s="8" t="inlineStr"/>
+      <c r="K227" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J227" s="8" t="inlineStr"/>
+      <c r="L227" s="8" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="8" t="inlineStr">
@@ -16345,11 +16805,13 @@
         </is>
       </c>
       <c r="G228" s="8" t="inlineStr"/>
-      <c r="H228" s="8" t="n">
+      <c r="H228" s="8" t="inlineStr"/>
+      <c r="I228" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I228" s="8" t="inlineStr"/>
       <c r="J228" s="8" t="inlineStr"/>
+      <c r="K228" s="8" t="inlineStr"/>
+      <c r="L228" s="8" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="8" t="inlineStr">
@@ -16385,11 +16847,13 @@
       <c r="G229" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H229" s="8" t="n">
+      <c r="H229" s="8" t="inlineStr"/>
+      <c r="I229" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I229" s="8" t="inlineStr"/>
-      <c r="J229" s="8" t="inlineStr">
+      <c r="J229" s="8" t="inlineStr"/>
+      <c r="K229" s="8" t="inlineStr"/>
+      <c r="L229" s="8" t="inlineStr">
         <is>
           <t>어긋난 화음 50%</t>
         </is>
@@ -16427,15 +16891,17 @@
         </is>
       </c>
       <c r="G230" s="8" t="inlineStr"/>
-      <c r="H230" s="8" t="n">
+      <c r="H230" s="8" t="inlineStr"/>
+      <c r="I230" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I230" s="8" t="inlineStr">
+      <c r="J230" s="8" t="inlineStr"/>
+      <c r="K230" s="8" t="inlineStr">
         <is>
           <t>숨김</t>
         </is>
       </c>
-      <c r="J230" s="8" t="inlineStr"/>
+      <c r="L230" s="8" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="8" t="inlineStr">
@@ -16471,11 +16937,13 @@
       <c r="G231" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H231" s="8" t="n">
+      <c r="H231" s="8" t="inlineStr"/>
+      <c r="I231" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I231" s="8" t="inlineStr"/>
       <c r="J231" s="8" t="inlineStr"/>
+      <c r="K231" s="8" t="inlineStr"/>
+      <c r="L231" s="8" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="8" t="inlineStr">
@@ -16510,12 +16978,14 @@
       </c>
       <c r="G232" s="8" t="inlineStr"/>
       <c r="H232" s="8" t="inlineStr"/>
-      <c r="I232" s="8" t="inlineStr">
+      <c r="I232" s="8" t="inlineStr"/>
+      <c r="J232" s="8" t="inlineStr"/>
+      <c r="K232" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J232" s="8" t="inlineStr"/>
+      <c r="L232" s="8" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="8" t="inlineStr">
@@ -16549,11 +17019,13 @@
         </is>
       </c>
       <c r="G233" s="8" t="inlineStr"/>
-      <c r="H233" s="8" t="n">
+      <c r="H233" s="8" t="inlineStr"/>
+      <c r="I233" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I233" s="8" t="inlineStr"/>
       <c r="J233" s="8" t="inlineStr"/>
+      <c r="K233" s="8" t="inlineStr"/>
+      <c r="L233" s="8" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="8" t="inlineStr">
@@ -16587,11 +17059,13 @@
         </is>
       </c>
       <c r="G234" s="8" t="inlineStr"/>
-      <c r="H234" s="8" t="n">
+      <c r="H234" s="8" t="inlineStr"/>
+      <c r="I234" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I234" s="8" t="inlineStr"/>
-      <c r="J234" s="8" t="inlineStr">
+      <c r="J234" s="8" t="inlineStr"/>
+      <c r="K234" s="8" t="inlineStr"/>
+      <c r="L234" s="8" t="inlineStr">
         <is>
           <t>확 타오르기 100%</t>
         </is>
@@ -16631,11 +17105,13 @@
       <c r="G235" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H235" s="8" t="n">
+      <c r="H235" s="8" t="inlineStr"/>
+      <c r="I235" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I235" s="8" t="inlineStr"/>
       <c r="J235" s="8" t="inlineStr"/>
+      <c r="K235" s="8" t="inlineStr"/>
+      <c r="L235" s="8" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="8" t="inlineStr">
@@ -16671,11 +17147,13 @@
       <c r="G236" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H236" s="8" t="n">
+      <c r="H236" s="8" t="inlineStr"/>
+      <c r="I236" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I236" s="8" t="inlineStr"/>
       <c r="J236" s="8" t="inlineStr"/>
+      <c r="K236" s="8" t="inlineStr"/>
+      <c r="L236" s="8" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="8" t="inlineStr">
@@ -16710,12 +17188,14 @@
       </c>
       <c r="G237" s="8" t="inlineStr"/>
       <c r="H237" s="8" t="inlineStr"/>
-      <c r="I237" s="8" t="inlineStr">
+      <c r="I237" s="8" t="inlineStr"/>
+      <c r="J237" s="8" t="inlineStr"/>
+      <c r="K237" s="8" t="inlineStr">
         <is>
           <t>계몽 17~19단계</t>
         </is>
       </c>
-      <c r="J237" s="8" t="inlineStr"/>
+      <c r="L237" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -7604,7 +7604,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>방어 10</t>
+          <t>방어 15</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>방어 15</t>
+          <t>방어 20</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>휴식</t>
+          <t>자해 15</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -4716,12 +4716,12 @@
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>기습 (5턴부터)</t>
+          <t>맹독니 (5턴부터)</t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t>거미줄 → 기습 (100%)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>사냥 (5턴부터)</t>
+          <t>상처 보듬기 (1턴부터)</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>으르렁 → 사냥 (50%)</t>
+          <t>울부짖기 → 물어뜯기 (50%)</t>
         </is>
       </c>
       <c r="M7" s="8" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>덩굴 채찍 (5턴부터)</t>
+          <t>덩굴 채찍 (3턴부터)</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>가시 세우기 → 덩굴 채찍 (100%)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>물기</t>
+          <t>독니</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>피해 5</t>
+          <t>독 3 · 피해 2</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -7885,9 +7885,11 @@
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr"/>
-      <c r="H16" s="8" t="inlineStr"/>
+      <c r="H16" s="8" t="n">
+        <v>5</v>
+      </c>
       <c r="I16" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="8" t="inlineStr"/>
       <c r="K16" s="8" t="inlineStr"/>
@@ -7927,15 +7929,11 @@
       <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="8" t="inlineStr"/>
       <c r="I17" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="8" t="inlineStr"/>
       <c r="K17" s="8" t="inlineStr"/>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t>기습 100%</t>
-        </is>
-      </c>
+      <c r="L17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -7955,22 +7953,20 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>기습</t>
+          <t>웅크리기</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>피해 10</t>
+          <t>방어 10</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>5</v>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr"/>
       <c r="H18" s="8" t="inlineStr"/>
       <c r="I18" s="8" t="n">
         <v>2</v>
@@ -7997,12 +7993,12 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>다리를 곧추세운다</t>
+          <t>맹독니</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>독 6 · 피해 2</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -8011,11 +8007,11 @@
         </is>
       </c>
       <c r="G19" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" s="8" t="inlineStr"/>
       <c r="I19" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" s="8" t="inlineStr"/>
       <c r="K19" s="8" t="inlineStr"/>
@@ -8086,18 +8082,18 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>피해 7</t>
+          <t>피해 3 ×2타</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr"/>
       <c r="H21" s="8" t="inlineStr"/>
       <c r="I21" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="8" t="inlineStr"/>
       <c r="K21" s="8" t="inlineStr"/>
@@ -8121,12 +8117,12 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>으르렁</t>
+          <t>울부짖기</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>힘 3</t>
+          <t>힘 2</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -8143,7 +8139,7 @@
       <c r="K22" s="8" t="inlineStr"/>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>사냥 50%</t>
+          <t>물어뜯기 50%</t>
         </is>
       </c>
     </row>
@@ -8165,12 +8161,12 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>사냥</t>
+          <t>상처 보듬기</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>피해 11 · 힘 2</t>
+          <t>휴식</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -8179,11 +8175,11 @@
         </is>
       </c>
       <c r="G23" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H23" s="8" t="inlineStr"/>
       <c r="I23" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="8" t="inlineStr"/>
       <c r="K23" s="8" t="inlineStr"/>
@@ -8207,12 +8203,12 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>송곳니를 드러낸다</t>
+          <t>허기</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>피해 5 · 힘 5</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -8221,11 +8217,11 @@
         </is>
       </c>
       <c r="G24" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H24" s="8" t="inlineStr"/>
       <c r="I24" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J24" s="8" t="inlineStr"/>
       <c r="K24" s="8" t="inlineStr"/>
@@ -8291,12 +8287,12 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>할퀴기</t>
+          <t>가시 뿜기</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>피해 5</t>
+          <t>피해 1 ×5타</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -8331,12 +8327,12 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>가시 세우기</t>
+          <t>줄기 방패</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>방어 8 · 혼란 1</t>
+          <t>방어 6</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
@@ -8351,11 +8347,7 @@
       </c>
       <c r="J27" s="8" t="inlineStr"/>
       <c r="K27" s="8" t="inlineStr"/>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t>덩굴 채찍 100%</t>
-        </is>
-      </c>
+      <c r="L27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -8380,20 +8372,20 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>피해 11</t>
+          <t>피해 11 · 혼란 2</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="G28" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H28" s="8" t="inlineStr"/>
       <c r="I28" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="8" t="inlineStr"/>
       <c r="K28" s="8" t="inlineStr"/>
@@ -8417,7 +8409,7 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>가시를 세운다</t>
+          <t>급성장</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
@@ -8431,11 +8423,11 @@
         </is>
       </c>
       <c r="G29" s="8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H29" s="8" t="inlineStr"/>
       <c r="I29" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J29" s="8" t="inlineStr"/>
       <c r="K29" s="8" t="inlineStr"/>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -14,11 +14,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유물" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적행동" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="무기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="만남" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지도·보상" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="경제" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계몽" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상태이상" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="무기" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="만남" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지도·보상" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="경제" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="계몽" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -559,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.16</t>
+          <t>v1.17</t>
         </is>
       </c>
     </row>
@@ -948,6 +949,993 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>만남 이벤트 11개</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>테마에 맞는 이벤트만 등장한다. 계몽 15단계부터 대가가 1.5배로 가혹해진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>이벤트 id</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>등장 테마</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>선택지</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>효과</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>결과 대사</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>ash_crone</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>숯쟁이 난쟁이</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>forest, cabin, mist</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>🧪 검은 물약을 마신다</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>HP 15 회복</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>회복 15</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>쓰디쓴 물약이 상처를 봉한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr"/>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>🩸 피의 거래</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>HP -8, 무작위 유물 획득</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>HP 감소 8 · 유물 획득</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>난쟁이가 웃으며 앞치마 주머니에서 무언가를 꺼내 쥐여 준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr"/>
+      <c r="B6" s="8" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>🚪 조용히 지나친다</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>난쟁이의 시선이 등 뒤에 오래 남는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>signpost</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>부러진 이정표</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>forest, stream</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>🪓 밑동을 파헤친다</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>무작위 족보 변형 획득</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>gainVariant</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>기름먹인 천에 싸인 낡은 두루마리 조각이 나왔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr"/>
+      <c r="B8" s="8" t="inlineStr"/>
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>🙏 무사한 여행을 빈다</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>최대 HP +4</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>maxHp 4</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>몸이 조금 단단해진 기분이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr"/>
+      <c r="B9" s="8" t="inlineStr"/>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>🚶 갈 길을 간다</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>바람이 이정표를 삐걱, 흔들었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>altar</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>이끼 낀 제단</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>cabin, grave, church</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>🙇 무릎 꿇고 기도한다</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>HP 8 회복</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>회복 8</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>촛불이 한 번 크게 흔들리고, 통증이 가라앉았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr"/>
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>🎲 제물을 훔친다</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>무작위 주사위 획득 (교체)</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>gainDie</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>제단 위의 주사위가 손안에서 차갑게 식어 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>🚶 떠난다</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>돌아보지 않는 편이 좋을 것 같았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>stream_chest</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>가라앉은 상자</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>stream, swamp</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>💰 물에 들어가 건진다</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>🪙 +40, HP -6</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>HP 감소 6 · gainCoins 40</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>차가운 물이 뼛속까지 스몄지만, 동전은 진짜였다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr"/>
+      <c r="B14" s="8" t="inlineStr"/>
+      <c r="C14" s="8" t="inlineStr"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>🎣 나뭇가지로 끌어본다</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>🪙 +15</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>gainCoins 15</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>상자가 반쯤 열리며 동전 몇 닢이 흘러나왔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr"/>
+      <c r="B15" s="8" t="inlineStr"/>
+      <c r="C15" s="8" t="inlineStr"/>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>🚶 지나친다</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>물속의 상자는 다음 길손을 기다린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>swamp_light</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>늪 위의 불빛</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>swamp</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>🕯️ 따라간다</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>🪙 +35, HP -8</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>HP 감소 8 · gainCoins 35</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>불빛이 꺼진 자리에 물에 젖은 돈주머니가 있었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr"/>
+      <c r="B17" s="8" t="inlineStr"/>
+      <c r="C17" s="8" t="inlineStr"/>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>🙏 시선을 피하고 걷는다</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>HP 6 회복</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>회복 6</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>불빛이 아쉬운 듯 멀어졌다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr"/>
+      <c r="B18" s="8" t="inlineStr"/>
+      <c r="C18" s="8" t="inlineStr"/>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>🚶 서둘러 벗어난다</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>등 뒤에서 물이 크게 출렁였다. 돌아보지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>voice_in_mist</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>안개 속 목소리</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>mist, dream</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>👂 목소리를 따라간다</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>무작위 족보 변형, HP -7</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>HP 감소 7 · gainVariant</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>목소리는 없었다. 하지만 나무 밑동에 두루마리가 놓여 있었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr"/>
+      <c r="B20" s="8" t="inlineStr"/>
+      <c r="C20" s="8" t="inlineStr"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>🧣 두건을 여미고 무시한다</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>최대 HP +4</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>maxHp 4</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>제 발로 걸어 나온 자신이 조금 단단해진 것 같다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr"/>
+      <c r="B21" s="8" t="inlineStr"/>
+      <c r="C21" s="8" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>🏃 반대쪽으로 달린다</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>목소리가 등 뒤에서 혀를 찼다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>open_grave</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>열린 관</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>grave, hill</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>🪦 관 속을 뒤진다</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>무작위 유물, HP -10</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>HP 감소 10 · 유물 획득</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>차가운 손이 스친 것 같았지만… 손에는 무언가 쥐어져 있었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr"/>
+      <c r="B23" s="8" t="inlineStr"/>
+      <c r="C23" s="8" t="inlineStr"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>🙏 뚜껑을 덮고 기도한다</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>HP 10 회복</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>회복 10</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>바람이 잦아들었다. 고맙다는 인사처럼.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr"/>
+      <c r="B24" s="8" t="inlineStr"/>
+      <c r="C24" s="8" t="inlineStr"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>🚶 못 본 척 지나간다</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>등 뒤에서 나무 삐걱이는 소리가 들렸다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>sweet_dream</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>달콤한 꿈</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>dream</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>😴 잠깐만 눕는다</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>HP 18 회복, 🪙 -20</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>loseCoins 20 · 회복 18</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>달게 잤다. 주머니가 가벼워진 건 눈뜨고 알았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr"/>
+      <c r="B26" s="8" t="inlineStr"/>
+      <c r="C26" s="8" t="inlineStr"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>🤏 이불만 챙긴다</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>최대 HP +5</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>maxHp 5</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>꿈의 천은 뜻밖에 질겼다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr"/>
+      <c r="B27" s="8" t="inlineStr"/>
+      <c r="C27" s="8" t="inlineStr"/>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>🚶 침대를 지나친다</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>베개가 아쉬운 듯 부풀었다 가라앉았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>whispering_stone</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>속삭이는 비석</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>hill</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>👂 귀를 댄다</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>정예 유물, HP -15</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>HP 감소 15 · gainRelicElite</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>코피가 흘렀다. 하지만 이제, 알고 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr"/>
+      <c r="B29" s="8" t="inlineStr"/>
+      <c r="C29" s="8" t="inlineStr"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>🪙 동전을 바친다</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>🪙 -25, HP 12 회복</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>loseCoins 25 · 회복 12</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>비석이 만족한 듯 조용해졌다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr"/>
+      <c r="B30" s="8" t="inlineStr"/>
+      <c r="C30" s="8" t="inlineStr"/>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>🏃 언덕을 뛰어 내려간다</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>속삭임이 한동안 귓가를 따라왔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>confession</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>텅 빈 고해실</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>church</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>🪙 헌금함에 돈을 넣는다</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>🪙 -30, HP 20 회복</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>loseCoins 30 · 회복 20</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>창살 너머의 숨소리가 평온해졌다. 상처도 함께.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr"/>
+      <c r="B32" s="8" t="inlineStr"/>
+      <c r="C32" s="8" t="inlineStr"/>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>🕯️ 헌금함을 턴다</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>🪙 +30, 최대 HP -4</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>gainCoins 30 · maxHpLoss 4</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>동전은 차가웠다. 숨소리가 멎었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr"/>
+      <c r="C33" s="8" t="inlineStr"/>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>🚶 조용히 나온다</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>문이 저절로, 아주 천천히 닫혔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>phantom_self</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>낯익은 환영</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>stream, mist, dream</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>🤝 손을 뻗는다</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>HP 12 회복</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>회복 12</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>손끝이 닿자 환영은 온기만 남기고 흩어졌다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr"/>
+      <c r="B35" s="8" t="inlineStr"/>
+      <c r="C35" s="8" t="inlineStr"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>👁 눈을 마주본다</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>HP -6, 최대 HP +4</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>HP 감소 6 · maxHp 4</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>나의 눈 속에서 더 깊은 숲을 보았다. 조금 단단해졌다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr"/>
+      <c r="B36" s="8" t="inlineStr"/>
+      <c r="C36" s="8" t="inlineStr"/>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>🚶 고개를 젓고 지나친다</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr"/>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>환영은 따라오지 않았다. 발소리만 오래 따라왔다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1235,7 +2223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1419,7 +2407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8538,7 +9526,7 @@
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>힘 3 · 혼란 1</t>
+          <t>힘 3 · 출혈 2칸</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
@@ -9416,7 +10404,7 @@
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
-          <t>혼란 2</t>
+          <t>기절 1칸</t>
         </is>
       </c>
       <c r="F53" s="16" t="inlineStr">
@@ -10550,7 +11538,7 @@
       </c>
       <c r="E80" s="16" t="inlineStr">
         <is>
-          <t>혼란 1 · 힘 2</t>
+          <t>저주 1칸 · 힘 2</t>
         </is>
       </c>
       <c r="F80" s="16" t="inlineStr">
@@ -11434,7 +12422,7 @@
       </c>
       <c r="E101" s="16" t="inlineStr">
         <is>
-          <t>방어 12</t>
+          <t>방어 12 · 포박 1칸</t>
         </is>
       </c>
       <c r="F101" s="16" t="inlineStr">
@@ -12598,7 +13586,7 @@
       </c>
       <c r="E128" s="16" t="inlineStr">
         <is>
-          <t>피해 11 · 혼란 1</t>
+          <t>피해 11 · 혼란 2칸</t>
         </is>
       </c>
       <c r="F128" s="16" t="inlineStr">
@@ -12724,7 +13712,7 @@
       </c>
       <c r="E131" s="16" t="inlineStr">
         <is>
-          <t>혼란 2 · 힘 2</t>
+          <t>혼란 2칸 · 힘 2</t>
         </is>
       </c>
       <c r="F131" s="16" t="inlineStr">
@@ -13608,7 +14596,7 @@
       </c>
       <c r="E152" s="16" t="inlineStr">
         <is>
-          <t>혼란 1 · 회복 10</t>
+          <t>독 2칸 · 회복 10</t>
         </is>
       </c>
       <c r="F152" s="16" t="inlineStr">
@@ -14746,7 +15734,7 @@
       </c>
       <c r="E179" s="16" t="inlineStr">
         <is>
-          <t>혼란 2 · 회복 12</t>
+          <t>봉인 1칸 · 회복 12</t>
         </is>
       </c>
       <c r="F179" s="16" t="inlineStr">
@@ -15842,7 +16830,7 @@
       </c>
       <c r="E205" s="16" t="inlineStr">
         <is>
-          <t>혼란 2 · 방어 12</t>
+          <t>잠식 1칸 · 방어 12</t>
         </is>
       </c>
       <c r="F205" s="16" t="inlineStr">
@@ -16856,7 +17844,7 @@
       </c>
       <c r="E229" s="16" t="inlineStr">
         <is>
-          <t>혼란 1 · 힘 3</t>
+          <t>축복 1칸 · 힘 3</t>
         </is>
       </c>
       <c r="F229" s="16" t="inlineStr">
@@ -17305,6 +18293,533 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>주사위 상태이상 13종</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>주사위 한 칸에 하나씩 붙는다. 새로 걸면 빈 칸을 먼저 채우고, 다 차면 아무 칸이나 덮는다. 지속 턴이 영구면 정화하거나 조건을 만족해야 풀린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>수치</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>지속 턴</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>색</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>bleed</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>쓰면 눈금만큼 피해</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>영구</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>#ff5a4a</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>이 주사위를 족보에 쓰면 눈금만큼 피해를 받는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>poison</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>독</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>쓰면 눈금만큼 피해</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>영구</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>#b8e04a</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>이 주사위를 족보에 쓰면 눈금만큼 피해를 받는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>bind</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>포박</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>다시 못 굴림</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>영구</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>#7fbf8a</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>이 주사위는 다시 굴릴 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>stun</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>기절</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>눈금 0으로 계산</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>영구</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>#dfe6ee</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>족보에는 들어가지만 눈금이 0으로 계산된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>curse</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>저주</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>수치 이하만 나옴</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>영구</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>#c78cff</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>이 주사위는 수치 이하의 눈만 나온다</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>blessing</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>축복</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>수치 이상만 나옴</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>영구</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>#f3ecdd</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>이 주사위는 수치 이상의 눈만 나온다</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>confuse</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>혼란</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>눈 가림</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>영구</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>#c68cff</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>눈이 보이지 않는다 (족보에는 그대로 들어간다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>seal</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>봉인</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>한 번 굴리기 전 값 없음</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>영구</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>#8fa8e0</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>한 번 다시 굴리기 전에는 값이 없다 — 족보에도 안 들어간다</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>rot</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>부패</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>턴 지나면 폭발</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>#d98cc0</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>턴이 다 차면 터져 수치만큼 피해. 그 전에 족보에 쓰면 해제된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>결속</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>같이 굴러감</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>영구</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>#a8c2d8</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>결속된 주사위끼리 항상 같이 굴러간다</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>numb</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>마비</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>리롤 더 소모</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>영구</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>#8fd4ff</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>이 주사위를 다시 굴리면 리롤을 수치만큼 쓴다</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>plunder</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>약탈</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>쓰면 눈금만큼 코인</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>영구</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>#d9a05a</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>이 주사위를 족보에 쓰면 눈금만큼 코인을 뺏긴다</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>devour</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>잠식</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>양옆으로 번짐</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>영구</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>#9fd8f0</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>쓰지 않으면 양옆으로 번진다. 다 잠식되면 공허의 부름만 남는다</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17526,991 +19041,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>만남 이벤트 11개</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>테마에 맞는 이벤트만 등장한다. 계몽 15단계부터 대가가 1.5배로 가혹해진다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>이벤트 id</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>NPC</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>등장 테마</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>선택지</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>요약</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>효과</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>결과 대사</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>ash_crone</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>숯쟁이 난쟁이</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>forest, cabin, mist</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>🧪 검은 물약을 마신다</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>HP 15 회복</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>회복 15</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>쓰디쓴 물약이 상처를 봉한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr"/>
-      <c r="B5" s="8" t="inlineStr"/>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>🩸 피의 거래</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>HP -8, 무작위 유물 획득</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>HP 감소 8 · 유물 획득</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>난쟁이가 웃으며 앞치마 주머니에서 무언가를 꺼내 쥐여 준다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr"/>
-      <c r="B6" s="8" t="inlineStr"/>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>🚪 조용히 지나친다</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>난쟁이의 시선이 등 뒤에 오래 남는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>signpost</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>부러진 이정표</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>forest, stream</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>🪓 밑동을 파헤친다</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>무작위 족보 변형 획득</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>gainVariant</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>기름먹인 천에 싸인 낡은 두루마리 조각이 나왔다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr"/>
-      <c r="B8" s="8" t="inlineStr"/>
-      <c r="C8" s="8" t="inlineStr"/>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>🙏 무사한 여행을 빈다</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>최대 HP +4</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>maxHp 4</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>몸이 조금 단단해진 기분이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr"/>
-      <c r="B9" s="8" t="inlineStr"/>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>🚶 갈 길을 간다</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>바람이 이정표를 삐걱, 흔들었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>altar</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>이끼 낀 제단</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>cabin, grave, church</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>🙇 무릎 꿇고 기도한다</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>HP 8 회복</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>회복 8</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>촛불이 한 번 크게 흔들리고, 통증이 가라앉았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr"/>
-      <c r="B11" s="8" t="inlineStr"/>
-      <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>🎲 제물을 훔친다</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>무작위 주사위 획득 (교체)</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>gainDie</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>제단 위의 주사위가 손안에서 차갑게 식어 있다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr"/>
-      <c r="B12" s="8" t="inlineStr"/>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>🚶 떠난다</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>돌아보지 않는 편이 좋을 것 같았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>stream_chest</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>가라앉은 상자</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>stream, swamp</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>💰 물에 들어가 건진다</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>🪙 +40, HP -6</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>HP 감소 6 · gainCoins 40</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>차가운 물이 뼛속까지 스몄지만, 동전은 진짜였다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr"/>
-      <c r="B14" s="8" t="inlineStr"/>
-      <c r="C14" s="8" t="inlineStr"/>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>🎣 나뭇가지로 끌어본다</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>🪙 +15</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>gainCoins 15</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>상자가 반쯤 열리며 동전 몇 닢이 흘러나왔다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr"/>
-      <c r="B15" s="8" t="inlineStr"/>
-      <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>🚶 지나친다</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>물속의 상자는 다음 길손을 기다린다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>swamp_light</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>늪 위의 불빛</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>swamp</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>🕯️ 따라간다</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>🪙 +35, HP -8</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>HP 감소 8 · gainCoins 35</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>불빛이 꺼진 자리에 물에 젖은 돈주머니가 있었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr"/>
-      <c r="B17" s="8" t="inlineStr"/>
-      <c r="C17" s="8" t="inlineStr"/>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>🙏 시선을 피하고 걷는다</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>HP 6 회복</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>회복 6</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>불빛이 아쉬운 듯 멀어졌다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr"/>
-      <c r="B18" s="8" t="inlineStr"/>
-      <c r="C18" s="8" t="inlineStr"/>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>🚶 서둘러 벗어난다</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>등 뒤에서 물이 크게 출렁였다. 돌아보지 않았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>voice_in_mist</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>안개 속 목소리</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>mist, dream</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>👂 목소리를 따라간다</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>무작위 족보 변형, HP -7</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>HP 감소 7 · gainVariant</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>목소리는 없었다. 하지만 나무 밑동에 두루마리가 놓여 있었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr"/>
-      <c r="B20" s="8" t="inlineStr"/>
-      <c r="C20" s="8" t="inlineStr"/>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>🧣 두건을 여미고 무시한다</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>최대 HP +4</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>maxHp 4</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>제 발로 걸어 나온 자신이 조금 단단해진 것 같다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr"/>
-      <c r="B21" s="8" t="inlineStr"/>
-      <c r="C21" s="8" t="inlineStr"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>🏃 반대쪽으로 달린다</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>목소리가 등 뒤에서 혀를 찼다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>open_grave</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>열린 관</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>grave, hill</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>🪦 관 속을 뒤진다</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>무작위 유물, HP -10</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>HP 감소 10 · 유물 획득</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>차가운 손이 스친 것 같았지만… 손에는 무언가 쥐어져 있었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr"/>
-      <c r="B23" s="8" t="inlineStr"/>
-      <c r="C23" s="8" t="inlineStr"/>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>🙏 뚜껑을 덮고 기도한다</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>HP 10 회복</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>회복 10</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>바람이 잦아들었다. 고맙다는 인사처럼.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr"/>
-      <c r="B24" s="8" t="inlineStr"/>
-      <c r="C24" s="8" t="inlineStr"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>🚶 못 본 척 지나간다</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>등 뒤에서 나무 삐걱이는 소리가 들렸다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>sweet_dream</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>달콤한 꿈</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>dream</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>😴 잠깐만 눕는다</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>HP 18 회복, 🪙 -20</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>loseCoins 20 · 회복 18</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>달게 잤다. 주머니가 가벼워진 건 눈뜨고 알았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr"/>
-      <c r="B26" s="8" t="inlineStr"/>
-      <c r="C26" s="8" t="inlineStr"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>🤏 이불만 챙긴다</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>최대 HP +5</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>maxHp 5</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>꿈의 천은 뜻밖에 질겼다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr"/>
-      <c r="B27" s="8" t="inlineStr"/>
-      <c r="C27" s="8" t="inlineStr"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>🚶 침대를 지나친다</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr"/>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>베개가 아쉬운 듯 부풀었다 가라앉았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>whispering_stone</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>속삭이는 비석</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>hill</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>👂 귀를 댄다</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>정예 유물, HP -15</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>HP 감소 15 · gainRelicElite</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>코피가 흘렀다. 하지만 이제, 알고 있다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr"/>
-      <c r="B29" s="8" t="inlineStr"/>
-      <c r="C29" s="8" t="inlineStr"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>🪙 동전을 바친다</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>🪙 -25, HP 12 회복</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>loseCoins 25 · 회복 12</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>비석이 만족한 듯 조용해졌다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr"/>
-      <c r="B30" s="8" t="inlineStr"/>
-      <c r="C30" s="8" t="inlineStr"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>🏃 언덕을 뛰어 내려간다</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr"/>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>속삭임이 한동안 귓가를 따라왔다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>confession</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>텅 빈 고해실</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>church</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>🪙 헌금함에 돈을 넣는다</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>🪙 -30, HP 20 회복</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>loseCoins 30 · 회복 20</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>창살 너머의 숨소리가 평온해졌다. 상처도 함께.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr"/>
-      <c r="B32" s="8" t="inlineStr"/>
-      <c r="C32" s="8" t="inlineStr"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>🕯️ 헌금함을 턴다</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>🪙 +30, 최대 HP -4</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>gainCoins 30 · maxHpLoss 4</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>동전은 차가웠다. 숨소리가 멎었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr"/>
-      <c r="B33" s="8" t="inlineStr"/>
-      <c r="C33" s="8" t="inlineStr"/>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>🚶 조용히 나온다</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr"/>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>문이 저절로, 아주 천천히 닫혔다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>phantom_self</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>낯익은 환영</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>stream, mist, dream</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>🤝 손을 뻗는다</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>HP 12 회복</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>회복 12</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>손끝이 닿자 환영은 온기만 남기고 흩어졌다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr"/>
-      <c r="B35" s="8" t="inlineStr"/>
-      <c r="C35" s="8" t="inlineStr"/>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>👁 눈을 마주본다</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>HP -6, 최대 HP +4</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>HP 감소 6 · maxHp 4</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>나의 눈 속에서 더 깊은 숲을 보았다. 조금 단단해졌다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr"/>
-      <c r="B36" s="8" t="inlineStr"/>
-      <c r="C36" s="8" t="inlineStr"/>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>🚶 고개를 젓고 지나친다</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr"/>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>환영은 따라오지 않았다. 발소리만 오래 따라왔다.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.17</t>
+          <t>v1.18</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>막 → 테마 → 난이도 순. 발동 조건 다섯 가지 — 가중치는 뽑힐 확률(0이면 추첨에서 빠지고 연계로만 나온다), 해금 턴은 "이 턴부터", 락 턴은 "이 턴이 되면 더 안 씀", 쿨다운은 "쓰고 나서 몇 턴 쉰다"(0=제한 없음, 2면 한 칸 걸러 나온다), 연계는 "앞 행동 다음에 확률로 확정".</t>
+          <t>상태이상 부여는 [종류 세기 N칸] 으로 읽는다 — 세기를 안 적으면 상태이상 시트의 기본값을 쓴다. 막 → 테마 → 난이도 순. 발동 조건 다섯 가지 — 가중치는 뽑힐 확률(0이면 추첨에서 빠지고 연계로만 나온다), 해금 턴은 "이 턴부터", 락 턴은 "이 턴이 되면 더 안 씀", 쿨다운은 "쓰고 나서 몇 턴 쉰다"(0=제한 없음, 2면 한 칸 걸러 나온다), 연계는 "앞 행동 다음에 확률로 확정".</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>힘 3 · 출혈 2칸</t>
+          <t>힘 3 · 출혈 세기1 2칸</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="E80" s="16" t="inlineStr">
         <is>
-          <t>저주 1칸 · 힘 2</t>
+          <t>저주 세기3 1칸 · 힘 2</t>
         </is>
       </c>
       <c r="F80" s="16" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="E152" s="16" t="inlineStr">
         <is>
-          <t>독 2칸 · 회복 10</t>
+          <t>독 세기2 2칸 · 회복 10</t>
         </is>
       </c>
       <c r="F152" s="16" t="inlineStr">
@@ -16830,7 +16830,7 @@
       </c>
       <c r="E205" s="16" t="inlineStr">
         <is>
-          <t>잠식 1칸 · 방어 12</t>
+          <t>잠식 세기1 1칸 · 방어 12</t>
         </is>
       </c>
       <c r="F205" s="16" t="inlineStr">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="E229" s="16" t="inlineStr">
         <is>
-          <t>축복 1칸 · 힘 3</t>
+          <t>축복 세기4 1칸 · 힘 3</t>
         </is>
       </c>
       <c r="F229" s="16" t="inlineStr">

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.18</t>
+          <t>v1.19</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>상태이상 부여는 [종류 세기 N칸] 으로 읽는다 — 세기를 안 적으면 상태이상 시트의 기본값을 쓴다. 막 → 테마 → 난이도 순. 발동 조건 다섯 가지 — 가중치는 뽑힐 확률(0이면 추첨에서 빠지고 연계로만 나온다), 해금 턴은 "이 턴부터", 락 턴은 "이 턴이 되면 더 안 씀", 쿨다운은 "쓰고 나서 몇 턴 쉰다"(0=제한 없음, 2면 한 칸 걸러 나온다), 연계는 "앞 행동 다음에 확률로 확정".</t>
+          <t>상태이상 부여는 [종류 N칸] 으로 읽는다 — 세기는 저주·축복·부패·마비 넷만 쓰고 나머지는 눈금이나 규칙 그대로다. 막 → 테마 → 난이도 순. 발동 조건 다섯 가지 — 가중치는 뽑힐 확률(0이면 추첨에서 빠지고 연계로만 나온다), 해금 턴은 "이 턴부터", 락 턴은 "이 턴이 되면 더 안 씀", 쿨다운은 "쓰고 나서 몇 턴 쉰다"(0=제한 없음, 2면 한 칸 걸러 나온다), 연계는 "앞 행동 다음에 확률로 확정".</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>힘 3 · 출혈 세기1 2칸</t>
+          <t>힘 3 · 출혈 2칸</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="E152" s="16" t="inlineStr">
         <is>
-          <t>독 세기2 2칸 · 회복 10</t>
+          <t>독 2칸 · 회복 10</t>
         </is>
       </c>
       <c r="F152" s="16" t="inlineStr">
@@ -16830,7 +16830,7 @@
       </c>
       <c r="E205" s="16" t="inlineStr">
         <is>
-          <t>잠식 세기1 1칸 · 방어 12</t>
+          <t>잠식 1칸 · 방어 12</t>
         </is>
       </c>
       <c r="F205" s="16" t="inlineStr">
@@ -18377,8 +18377,10 @@
           <t>쓰면 눈금만큼 피해</t>
         </is>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>1</v>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
@@ -18390,9 +18392,9 @@
           <t>#ff5a4a</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>이 주사위를 족보에 쓰면 눈금만큼 피해를 받는다</t>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>이 주사위를 족보에 쓰면 눈금만큼 피해를 받는다 (세기 없음)</t>
         </is>
       </c>
     </row>
@@ -18412,8 +18414,10 @@
           <t>쓰면 눈금만큼 피해</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
-        <v>1</v>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
@@ -18425,9 +18429,9 @@
           <t>#b8e04a</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>이 주사위를 족보에 쓰면 눈금만큼 피해를 받는다</t>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>이 주사위를 족보에 쓰면 눈금만큼 피해를 받는다 (세기 없음)</t>
         </is>
       </c>
     </row>
@@ -18447,8 +18451,10 @@
           <t>다시 못 굴림</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>0</v>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -18482,8 +18488,10 @@
           <t>눈금 0으로 계산</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
-        <v>0</v>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
@@ -18587,8 +18595,10 @@
           <t>눈 가림</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n">
-        <v>0</v>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
@@ -18622,8 +18632,10 @@
           <t>한 번 굴리기 전 값 없음</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>0</v>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
@@ -18690,8 +18702,10 @@
           <t>같이 굴러감</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n">
-        <v>0</v>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
@@ -18760,8 +18774,10 @@
           <t>쓰면 눈금만큼 코인</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n">
-        <v>1</v>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
@@ -18773,9 +18789,9 @@
           <t>#d9a05a</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>이 주사위를 족보에 쓰면 눈금만큼 코인을 뺏긴다</t>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>이 주사위를 족보에 쓰면 눈금만큼 코인을 뺏긴다 (세기 없음)</t>
         </is>
       </c>
     </row>
@@ -18795,8 +18811,10 @@
           <t>양옆으로 번짐</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
-        <v>1</v>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.19</t>
+          <t>v1.20</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>상태이상 부여는 [종류 N칸] 으로 읽는다 — 세기는 저주·축복·부패·마비 넷만 쓰고 나머지는 눈금이나 규칙 그대로다. 막 → 테마 → 난이도 순. 발동 조건 다섯 가지 — 가중치는 뽑힐 확률(0이면 추첨에서 빠지고 연계로만 나온다), 해금 턴은 "이 턴부터", 락 턴은 "이 턴이 되면 더 안 씀", 쿨다운은 "쓰고 나서 몇 턴 쉰다"(0=제한 없음, 2면 한 칸 걸러 나온다), 연계는 "앞 행동 다음에 확률로 확정".</t>
+          <t>상태이상 부여는 [종류 N칸] 으로 읽는다 — 적 행동에서 세기를 정하는 건 부패뿐이고 나머지는 상태이상 시트의 값으로 고정이다. 막 → 테마 → 난이도 순. 발동 조건 다섯 가지 — 가중치는 뽑힐 확률(0이면 추첨에서 빠지고 연계로만 나온다), 해금 턴은 "이 턴부터", 락 턴은 "이 턴이 되면 더 안 씀", 쿨다운은 "쓰고 나서 몇 턴 쉰다"(0=제한 없음, 2면 한 칸 걸러 나온다), 연계는 "앞 행동 다음에 확률로 확정".</t>
         </is>
       </c>
     </row>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="E80" s="16" t="inlineStr">
         <is>
-          <t>저주 세기3 1칸 · 힘 2</t>
+          <t>저주 1칸 · 힘 2</t>
         </is>
       </c>
       <c r="F80" s="16" t="inlineStr">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="E229" s="16" t="inlineStr">
         <is>
-          <t>축복 세기4 1칸 · 힘 3</t>
+          <t>축복 1칸 · 힘 3</t>
         </is>
       </c>
       <c r="F229" s="16" t="inlineStr">
@@ -18320,7 +18320,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>주사위 한 칸에 하나씩 붙는다. 새로 걸면 빈 칸을 먼저 채우고, 다 차면 아무 칸이나 덮는다. 지속 턴이 영구면 정화하거나 조건을 만족해야 풀린다.</t>
+          <t>주사위 한 칸에 하나씩 붙는다. 새로 걸면 빈 칸을 먼저 채우고, 다 차면 아무 칸이나 덮는다. 지속 턴이 영구면 정화하거나 조건을 만족해야 풀린다. 적 행동에서 수치를 덮어쓸 수 있는 건 부패뿐이다.</t>
         </is>
       </c>
     </row>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.20</t>
+          <t>v1.21</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>상태이상 부여는 [종류 N칸] 으로 읽는다 — 적 행동에서 세기를 정하는 건 부패뿐이고 나머지는 상태이상 시트의 값으로 고정이다. 막 → 테마 → 난이도 순. 발동 조건 다섯 가지 — 가중치는 뽑힐 확률(0이면 추첨에서 빠지고 연계로만 나온다), 해금 턴은 "이 턴부터", 락 턴은 "이 턴이 되면 더 안 씀", 쿨다운은 "쓰고 나서 몇 턴 쉰다"(0=제한 없음, 2면 한 칸 걸러 나온다), 연계는 "앞 행동 다음에 확률로 확정".</t>
+          <t>상태이상 부여는 [종류 N칸] 으로 읽는다 — 적마다 다를 수 있는 건 부패의 폭발 피해뿐이고, 지속 턴을 포함한 나머지는 상태이상 시트의 값으로 고정이다. 막 → 테마 → 난이도 순. 발동 조건 다섯 가지 — 가중치는 뽑힐 확률(0이면 추첨에서 빠지고 연계로만 나온다), 해금 턴은 "이 턴부터", 락 턴은 "이 턴이 되면 더 안 씀", 쿨다운은 "쓰고 나서 몇 턴 쉰다"(0=제한 없음, 2면 한 칸 걸러 나온다), 연계는 "앞 행동 다음에 확률로 확정".</t>
         </is>
       </c>
     </row>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.21</t>
+          <t>v1.22</t>
         </is>
       </c>
     </row>
@@ -12212,7 +12212,7 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>방어 12</t>
+          <t>방어 12 · 결속 2칸</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
@@ -14344,7 +14344,7 @@
       </c>
       <c r="E146" s="10" t="inlineStr">
         <is>
-          <t>피해 15</t>
+          <t>피해 15 · 부패 폭발12 1칸</t>
         </is>
       </c>
       <c r="F146" s="10" t="inlineStr">
@@ -15394,7 +15394,7 @@
       </c>
       <c r="E171" s="10" t="inlineStr">
         <is>
-          <t>피해 13</t>
+          <t>피해 13 · 마비 1칸</t>
         </is>
       </c>
       <c r="F171" s="10" t="inlineStr">
@@ -17670,7 +17670,7 @@
       </c>
       <c r="E225" s="10" t="inlineStr">
         <is>
-          <t>힘 4</t>
+          <t>힘 4 · 약탈 1칸</t>
         </is>
       </c>
       <c r="F225" s="10" t="inlineStr">

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.22</t>
+          <t>v1.23</t>
         </is>
       </c>
     </row>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -9182,7 +9182,7 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>피해 10 · 출혈 2칸</t>
+          <t>피해 10</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -18466,19 +18466,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>영구</t>
-        </is>
+      <c r="E4" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
           <t>#ff5a4a</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>이 주사위를 족보에 쓰면 눈금만큼 피해를 받는다 (세기 없음)</t>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>이 주사위를 족보에 쓰면 눈금만큼 피해를 받는다</t>
         </is>
       </c>
     </row>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -9182,7 +9182,7 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>피해 10</t>
+          <t>피해 10 · 출혈 2칸</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>피해 7 ×3타 · 출혈 5칸</t>
+          <t>피해 5 ×3타 · 출혈 5칸</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
@@ -9285,7 +9285,11 @@
       <c r="I26" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="10" t="inlineStr"/>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>1 → unique1</t>
+        </is>
+      </c>
       <c r="K26" s="10" t="inlineStr"/>
       <c r="L26" s="10" t="inlineStr"/>
     </row>
@@ -18501,10 +18505,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>영구</t>
-        </is>
+      <c r="E5" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
@@ -18538,10 +18540,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>영구</t>
-        </is>
+      <c r="E6" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
@@ -18575,10 +18575,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>영구</t>
-        </is>
+      <c r="E7" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
@@ -18610,10 +18608,8 @@
       <c r="D8" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>영구</t>
-        </is>
+      <c r="E8" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
@@ -18645,10 +18641,8 @@
       <c r="D9" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>영구</t>
-        </is>
+      <c r="E9" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
@@ -18682,10 +18676,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>영구</t>
-        </is>
+      <c r="E10" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
@@ -18719,10 +18711,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>영구</t>
-        </is>
+      <c r="E11" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
@@ -18755,7 +18745,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
@@ -18789,10 +18779,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>영구</t>
-        </is>
+      <c r="E13" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
@@ -18824,10 +18812,8 @@
       <c r="D14" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>영구</t>
-        </is>
+      <c r="E14" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
@@ -18861,10 +18847,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>영구</t>
-        </is>
+      <c r="E15" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
@@ -18898,10 +18882,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>영구</t>
-        </is>
+      <c r="E16" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -8987,7 +8987,7 @@
       <c r="G19" s="8" t="inlineStr"/>
       <c r="H19" s="8" t="inlineStr"/>
       <c r="I19" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" s="8" t="inlineStr"/>
       <c r="K19" s="8" t="inlineStr"/>
@@ -9027,7 +9027,7 @@
       <c r="G20" s="8" t="inlineStr"/>
       <c r="H20" s="8" t="inlineStr"/>
       <c r="I20" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" s="8" t="inlineStr"/>
       <c r="K20" s="8" t="inlineStr"/>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>힘 3</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="E31" s="16" t="inlineStr">
         <is>
-          <t>힘 5</t>
+          <t>힘 3</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>방어 10</t>
+          <t>휴식</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.26</t>
+          <t>v1.27</t>
         </is>
       </c>
     </row>
@@ -10575,7 +10575,7 @@
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>20 → unique1</t>
+          <t>30 → unique1</t>
         </is>
       </c>
       <c r="K56" s="16" t="inlineStr"/>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>10 → unique1</t>
+          <t>20 → unique1</t>
         </is>
       </c>
       <c r="K58" s="16" t="inlineStr"/>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>25 → unique1</t>
+          <t>35 → unique1</t>
         </is>
       </c>
       <c r="K61" s="16" t="inlineStr"/>
@@ -10839,7 +10839,7 @@
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>15 → unique1</t>
+          <t>25 → unique1</t>
         </is>
       </c>
       <c r="K62" s="16" t="inlineStr"/>
@@ -10927,7 +10927,7 @@
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>30 → unique1</t>
+          <t>40 → unique1</t>
         </is>
       </c>
       <c r="K64" s="16" t="inlineStr"/>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>20 → unique1</t>
+          <t>30 → unique1</t>
         </is>
       </c>
       <c r="K65" s="16" t="inlineStr"/>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.27</t>
+          <t>v1.28</t>
         </is>
       </c>
     </row>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.28</t>
+          <t>v1.29</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>9종 · 변형 18개</t>
+          <t>9종 · 변형 21개</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>13종</t>
+          <t>19종</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>26개</t>
+          <t>32개</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3431,830 +3431,986 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
+          <t>chance</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>노페어</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>catch_breath</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>숨 고르기</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>언제나 성립 — 피해: 가장 높은 눈 하나 (보험)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>highestDie</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>🔥 벼름 +1 — 약하게 흘리고 다음 한 방을 벼린다</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>6 4 3 2 1</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>slash</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
           <t>onePair</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>원페어</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>clasped_hands</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>맞잡은 손</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>같은 눈 2개 이상 — 피해: 같은 눈들의 합</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>matchedSum</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>❤️ 재생 +1 + 방어도 3</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>❤️ 재생 1 · 🛡 방어 3 · 🔥 벼름 +1</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>5 5 4 2 1</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>slash</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>onePair</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>원페어</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>red_shoes</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>한 켤레 붉은 구두</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>같은 눈 2개 이상 — 피해: 같은 눈들의 합</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>matchedSum</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>🗡️ 힘 +2 (족보 피해 +2, 매 턴 1씩 소멸)</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>5 5 4 2 1</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>slash</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>twoPair</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>투페어</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>twin_sisters</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>쌍둥이 자매</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>서로 다른 눈 2쌍 — 피해: 두 쌍(주사위 4개)의 합 ×1.25 (내림)</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>matchedSum</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>방어도 +5</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>5 5 3 3 1</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>slash2</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>twoPair</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>투페어</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>two_moons</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>두 개의 달</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>서로 다른 눈 2쌍 — 피해: 두 쌍(주사위 4개)의 합 ×1.25 (내림)</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>matchedSum</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>🎯 맞은 적 취약 +2 (받는 피해 +2)</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>5 5 3 3 1</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>slash2</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>threeKind</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>트리플</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>triple_axe</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>세 번 찍는 도끼</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>같은 눈 3개 이상 — 피해: 같은 눈들의 합 ×1.5 (내림)</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>matchedSum</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>🗡️ 힘 +2</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>4 4 4</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>slash2</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>threeKind</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>트리플</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>woodsman_breath</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>나무꾼의 호흡</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>같은 눈 3개 이상 — 피해: 같은 눈들의 합 ×1.5 (내림)</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>matchedSum</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>🔻 맞은 적 약화 +2 (공격력 -2)</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>4 4 4</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr">
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>slash2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>fourKind</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>포카드</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>four_fangs</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>네 개의 송곳니</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>같은 눈 4개 이상 — 피해: 같은 눈들의 합 ×3</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>matchedSum</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>🩸 맞은 적 출혈 +4 (행동마다 피해, 점차 감소)</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>4 4 4 4</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="inlineStr">
-        <is>
-          <t>smash</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
+          <t>threeKind</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>트리플</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>chopping</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>장작 패기</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>같은 눈 3개 이상 — 피해: 같은 눈들의 합 ×1.5 (내림)</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>matchedSum</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>🔥 벼름 +1 · 🗡️ 힘 +1</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>4 4 4</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>slash2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
           <t>fourKind</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>포카드</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>four_fangs</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>네 개의 송곳니</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>같은 눈 4개 이상 — 피해: 같은 눈들의 합 ×3</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>matchedSum</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>🩸 맞은 적 출혈 +4 (행동마다 피해, 점차 감소)</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>4 4 4 4</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>smash</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>fourKind</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>포카드</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>heavy_blow</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>묵직한 일격</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>같은 눈 4개 이상 — 피해: 같은 눈들의 합 ×3</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>matchedSum</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>🗡️ 힘 +3</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>4 4 4 4</t>
         </is>
       </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>smash</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>fourKind</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>포카드</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>hunger</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>굶주림</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>같은 눈 4개 이상 — 피해: 같은 눈들의 합 ×3</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>matchedSum</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>🔥 벼름 +2 — 크게 벼려 다음을 노린다</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>4 4 4 4</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>smash</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>fullHouse</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>풀하우스</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>cottage</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>할머니의 오두막</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>방어도 +15</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>5 5 5 2 2</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>ring</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>fullHouse</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>풀하우스</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>hearth</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>따뜻한 화덕</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
-        </is>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr">
-        <is>
-          <t>❤️ 재생 +2 + 방어도 8</t>
-        </is>
-      </c>
-      <c r="I15" s="12" t="inlineStr">
-        <is>
-          <t>5 5 5 2 2</t>
-        </is>
-      </c>
-      <c r="J15" s="12" t="inlineStr">
-        <is>
-          <t>ring</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>smallStraight</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>스몰 스트레이트</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>windpath</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>바람길</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>연속된 눈 4개(예: 2·3·4·5)면 성립. 모든 적에게 피해 30.</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>🔻 맞은 모든 적 약화 +3</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>2 3 4 5</t>
-        </is>
-      </c>
-      <c r="J16" s="10" t="inlineStr">
-        <is>
-          <t>wave</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>smallStraight</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>스몰 스트레이트</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>hunt_drive</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>몰이사냥</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>연속된 눈 4개(예: 2·3·4·5)면 성립. 모든 적에게 피해 30.</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>방어도 +10</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>2 3 4 5</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>wave</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
+          <t>fullHouse</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>풀하우스</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>hearth</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>따뜻한 화덕</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>❤️ 재생 +2 + 방어도 8</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>5 5 5 2 2</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>ring</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>smallStraight</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>스몰 스트레이트</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>windpath</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>바람길</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>연속된 눈 4개(예: 2·3·4·5)면 성립. 모든 적에게 피해 30.</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>🔻 적 약화 2 · 🔥 벼름 +1</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>2 3 4 5</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>wave</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>smallStraight</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>스몰 스트레이트</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>hunt_drive</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>몰이사냥</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>연속된 눈 4개(예: 2·3·4·5)면 성립. 모든 적에게 피해 30.</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>방어도 +10</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>2 3 4 5</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>wave</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
           <t>largeStraight</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>라지 스트레이트</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>moonpath</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>달빛 오솔길</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>연속된 눈 5개(1~5 또는 2~6)면 성립. 모든 적에게 피해 40.</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>🎯 맞은 모든 적 취약 +3 + 🎲 집중 +1</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>2 3 4 5 6</t>
         </is>
       </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>bigwave</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>largeStraight</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>라지 스트레이트</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>storm_run</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>폭풍 질주</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>epic</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>연속된 눈 5개(1~5 또는 2~6)면 성립. 모든 적에게 피해 40.</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>🗡️ 힘 +4 + 🔻 맞은 모든 적 약화 +2</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
         <is>
           <t>2 3 4 5 6</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>bigwave</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>yahtzee</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>야찌</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>judgment_night</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>심판의 밤</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>epic</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>주사위 5개가 모두 같은 눈이면 성립. 피해 50.</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>🩸 출혈 +6 + 🔻 약화 +4 + 방어도 12</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>6 6 6 6 6</t>
         </is>
       </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>judgment</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>yahtzee</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>야찌</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>blood_moon</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>핏빛 만월</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>epic</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F24" s="15" t="inlineStr">
         <is>
           <t>주사위 5개가 모두 같은 눈이면 성립. 피해 50.</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>🗡️ 힘 +6 + 🩸 출혈 +5</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>6 6 6 6 6</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>judgment</t>
         </is>
@@ -4271,7 +4427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4673,6 +4829,168 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>nail</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>못 주사위</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>1 2 3 4 5 6</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>족보를 확정하면 이 눈이 그대로 새겨져 다음 턴까지 남는다. 다시 굴리면 풀린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>guide</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>길잡이 주사위</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>1 2 3 4 5 6</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>다시 굴리면 무작위가 아니라 눈이 한 칸 올라간다 (6 다음은 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>mirror</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>되비침 주사위</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>1 2 3 4 5 6</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>굴린 직후 그 판에서 가장 많이 나온 눈으로 바뀐다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>spark</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>불티 주사위</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>1 1 2 2 3 3</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>눈은 낮지만, 족보에 안 쓰이면 🔥벼름 +1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>twin</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>쌍눈 주사위</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>2 3 3 4 4 5</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>같은 눈 족보(원페어·트리플·포카드·야찌)에서 자기 눈을 두 번 센다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>chainlink</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>이음 주사위</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>1 2 3 4 5 6</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>굴린 직후 다른 눈과 겹치지 않고 이어지기 좋은 눈으로 바뀐다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4684,7 +5002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5271,7 +5589,7 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>방어도가 턴이 지나도 사라지지 않는다.</t>
+          <t>턴이 지나도 방어도의 절반이 남는다.</t>
         </is>
       </c>
     </row>
@@ -5434,6 +5752,168 @@
       <c r="E29" s="10" t="inlineStr">
         <is>
           <t>야찌 피해 2배.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>whetstone</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>숫돌</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>🪨</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>매 턴 시작 시 🔥벼름 +1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>hunters_eye</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>사냥꾼의 눈</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>👁</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>같은 눈이 3개 이상 나온 판을 확정하면 🔥벼름 +1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>waymark</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>길표</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>🪧</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>스트레이트 족보를 확정하면 다음 턴 리롤 +2 · 🔥벼름 +1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>bears_back</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>곰의 등</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>🐻</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>정예</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>두르고 있는 방어도 10마다 모든 족보 피해 +3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>dried_heart</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>말라붙은 심장</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>🫀</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>정예</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>HP가 3분의 1 이하면 모든 족보 피해 1.5배.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>leech_ring</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>거머리 반지</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>💍</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>정예</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>주사위 때문에 자해할 때마다 🔥벼름 +2.</t>
         </is>
       </c>
     </row>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.30</t>
+          <t>v1.31</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="12">
@@ -740,7 +740,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>9종 · 변형 21개</t>
+          <t>9종 · 변형 25개</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3587,206 +3587,206 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
+          <t>onePair</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>원페어</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>clash</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>맞부딪기</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>같은 눈 2개 이상 — 피해: 같은 눈들의 합</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>matchedSum</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>⚡ 일격 — 쌓아둔 🔥벼름을 전부 태운다</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>5 5 4 2 1</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>slash</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
           <t>twoPair</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>투페어</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>twin_sisters</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>쌍둥이 자매</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>서로 다른 눈 2쌍 — 피해: 두 쌍(주사위 4개)의 합 ×1.25 (내림)</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>matchedSum</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>방어도 +5</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>5 5 3 3 1</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>slash2</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>twoPair</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>투페어</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>two_moons</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>두 개의 달</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>서로 다른 눈 2쌍 — 피해: 두 쌍(주사위 4개)의 합 ×1.25 (내림)</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>matchedSum</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>🎯 맞은 적 취약 +2 (받는 피해 +2)</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>5 5 3 3 1</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>slash2</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>threeKind</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>트리플</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>triple_axe</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>세 번 찍는 도끼</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>common</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>같은 눈 3개 이상 — 피해: 같은 눈들의 합 ×1.5 (내림)</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>matchedSum</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>🗡️ 힘 +2</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>4 4 4</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>slash2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>threeKind</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>트리플</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>woodsman_breath</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>나무꾼의 호흡</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>같은 눈 3개 이상 — 피해: 같은 눈들의 합 ×1.5 (내림)</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>matchedSum</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>🔻 맞은 적 약화 +2 (공격력 -2)</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>4 4 4</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>slash2</t>
         </is>
@@ -3805,116 +3805,116 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
+          <t>woodsman_breath</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>나무꾼의 호흡</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>같은 눈 3개 이상 — 피해: 같은 눈들의 합 ×1.5 (내림)</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>matchedSum</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>🔻 맞은 적 약화 +2 (공격력 -2)</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>4 4 4</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>slash2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>threeKind</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>트리플</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
           <t>chopping</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>장작 패기</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>같은 눈 3개 이상 — 피해: 같은 눈들의 합 ×1.5 (내림)</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>matchedSum</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>🔥 벼름 +1 · 🗡️ 힘 +1</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>4 4 4</t>
         </is>
       </c>
-      <c r="J13" s="10" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>slash2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>fourKind</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>포카드</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>four_fangs</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>네 개의 송곳니</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>같은 눈 4개 이상 — 피해: 같은 눈들의 합 ×3</t>
-        </is>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>matchedSum</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>🩸 맞은 적 출혈 +4 (행동마다 피해, 점차 감소)</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>4 4 4 4</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>smash</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>fourKind</t>
+          <t>threeKind</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>포카드</t>
+          <t>트리플</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>heavy_blow</t>
+          <t>downstroke</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>묵직한 일격</t>
+          <t>내리찍기</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>같은 눈 4개 이상 — 피해: 같은 눈들의 합 ×3</t>
+          <t>같은 눈 3개 이상 — 피해: 같은 눈들의 합 ×1.5 (내림)</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -3932,19 +3932,19 @@
           <t>matchedSum</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>🗡️ 힘 +3</t>
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🗡️ 힘 +1</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>4 4 4 4</t>
+          <t>4 4 4</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>smash</t>
+          <t>slash2</t>
         </is>
       </c>
     </row>
@@ -3961,12 +3961,12 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>hunger</t>
+          <t>four_fangs</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>굶주림</t>
+          <t>네 개의 송곳니</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -3984,9 +3984,9 @@
           <t>matchedSum</t>
         </is>
       </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>🔥 벼름 +2 — 크게 벼려 다음을 노린다</t>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>🩸 맞은 적 출혈 +4 (행동마다 피해, 점차 감소)</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -4003,22 +4003,22 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>fullHouse</t>
+          <t>fourKind</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>풀하우스</t>
+          <t>포카드</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>cottage</t>
+          <t>heavy_blow</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>할머니의 오두막</t>
+          <t>묵직한 일격</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
@@ -4028,49 +4028,49 @@
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
+          <t>같은 눈 4개 이상 — 피해: 같은 눈들의 합 ×3</t>
         </is>
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>방어도 +15</t>
+          <t>matchedSum</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🗡️ 힘 +3</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>5 5 5 2 2</t>
+          <t>4 4 4 4</t>
         </is>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>ring</t>
+          <t>smash</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>fullHouse</t>
+          <t>fourKind</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>풀하우스</t>
+          <t>포카드</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>hearth</t>
+          <t>hunger</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>따뜻한 화덕</t>
+          <t>굶주림</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -4080,49 +4080,49 @@
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
+          <t>같은 눈 4개 이상 — 피해: 같은 눈들의 합 ×3</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>matchedSum</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>❤️ 재생 +2 + 방어도 8</t>
+          <t>🔥 벼름 +2 — 크게 벼려 다음을 노린다</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>5 5 5 2 2</t>
+          <t>4 4 4 4</t>
         </is>
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>ring</t>
+          <t>smash</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>smallStraight</t>
+          <t>fullHouse</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>스몰 스트레이트</t>
+          <t>풀하우스</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>windpath</t>
+          <t>cottage</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>바람길</t>
+          <t>할머니의 오두막</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -4132,285 +4132,493 @@
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>연속된 눈 4개(예: 2·3·4·5)면 성립. 모든 적에게 피해 30.</t>
+          <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
-          <t>🔻 적 약화 2 · 🔥 벼름 +1</t>
+          <t>방어도 +15</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>2 3 4 5</t>
+          <t>5 5 5 2 2</t>
         </is>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>wave</t>
+          <t>ring</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>smallStraight</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>스몰 스트레이트</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>hunt_drive</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>몰이사냥</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>연속된 눈 4개(예: 2·3·4·5)면 성립. 모든 적에게 피해 30.</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>방어도 +10</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>2 3 4 5</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>wave</t>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>fullHouse</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>풀하우스</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>hearth</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>따뜻한 화덕</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>❤️ 재생 +2 + 방어도 8</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>5 5 5 2 2</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>ring</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
+          <t>fullHouse</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>풀하우스</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>wedge</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>쐐기</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🎯 취약 2</t>
+        </is>
+      </c>
+      <c r="I21" s="12" t="inlineStr">
+        <is>
+          <t>5 5 5 2 2</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>ring</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>smallStraight</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>스몰 스트레이트</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>windpath</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>바람길</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>연속된 눈 4개(예: 2·3·4·5)면 성립. 모든 적에게 피해 30.</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>🔻 적 약화 2 · 🔥 벼름 +1</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>2 3 4 5</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>wave</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>smallStraight</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>스몰 스트레이트</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>hunt_drive</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>몰이사냥</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>연속된 눈 4개(예: 2·3·4·5)면 성립. 모든 적에게 피해 30.</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>방어도 +10</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>2 3 4 5</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>wave</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>smallStraight</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>스몰 스트레이트</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>snare</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>덫 놓기</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>연속된 눈 4개(예: 2·3·4·5)면 성립. 모든 적에게 피해 30.</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🔻 적 약화 2</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>2 3 4 5</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>wave</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
           <t>largeStraight</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>라지 스트레이트</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>moonpath</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>달빛 오솔길</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>연속된 눈 5개(1~5 또는 2~6)면 성립. 모든 적에게 피해 40.</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>🎯 맞은 모든 적 취약 +3 + 🎲 집중 +1</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>2 3 4 5 6</t>
         </is>
       </c>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="J25" s="12" t="inlineStr">
         <is>
           <t>bigwave</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>largeStraight</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>라지 스트레이트</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>storm_run</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>폭풍 질주</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>epic</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F26" s="15" t="inlineStr">
         <is>
           <t>연속된 눈 5개(1~5 또는 2~6)면 성립. 모든 적에게 피해 40.</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>🗡️ 힘 +4 + 🔻 맞은 모든 적 약화 +2</t>
-        </is>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🗡️ 힘 +4 · 🔻 약화 2</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
         <is>
           <t>2 3 4 5 6</t>
         </is>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="J26" s="14" t="inlineStr">
         <is>
           <t>bigwave</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>yahtzee</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>야찌</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>judgment_night</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>심판의 밤</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>epic</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F27" s="15" t="inlineStr">
         <is>
           <t>주사위 5개가 모두 같은 눈이면 성립. 피해 50.</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>🩸 출혈 +6 + 🔻 약화 +4 + 방어도 12</t>
-        </is>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🩸 출혈 6 · 🔻 약화 4 · 🛡 방어 12</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
         <is>
           <t>6 6 6 6 6</t>
         </is>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="J27" s="14" t="inlineStr">
         <is>
           <t>judgment</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>yahtzee</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>야찌</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>blood_moon</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>핏빛 만월</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>epic</t>
         </is>
       </c>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="F28" s="15" t="inlineStr">
         <is>
           <t>주사위 5개가 모두 같은 눈이면 성립. 피해 50.</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H28" s="14" t="inlineStr">
         <is>
           <t>🗡️ 힘 +6 + 🩸 출혈 +5</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
         <is>
           <t>6 6 6 6 6</t>
         </is>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="J28" s="14" t="inlineStr">
         <is>
           <t>judgment</t>
         </is>
@@ -6053,7 +6261,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>35~39</t>
+          <t>34~38</t>
         </is>
       </c>
       <c r="G4" s="8" t="n">
@@ -6114,7 +6322,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>42~46</t>
+          <t>41~45</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
@@ -6175,7 +6383,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>38~42</t>
+          <t>37~41</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
@@ -6236,7 +6444,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>45~49</t>
+          <t>44~48</t>
         </is>
       </c>
       <c r="G7" s="8" t="n">
@@ -6297,7 +6505,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>71</t>
         </is>
       </c>
       <c r="G8" s="10" t="n">
@@ -6358,7 +6566,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G9" s="16" t="n">
@@ -6419,7 +6627,7 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>33~38</t>
+          <t>32~37</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
@@ -6480,7 +6688,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>30~33</t>
+          <t>29~32</t>
         </is>
       </c>
       <c r="G11" s="8" t="n">
@@ -6541,7 +6749,7 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G12" s="10" t="n">
@@ -6602,7 +6810,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G13" s="16" t="n">
@@ -6663,7 +6871,7 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>31~36</t>
+          <t>30~35</t>
         </is>
       </c>
       <c r="G14" s="8" t="n">
@@ -6724,7 +6932,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>36~40</t>
+          <t>35~39</t>
         </is>
       </c>
       <c r="G15" s="8" t="n">
@@ -6785,7 +6993,7 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>53~58</t>
+          <t>51~56</t>
         </is>
       </c>
       <c r="G16" s="8" t="n">
@@ -6846,7 +7054,7 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G17" s="10" t="n">
@@ -6907,7 +7115,7 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>119</t>
         </is>
       </c>
       <c r="G18" s="16" t="n">
@@ -6968,7 +7176,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>38~42</t>
+          <t>37~41</t>
         </is>
       </c>
       <c r="G19" s="8" t="n">
@@ -7029,7 +7237,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>27~31</t>
+          <t>26~30</t>
         </is>
       </c>
       <c r="G20" s="8" t="n">
@@ -7090,7 +7298,7 @@
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G21" s="10" t="n">
@@ -7151,7 +7359,7 @@
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>125</t>
         </is>
       </c>
       <c r="G22" s="16" t="n">
@@ -7212,7 +7420,7 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>35~39</t>
+          <t>34~38</t>
         </is>
       </c>
       <c r="G23" s="8" t="n">
@@ -7273,7 +7481,7 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>31~36</t>
+          <t>30~35</t>
         </is>
       </c>
       <c r="G24" s="8" t="n">
@@ -7334,7 +7542,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>40~44</t>
+          <t>39~43</t>
         </is>
       </c>
       <c r="G25" s="8" t="n">
@@ -7395,7 +7603,7 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G26" s="10" t="n">
@@ -7456,7 +7664,7 @@
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>121</t>
         </is>
       </c>
       <c r="G27" s="16" t="n">
@@ -7517,7 +7725,7 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>38~42</t>
+          <t>37~41</t>
         </is>
       </c>
       <c r="G28" s="8" t="n">
@@ -7578,7 +7786,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>33~37</t>
+          <t>32~36</t>
         </is>
       </c>
       <c r="G29" s="8" t="n">
@@ -7639,7 +7847,7 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G30" s="10" t="n">
@@ -7700,7 +7908,7 @@
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>127</t>
         </is>
       </c>
       <c r="G31" s="16" t="n">
@@ -7761,7 +7969,7 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>36~40</t>
+          <t>35~39</t>
         </is>
       </c>
       <c r="G32" s="8" t="n">
@@ -7822,7 +8030,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>31~36</t>
+          <t>30~35</t>
         </is>
       </c>
       <c r="G33" s="8" t="n">
@@ -7883,7 +8091,7 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>33~38</t>
+          <t>32~37</t>
         </is>
       </c>
       <c r="G34" s="8" t="n">
@@ -7944,7 +8152,7 @@
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>79</t>
         </is>
       </c>
       <c r="G35" s="10" t="n">
@@ -8005,7 +8213,7 @@
       </c>
       <c r="F36" s="16" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>130</t>
         </is>
       </c>
       <c r="G36" s="16" t="n">
@@ -8066,7 +8274,7 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>38~42</t>
+          <t>37~41</t>
         </is>
       </c>
       <c r="G37" s="8" t="n">
@@ -8127,7 +8335,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>36~40</t>
+          <t>35~39</t>
         </is>
       </c>
       <c r="G38" s="8" t="n">
@@ -8188,7 +8396,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>44~48</t>
+          <t>43~47</t>
         </is>
       </c>
       <c r="G39" s="8" t="n">
@@ -8249,7 +8457,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>82</t>
         </is>
       </c>
       <c r="G40" s="10" t="n">
@@ -8310,7 +8518,7 @@
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G41" s="16" t="n">
@@ -8371,7 +8579,7 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>38~42</t>
+          <t>37~41</t>
         </is>
       </c>
       <c r="G42" s="8" t="n">
@@ -8432,7 +8640,7 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>33~38</t>
+          <t>32~37</t>
         </is>
       </c>
       <c r="G43" s="8" t="n">
@@ -8493,7 +8701,7 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>31~36</t>
+          <t>30~35</t>
         </is>
       </c>
       <c r="G44" s="8" t="n">
@@ -8554,7 +8762,7 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="G45" s="10" t="n">
@@ -8615,7 +8823,7 @@
       </c>
       <c r="F46" s="16" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>127</t>
         </is>
       </c>
       <c r="G46" s="16" t="n">
@@ -11614,7 +11822,7 @@
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
-          <t>ward 46</t>
+          <t>ward 80</t>
         </is>
       </c>
       <c r="F69" s="16" t="inlineStr">
@@ -13634,7 +13842,7 @@
       </c>
       <c r="E117" s="10" t="inlineStr">
         <is>
-          <t>ward 24</t>
+          <t>ward 40</t>
         </is>
       </c>
       <c r="F117" s="10" t="inlineStr">
@@ -15890,7 +16098,7 @@
       </c>
       <c r="E170" s="10" t="inlineStr">
         <is>
-          <t>ward 22</t>
+          <t>ward 36</t>
         </is>
       </c>
       <c r="F170" s="10" t="inlineStr">
@@ -16182,7 +16390,7 @@
       </c>
       <c r="E177" s="16" t="inlineStr">
         <is>
-          <t>ward 48</t>
+          <t>ward 85</t>
         </is>
       </c>
       <c r="F177" s="16" t="inlineStr">
@@ -20693,7 +20901,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>노페어=떠돌이의 직감 · 포카드=묵직한 일격 · 투페어=쌍둥이 자매</t>
+          <t>노페어=숨 고르기 · 포카드=묵직한 일격 · 투페어=쌍둥이 자매</t>
         </is>
       </c>
     </row>
@@ -20720,7 +20928,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>노페어=떠돌이의 직감 · 트리플=세 번 찍는 도끼 · 스몰 스트레이트=몰이사냥</t>
+          <t>노페어=떠돌이의 직감 · 트리플=장작 패기 · 원페어=맞부딪기</t>
         </is>
       </c>
     </row>
@@ -20747,7 +20955,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>노페어=숲의 속삭임 · 풀하우스=할머니의 오두막 · 원페어=맞잡은 손</t>
+          <t>노페어=숨 고르기 · 풀하우스=할머니의 오두막 · 원페어=맞부딪기</t>
         </is>
       </c>
     </row>
@@ -20774,7 +20982,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>노페어=떠돌이의 직감 · 투페어=쌍둥이 자매 · 트리플=나무꾼의 호흡</t>
+          <t>노페어=떠돌이의 직감 · 원페어=맞잡은 손 · 트리플=내리찍기</t>
         </is>
       </c>
     </row>
@@ -20801,7 +21009,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>노페어=떠돌이의 직감 · 투페어=두 개의 달 · 스몰 스트레이트=바람길</t>
+          <t>노페어=떠돌이의 직감 · 스몰 스트레이트=바람길 · 원페어=맞부딪기</t>
         </is>
       </c>
     </row>
@@ -20828,7 +21036,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>노페어=숲의 속삭임 · 원페어=한 켤레 붉은 구두 · 트리플=세 번 찍는 도끼</t>
+          <t>노페어=숨 고르기 · 원페어=한 켤레 붉은 구두 · 트리플=내리찍기</t>
         </is>
       </c>
     </row>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.31</t>
+          <t>v1.32</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>피해 3 ×2타</t>
+          <t>피해 4 ×2타</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>혼란 2칸</t>
+          <t>혼란 3칸</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>피해 8 · 혼란 1</t>
+          <t>피해 9 · 혼란 1</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>피해 10</t>
+          <t>피해 11</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>피해 12 · 회복 5</t>
+          <t>피해 14 · 회복 5</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>독 2칸 · 피해 5</t>
+          <t>독 3칸 · 피해 5</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>포박 2칸</t>
+          <t>포박 3칸</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>독 5칸 · 피해 5</t>
+          <t>독 4칸 · 피해 5</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>피해 9 · 혼란 1</t>
+          <t>피해 11 · 혼란 1</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>피해 11 · 포박 2칸</t>
+          <t>피해 12 · 포박 3칸</t>
         </is>
       </c>
       <c r="F21" s="8" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>피해 10 · 방어 6</t>
+          <t>피해 12 · 방어 6</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>피해 5 ×3타 · 출혈 5칸</t>
+          <t>피해 5 ×3타 · 출혈 3칸</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>출혈 5칸</t>
+          <t>출혈 3칸</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>demand 16</t>
+          <t>demand 18 · 출혈 3칸</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>피해 19 · 힘 2</t>
+          <t>피해 24 · 힘 2</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>22 → unique1</t>
+          <t>29 → unique1</t>
         </is>
       </c>
       <c r="K32" s="16" t="inlineStr"/>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="E33" s="16" t="inlineStr">
         <is>
-          <t>피해 17</t>
+          <t>피해 18</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="E34" s="16" t="inlineStr">
         <is>
-          <t>피해 5 · 출혈 5칸</t>
+          <t>피해 5 · 출혈 4칸</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="E36" s="16" t="inlineStr">
         <is>
-          <t>demand 22</t>
+          <t>demand 40 · 출혈 4칸</t>
         </is>
       </c>
       <c r="F36" s="16" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
-          <t>출혈 5칸</t>
+          <t>출혈 4칸</t>
         </is>
       </c>
       <c r="F38" s="16" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
-          <t>피해 19 · 힘 2</t>
+          <t>피해 25 · 힘 2</t>
         </is>
       </c>
       <c r="F39" s="16" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>방어 6 · 혼란 2칸</t>
+          <t>방어 6 · 혼란 3칸</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>피해 20 · 혼란 5칸</t>
+          <t>피해 22 · 혼란 3칸</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>피해 8 · 혼란 1</t>
+          <t>피해 9 · 혼란 1</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -10817,7 +10817,7 @@
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>20 → unique1</t>
+          <t>24 → unique1</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr"/>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>5 → unique1</t>
+          <t>6 → unique1</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr"/>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>피해 7 · 회복 8</t>
+          <t>피해 8 · 회복 8</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="J53" s="10" t="inlineStr">
         <is>
-          <t>11 → unique1</t>
+          <t>14 → unique1</t>
         </is>
       </c>
       <c r="K53" s="10" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>기절 1칸 · 힘 2</t>
+          <t>기절 2칸 · 힘 2</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>cap 22</t>
+          <t>cap 22 · 기절 2칸</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>피해 21</t>
+          <t>피해 22</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>피해 21</t>
+          <t>피해 26</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t>기절 1칸</t>
+          <t>기절 3칸</t>
         </is>
       </c>
       <c r="F58" s="16" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>33 → unique1</t>
+          <t>43 → unique1</t>
         </is>
       </c>
       <c r="K59" s="16" t="inlineStr"/>
@@ -11477,7 +11477,7 @@
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>22 → unique1</t>
+          <t>29 → unique1</t>
         </is>
       </c>
       <c r="K61" s="16" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
-          <t>피해 22</t>
+          <t>피해 24</t>
         </is>
       </c>
       <c r="F62" s="16" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
-          <t>기절 2칸</t>
+          <t>기절 3칸</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
@@ -11605,7 +11605,7 @@
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>39 → unique1</t>
+          <t>51 → unique1</t>
         </is>
       </c>
       <c r="K64" s="16" t="inlineStr"/>
@@ -11653,7 +11653,7 @@
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>27 → unique1</t>
+          <t>35 → unique1</t>
         </is>
       </c>
       <c r="K65" s="16" t="inlineStr"/>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>44 → unique1</t>
+          <t>57 → unique1</t>
         </is>
       </c>
       <c r="K67" s="16" t="inlineStr"/>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>33 → unique1</t>
+          <t>43 → unique1</t>
         </is>
       </c>
       <c r="K68" s="16" t="inlineStr"/>
@@ -11822,7 +11822,7 @@
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
-          <t>ward 80</t>
+          <t>ward 80 · 기절 3칸</t>
         </is>
       </c>
       <c r="F69" s="16" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
-          <t>기절 1칸</t>
+          <t>기절 3칸</t>
         </is>
       </c>
       <c r="F70" s="16" t="inlineStr">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
-          <t>피해 15 · 혼란 1</t>
+          <t>피해 20 · 혼란 1</t>
         </is>
       </c>
       <c r="F73" s="16" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>피해 9</t>
+          <t>피해 11</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>혼란 1</t>
+          <t>혼란 2</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -12410,7 +12410,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>피해 11</t>
+          <t>피해 13</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>피해 14</t>
+          <t>피해 15</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>피해 13 · 방어 8</t>
+          <t>피해 15 · 방어 8</t>
         </is>
       </c>
       <c r="F89" s="8" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>피해 16</t>
+          <t>피해 17</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>drainWhet 0 · 힘 4</t>
+          <t>drainWhet 0 · 힘 4 · 혼란 3칸</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>피해 19 · 혼란 1</t>
+          <t>피해 24 · 혼란 1</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="E96" s="16" t="inlineStr">
         <is>
-          <t>피해 12</t>
+          <t>피해 13</t>
         </is>
       </c>
       <c r="F96" s="16" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="E97" s="16" t="inlineStr">
         <is>
-          <t>저주 1칸 · 힘 2</t>
+          <t>저주 3칸 · 힘 2</t>
         </is>
       </c>
       <c r="F97" s="16" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="E98" s="16" t="inlineStr">
         <is>
-          <t>피해 19</t>
+          <t>피해 21</t>
         </is>
       </c>
       <c r="F98" s="16" t="inlineStr">
@@ -13170,7 +13170,7 @@
       </c>
       <c r="E101" s="16" t="inlineStr">
         <is>
-          <t>drainWhet 0 · 저주 1칸</t>
+          <t>drainWhet 0 · 저주 3칸</t>
         </is>
       </c>
       <c r="F101" s="16" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="E102" s="16" t="inlineStr">
         <is>
-          <t>피해 15 · 힘 2</t>
+          <t>피해 20 · 힘 2</t>
         </is>
       </c>
       <c r="F102" s="16" t="inlineStr">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>피해 12 · 회복 5</t>
+          <t>피해 14 · 회복 5</t>
         </is>
       </c>
       <c r="F107" s="8" t="inlineStr">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>혼란 1</t>
+          <t>혼란 2</t>
         </is>
       </c>
       <c r="F109" s="8" t="inlineStr">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>피해 7 · 혼란 1</t>
+          <t>피해 8 · 혼란 1</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>방어 12 · 결속 2칸</t>
+          <t>방어 12 · 결속 3칸</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="E115" s="10" t="inlineStr">
         <is>
-          <t>피해 15 · 혼란 1</t>
+          <t>피해 16 · 혼란 2</t>
         </is>
       </c>
       <c r="F115" s="10" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="E117" s="10" t="inlineStr">
         <is>
-          <t>ward 40</t>
+          <t>ward 40 · 결속 3칸</t>
         </is>
       </c>
       <c r="F117" s="10" t="inlineStr">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>피해 20 · 혼란 1</t>
+          <t>피해 25 · 혼란 1</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="E119" s="16" t="inlineStr">
         <is>
-          <t>피해 13</t>
+          <t>피해 14</t>
         </is>
       </c>
       <c r="F119" s="16" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="E120" s="16" t="inlineStr">
         <is>
-          <t>방어 12 · 포박 1칸</t>
+          <t>방어 12 · 포박 3칸</t>
         </is>
       </c>
       <c r="F120" s="16" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="E121" s="16" t="inlineStr">
         <is>
-          <t>피해 20</t>
+          <t>피해 22</t>
         </is>
       </c>
       <c r="F121" s="16" t="inlineStr">
@@ -14138,7 +14138,7 @@
       </c>
       <c r="E124" s="16" t="inlineStr">
         <is>
-          <t>demand 24</t>
+          <t>demand 40 · 포박 3칸</t>
         </is>
       </c>
       <c r="F124" s="16" t="inlineStr">
@@ -14180,7 +14180,7 @@
       </c>
       <c r="E125" s="16" t="inlineStr">
         <is>
-          <t>피해 17 · 회복 8</t>
+          <t>피해 22 · 회복 8</t>
         </is>
       </c>
       <c r="F125" s="16" t="inlineStr">
@@ -14310,7 +14310,7 @@
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>피해 8 · 혼란 1</t>
+          <t>피해 8 · 혼란 2</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr">
@@ -14394,7 +14394,7 @@
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>피해 11 · 혼란 1</t>
+          <t>피해 13 · 혼란 1</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>피해 15</t>
+          <t>피해 16</t>
         </is>
       </c>
       <c r="F133" s="8" t="inlineStr">
@@ -14618,7 +14618,7 @@
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>피해 30</t>
+          <t>피해 32</t>
         </is>
       </c>
       <c r="F135" s="8" t="inlineStr">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>피해 11 · 혼란 1</t>
+          <t>피해 13 · 혼란 1</t>
         </is>
       </c>
       <c r="F137" s="8" t="inlineStr">
@@ -14836,7 +14836,7 @@
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>피해 12</t>
+          <t>피해 13</t>
         </is>
       </c>
       <c r="F140" s="8" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>피해 14</t>
+          <t>피해 17</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="E147" s="10" t="inlineStr">
         <is>
-          <t>demand 18</t>
+          <t>demand 18 · 포박 2칸</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="E148" s="10" t="inlineStr">
         <is>
-          <t>피해 23</t>
+          <t>피해 29</t>
         </is>
       </c>
       <c r="F148" s="10" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="E149" s="16" t="inlineStr">
         <is>
-          <t>피해 12 · 혼란 2칸</t>
+          <t>피해 13 · 혼란 3칸</t>
         </is>
       </c>
       <c r="F149" s="16" t="inlineStr">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="E151" s="16" t="inlineStr">
         <is>
-          <t>피해 19</t>
+          <t>피해 21</t>
         </is>
       </c>
       <c r="F151" s="16" t="inlineStr">
@@ -15340,7 +15340,7 @@
       </c>
       <c r="E152" s="16" t="inlineStr">
         <is>
-          <t>혼란 2칸 · 힘 2</t>
+          <t>혼란 3칸 · 힘 2</t>
         </is>
       </c>
       <c r="F152" s="16" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="E154" s="16" t="inlineStr">
         <is>
-          <t>unpin · 혼란 2칸</t>
+          <t>unpin · 혼란 3칸</t>
         </is>
       </c>
       <c r="F154" s="16" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="E155" s="16" t="inlineStr">
         <is>
-          <t>피해 15 · 혼란 2</t>
+          <t>피해 20 · 혼란 2</t>
         </is>
       </c>
       <c r="F155" s="16" t="inlineStr">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>피해 10</t>
+          <t>피해 11</t>
         </is>
       </c>
       <c r="F158" s="8" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>피해 13 · 방어 6</t>
+          <t>피해 15 · 방어 6</t>
         </is>
       </c>
       <c r="F160" s="8" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>피해 11</t>
+          <t>피해 12</t>
         </is>
       </c>
       <c r="F163" s="8" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>피해 12 · 회복 6</t>
+          <t>피해 14 · 회복 6</t>
         </is>
       </c>
       <c r="F165" s="8" t="inlineStr">
@@ -15970,7 +15970,7 @@
       </c>
       <c r="E167" s="10" t="inlineStr">
         <is>
-          <t>혼란 2</t>
+          <t>혼란 3</t>
         </is>
       </c>
       <c r="F167" s="10" t="inlineStr">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="E168" s="10" t="inlineStr">
         <is>
-          <t>피해 16 · 부패 폭발12 1칸</t>
+          <t>피해 17 · 부패 폭발12 2칸</t>
         </is>
       </c>
       <c r="F168" s="10" t="inlineStr">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="E170" s="10" t="inlineStr">
         <is>
-          <t>ward 36</t>
+          <t>ward 36 · 부패 폭발10 2칸</t>
         </is>
       </c>
       <c r="F170" s="10" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="E171" s="10" t="inlineStr">
         <is>
-          <t>피해 18 · 힘 3</t>
+          <t>피해 22 · 힘 3</t>
         </is>
       </c>
       <c r="F171" s="10" t="inlineStr">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="E172" s="16" t="inlineStr">
         <is>
-          <t>피해 13</t>
+          <t>피해 14</t>
         </is>
       </c>
       <c r="F172" s="16" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="E174" s="16" t="inlineStr">
         <is>
-          <t>피해 17</t>
+          <t>피해 18</t>
         </is>
       </c>
       <c r="F174" s="16" t="inlineStr">
@@ -16308,7 +16308,7 @@
       </c>
       <c r="E175" s="16" t="inlineStr">
         <is>
-          <t>독 2칸 · 회복 10</t>
+          <t>독 4칸 · 회복 10</t>
         </is>
       </c>
       <c r="F175" s="16" t="inlineStr">
@@ -16390,7 +16390,7 @@
       </c>
       <c r="E177" s="16" t="inlineStr">
         <is>
-          <t>ward 85</t>
+          <t>ward 85 · 독 3칸</t>
         </is>
       </c>
       <c r="F177" s="16" t="inlineStr">
@@ -16432,7 +16432,7 @@
       </c>
       <c r="E178" s="16" t="inlineStr">
         <is>
-          <t>피해 17 · 힘 3</t>
+          <t>피해 22 · 힘 3</t>
         </is>
       </c>
       <c r="F178" s="16" t="inlineStr">
@@ -16558,7 +16558,7 @@
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>피해 9 · 혼란 1</t>
+          <t>피해 10 · 혼란 2</t>
         </is>
       </c>
       <c r="F181" s="8" t="inlineStr">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>피해 13</t>
+          <t>피해 15</t>
         </is>
       </c>
       <c r="F183" s="8" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>혼란 2</t>
+          <t>혼란 3</t>
         </is>
       </c>
       <c r="F184" s="8" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>피해 10</t>
+          <t>피해 11</t>
         </is>
       </c>
       <c r="F185" s="8" t="inlineStr">
@@ -16856,7 +16856,7 @@
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>피해 11 · 혼란 2</t>
+          <t>피해 13 · 혼란 2</t>
         </is>
       </c>
       <c r="F188" s="8" t="inlineStr">
@@ -16898,7 +16898,7 @@
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>혼란 1</t>
+          <t>혼란 2</t>
         </is>
       </c>
       <c r="F189" s="8" t="inlineStr">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>피해 10 · 회복 8</t>
+          <t>피해 12 · 회복 8</t>
         </is>
       </c>
       <c r="F193" s="8" t="inlineStr">
@@ -17108,7 +17108,7 @@
       </c>
       <c r="E194" s="10" t="inlineStr">
         <is>
-          <t>혼란 2</t>
+          <t>혼란 3</t>
         </is>
       </c>
       <c r="F194" s="10" t="inlineStr">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="E195" s="10" t="inlineStr">
         <is>
-          <t>피해 14 · 마비 1칸</t>
+          <t>피해 14 · 마비 2칸</t>
         </is>
       </c>
       <c r="F195" s="10" t="inlineStr">
@@ -17316,7 +17316,7 @@
       </c>
       <c r="E199" s="10" t="inlineStr">
         <is>
-          <t>unpin · 혼란 2</t>
+          <t>unpin · 혼란 3 · 마비 2칸</t>
         </is>
       </c>
       <c r="F199" s="10" t="inlineStr">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="E200" s="10" t="inlineStr">
         <is>
-          <t>피해 21 · 혼란 2</t>
+          <t>피해 26 · 혼란 2</t>
         </is>
       </c>
       <c r="F200" s="10" t="inlineStr">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="E201" s="16" t="inlineStr">
         <is>
-          <t>피해 14</t>
+          <t>피해 15</t>
         </is>
       </c>
       <c r="F201" s="16" t="inlineStr">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="E203" s="16" t="inlineStr">
         <is>
-          <t>피해 21</t>
+          <t>피해 22</t>
         </is>
       </c>
       <c r="F203" s="16" t="inlineStr">
@@ -17530,7 +17530,7 @@
       </c>
       <c r="E204" s="16" t="inlineStr">
         <is>
-          <t>봉인 1칸 · 회복 12</t>
+          <t>봉인 3칸 · 회복 12</t>
         </is>
       </c>
       <c r="F204" s="16" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="E206" s="16" t="inlineStr">
         <is>
-          <t>demand 24</t>
+          <t>demand 40 · 봉인 3칸</t>
         </is>
       </c>
       <c r="F206" s="16" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="E207" s="16" t="inlineStr">
         <is>
-          <t>피해 19 · 혼란 2</t>
+          <t>피해 25 · 혼란 2</t>
         </is>
       </c>
       <c r="F207" s="16" t="inlineStr">
@@ -17696,7 +17696,7 @@
       </c>
       <c r="E208" s="8" t="inlineStr">
         <is>
-          <t>혼란 1 · 힘 2</t>
+          <t>혼란 2 · 힘 2</t>
         </is>
       </c>
       <c r="F208" s="8" t="inlineStr">
@@ -17784,7 +17784,7 @@
       </c>
       <c r="E210" s="8" t="inlineStr">
         <is>
-          <t>피해 11</t>
+          <t>피해 12</t>
         </is>
       </c>
       <c r="F210" s="8" t="inlineStr">
@@ -17868,7 +17868,7 @@
       </c>
       <c r="E212" s="8" t="inlineStr">
         <is>
-          <t>피해 13 · 힘 3</t>
+          <t>피해 15 · 힘 3</t>
         </is>
       </c>
       <c r="F212" s="8" t="inlineStr">
@@ -17998,7 +17998,7 @@
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>피해 13</t>
+          <t>피해 14</t>
         </is>
       </c>
       <c r="F215" s="8" t="inlineStr">
@@ -18082,7 +18082,7 @@
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>피해 11 · 회복 10</t>
+          <t>피해 13 · 회복 10</t>
         </is>
       </c>
       <c r="F217" s="8" t="inlineStr">
@@ -18124,7 +18124,7 @@
       </c>
       <c r="E218" s="8" t="inlineStr">
         <is>
-          <t>피해 7 · 혼란 1</t>
+          <t>피해 7 · 혼란 2</t>
         </is>
       </c>
       <c r="F218" s="8" t="inlineStr">
@@ -18208,7 +18208,7 @@
       </c>
       <c r="E220" s="8" t="inlineStr">
         <is>
-          <t>피해 12</t>
+          <t>피해 13</t>
         </is>
       </c>
       <c r="F220" s="8" t="inlineStr">
@@ -18292,7 +18292,7 @@
       </c>
       <c r="E222" s="8" t="inlineStr">
         <is>
-          <t>피해 13 · 혼란 2</t>
+          <t>피해 15 · 혼란 2</t>
         </is>
       </c>
       <c r="F222" s="8" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="E224" s="10" t="inlineStr">
         <is>
-          <t>피해 9 · 혼란 1</t>
+          <t>피해 10 · 혼란 2</t>
         </is>
       </c>
       <c r="F224" s="10" t="inlineStr">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="E226" s="10" t="inlineStr">
         <is>
-          <t>피해 19</t>
+          <t>피해 20</t>
         </is>
       </c>
       <c r="F226" s="10" t="inlineStr">
@@ -18542,7 +18542,7 @@
       </c>
       <c r="E228" s="10" t="inlineStr">
         <is>
-          <t>demand 20</t>
+          <t>demand 18 · 포박 3칸</t>
         </is>
       </c>
       <c r="F228" s="10" t="inlineStr">
@@ -18584,7 +18584,7 @@
       </c>
       <c r="E229" s="10" t="inlineStr">
         <is>
-          <t>피해 23</t>
+          <t>피해 29</t>
         </is>
       </c>
       <c r="F229" s="10" t="inlineStr">
@@ -18626,7 +18626,7 @@
       </c>
       <c r="E230" s="16" t="inlineStr">
         <is>
-          <t>피해 14</t>
+          <t>피해 15</t>
         </is>
       </c>
       <c r="F230" s="16" t="inlineStr">
@@ -18710,7 +18710,7 @@
       </c>
       <c r="E232" s="16" t="inlineStr">
         <is>
-          <t>잠식 1칸 · 방어 12</t>
+          <t>잠식 3칸 · 방어 12</t>
         </is>
       </c>
       <c r="F232" s="16" t="inlineStr">
@@ -18750,7 +18750,7 @@
       </c>
       <c r="E233" s="16" t="inlineStr">
         <is>
-          <t>피해 23</t>
+          <t>피해 25</t>
         </is>
       </c>
       <c r="F233" s="16" t="inlineStr">
@@ -18834,7 +18834,7 @@
       </c>
       <c r="E235" s="16" t="inlineStr">
         <is>
-          <t>cap 38</t>
+          <t>cap 38 · 잠식 2칸</t>
         </is>
       </c>
       <c r="F235" s="16" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="E236" s="16" t="inlineStr">
         <is>
-          <t>피해 20 · 힘 4</t>
+          <t>피해 26 · 힘 4</t>
         </is>
       </c>
       <c r="F236" s="16" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>혼란 1</t>
+          <t>혼란 2</t>
         </is>
       </c>
       <c r="F237" s="8" t="inlineStr">
@@ -19086,7 +19086,7 @@
       </c>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>피해 12 · 혼란 1</t>
+          <t>피해 14 · 혼란 1</t>
         </is>
       </c>
       <c r="F241" s="8" t="inlineStr">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="E242" s="8" t="inlineStr">
         <is>
-          <t>피해 6 · 혼란 1</t>
+          <t>피해 6 · 혼란 2</t>
         </is>
       </c>
       <c r="F242" s="8" t="inlineStr">
@@ -19168,7 +19168,7 @@
       </c>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>피해 10</t>
+          <t>피해 11</t>
         </is>
       </c>
       <c r="F243" s="8" t="inlineStr">
@@ -19300,7 +19300,7 @@
       </c>
       <c r="E246" s="8" t="inlineStr">
         <is>
-          <t>피해 13</t>
+          <t>피해 15</t>
         </is>
       </c>
       <c r="F246" s="8" t="inlineStr">
@@ -19382,7 +19382,7 @@
       </c>
       <c r="E248" s="8" t="inlineStr">
         <is>
-          <t>혼란 1 · 힘 2</t>
+          <t>혼란 2 · 힘 2</t>
         </is>
       </c>
       <c r="F248" s="8" t="inlineStr">
@@ -19426,7 +19426,7 @@
       </c>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>피해 11</t>
+          <t>피해 12</t>
         </is>
       </c>
       <c r="F249" s="8" t="inlineStr">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>피해 12 · 회복 5</t>
+          <t>피해 14 · 회복 5</t>
         </is>
       </c>
       <c r="F251" s="8" t="inlineStr">
@@ -19552,7 +19552,7 @@
       </c>
       <c r="E252" s="10" t="inlineStr">
         <is>
-          <t>피해 12 · 혼란 1</t>
+          <t>피해 12 · 혼란 2</t>
         </is>
       </c>
       <c r="F252" s="10" t="inlineStr">
@@ -19592,7 +19592,7 @@
       </c>
       <c r="E253" s="10" t="inlineStr">
         <is>
-          <t>힘 4 · 약탈 1칸</t>
+          <t>힘 4 · 약탈 2칸</t>
         </is>
       </c>
       <c r="F253" s="10" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="E256" s="10" t="inlineStr">
         <is>
-          <t>cap 20</t>
+          <t>cap 20 · 약탈 2칸</t>
         </is>
       </c>
       <c r="F256" s="10" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="E257" s="10" t="inlineStr">
         <is>
-          <t>피해 22 · 혼란 1</t>
+          <t>피해 27 · 혼란 1</t>
         </is>
       </c>
       <c r="F257" s="10" t="inlineStr">
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E258" s="16" t="inlineStr">
         <is>
-          <t>축복 1칸 · 힘 3</t>
+          <t>축복 3칸 · 힘 3</t>
         </is>
       </c>
       <c r="F258" s="16" t="inlineStr">
@@ -19848,7 +19848,7 @@
       </c>
       <c r="E259" s="16" t="inlineStr">
         <is>
-          <t>피해 15</t>
+          <t>피해 16</t>
         </is>
       </c>
       <c r="F259" s="16" t="inlineStr">
@@ -19936,7 +19936,7 @@
       </c>
       <c r="E261" s="16" t="inlineStr">
         <is>
-          <t>피해 22</t>
+          <t>피해 24</t>
         </is>
       </c>
       <c r="F261" s="16" t="inlineStr">
@@ -20018,9 +20018,9 @@
           <t>겸손을 강요한다</t>
         </is>
       </c>
-      <c r="E263" s="16" t="inlineStr">
-        <is>
-          <t>drainWhet 0 · 축복 1칸</t>
+      <c r="E263" s="17" t="inlineStr">
+        <is>
+          <t>drainWhet 0 · 축복 1칸 · 저주 3칸</t>
         </is>
       </c>
       <c r="F263" s="16" t="inlineStr">
@@ -20062,7 +20062,7 @@
       </c>
       <c r="E264" s="16" t="inlineStr">
         <is>
-          <t>피해 17 · 회복 12</t>
+          <t>피해 22 · 회복 12</t>
         </is>
       </c>
       <c r="F264" s="16" t="inlineStr">

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.32</t>
+          <t>v1.33</t>
         </is>
       </c>
     </row>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.33</t>
+          <t>v1.34</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>34~38</t>
+          <t>37~42</t>
         </is>
       </c>
       <c r="G4" s="8" t="n">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>41~45</t>
+          <t>45~48</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>37~41</t>
+          <t>40~45</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>44~48</t>
+          <t>48~52</t>
         </is>
       </c>
       <c r="G7" s="8" t="n">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G8" s="10" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G9" s="16" t="n">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>32~37</t>
+          <t>35~40</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>29~32</t>
+          <t>31~35</t>
         </is>
       </c>
       <c r="G11" s="8" t="n">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>85</t>
         </is>
       </c>
       <c r="G12" s="10" t="n">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G13" s="16" t="n">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>30~35</t>
+          <t>33~38</t>
         </is>
       </c>
       <c r="G14" s="8" t="n">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>35~39</t>
+          <t>38~43</t>
         </is>
       </c>
       <c r="G15" s="8" t="n">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>51~56</t>
+          <t>55~61</t>
         </is>
       </c>
       <c r="G16" s="8" t="n">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G17" s="10" t="n">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G18" s="16" t="n">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>37~41</t>
+          <t>40~45</t>
         </is>
       </c>
       <c r="G19" s="8" t="n">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>26~30</t>
+          <t>28~33</t>
         </is>
       </c>
       <c r="G20" s="8" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>92</t>
         </is>
       </c>
       <c r="G21" s="10" t="n">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>144</t>
         </is>
       </c>
       <c r="G22" s="16" t="n">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>34~38</t>
+          <t>37~42</t>
         </is>
       </c>
       <c r="G23" s="8" t="n">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>30~35</t>
+          <t>33~38</t>
         </is>
       </c>
       <c r="G24" s="8" t="n">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>39~43</t>
+          <t>43~47</t>
         </is>
       </c>
       <c r="G25" s="8" t="n">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G26" s="10" t="n">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>141</t>
         </is>
       </c>
       <c r="G27" s="16" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>37~41</t>
+          <t>40~45</t>
         </is>
       </c>
       <c r="G28" s="8" t="n">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>32~36</t>
+          <t>35~39</t>
         </is>
       </c>
       <c r="G29" s="8" t="n">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G30" s="10" t="n">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>147</t>
         </is>
       </c>
       <c r="G31" s="16" t="n">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>35~39</t>
+          <t>38~43</t>
         </is>
       </c>
       <c r="G32" s="8" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>30~35</t>
+          <t>33~38</t>
         </is>
       </c>
       <c r="G33" s="8" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>32~37</t>
+          <t>35~40</t>
         </is>
       </c>
       <c r="G34" s="8" t="n">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>90</t>
         </is>
       </c>
       <c r="G35" s="10" t="n">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F36" s="16" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>151</t>
         </is>
       </c>
       <c r="G36" s="16" t="n">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>37~41</t>
+          <t>40~45</t>
         </is>
       </c>
       <c r="G37" s="8" t="n">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>35~39</t>
+          <t>38~43</t>
         </is>
       </c>
       <c r="G38" s="8" t="n">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>43~47</t>
+          <t>47~51</t>
         </is>
       </c>
       <c r="G39" s="8" t="n">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G40" s="10" t="n">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>154</t>
         </is>
       </c>
       <c r="G41" s="16" t="n">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>37~41</t>
+          <t>40~45</t>
         </is>
       </c>
       <c r="G42" s="8" t="n">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>32~37</t>
+          <t>35~40</t>
         </is>
       </c>
       <c r="G43" s="8" t="n">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>30~35</t>
+          <t>33~38</t>
         </is>
       </c>
       <c r="G44" s="8" t="n">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>86</t>
         </is>
       </c>
       <c r="G45" s="10" t="n">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="F46" s="16" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>147</t>
         </is>
       </c>
       <c r="G46" s="16" t="n">

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.34</t>
+          <t>v1.35</t>
         </is>
       </c>
     </row>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.35</t>
+          <t>v1.36</t>
         </is>
       </c>
     </row>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.36</t>
+          <t>v1.37</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>떠돌이의 직감</t>
+          <t>들짐승 눈</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>한 켤레 붉은 구두</t>
+          <t>붉은 구두</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>세 번 찍는 도끼</t>
+          <t>세 번 도끼</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>나무꾼의 호흡</t>
+          <t>나무꾼 숨</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>네 개의 송곳니</t>
+          <t>네 송곳니</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>할머니의 오두막</t>
+          <t>오두막</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -20928,7 +20928,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>노페어=떠돌이의 직감 · 트리플=장작 패기 · 원페어=맞부딪기</t>
+          <t>노페어=들짐승 눈 · 트리플=장작 패기 · 원페어=맞부딪기</t>
         </is>
       </c>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>노페어=숨 고르기 · 풀하우스=할머니의 오두막 · 원페어=맞부딪기</t>
+          <t>노페어=숨 고르기 · 풀하우스=오두막 · 원페어=맞부딪기</t>
         </is>
       </c>
     </row>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>노페어=떠돌이의 직감 · 원페어=맞잡은 손 · 트리플=내리찍기</t>
+          <t>노페어=들짐승 눈 · 원페어=맞잡은 손 · 트리플=내리찍기</t>
         </is>
       </c>
     </row>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>노페어=떠돌이의 직감 · 스몰 스트레이트=바람길 · 원페어=맞부딪기</t>
+          <t>노페어=들짐승 눈 · 스몰 스트레이트=바람길 · 원페어=맞부딪기</t>
         </is>
       </c>
     </row>
@@ -21036,7 +21036,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>노페어=숨 고르기 · 원페어=한 켤레 붉은 구두 · 트리플=내리찍기</t>
+          <t>노페어=숨 고르기 · 원페어=붉은 구두 · 트리플=내리찍기</t>
         </is>
       </c>
     </row>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.37</t>
+          <t>v1.40</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>9종 · 변형 25개</t>
+          <t>8종 · 변형 25개</t>
         </is>
       </c>
     </row>
@@ -4105,522 +4105,522 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>largeStraight</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>스트레이트</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>moonpath</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>달빛 오솔길</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>다섯 눈이 이어진다 — 피해 60 (전체 공격)</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>🎯 맞은 모든 적 취약 +3 + 🎲 집중 +1</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>2 3 4 5 6</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>bigwave</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>largeStraight</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>스트레이트</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>storm_run</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>폭풍 질주</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>다섯 눈이 이어진다 — 피해 60 (전체 공격)</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🗡️ 힘 +4 · 🔻 약화 2</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>2 3 4 5 6</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>bigwave</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>largeStraight</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>스트레이트</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>windpath</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>바람길</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>다섯 눈이 이어진다 — 피해 60 (전체 공격)</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>🔻 적 약화 2 · 🔥 벼름 +1</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>2 3 4 5 6</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>bigwave</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>largeStraight</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>스트레이트</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>hunt_drive</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>몰이사냥</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>다섯 눈이 이어진다 — 피해 60 (전체 공격)</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>방어도 +10</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>2 3 4 5 6</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>bigwave</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>largeStraight</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>스트레이트</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>snare</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>덫 놓기</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>다섯 눈이 이어진다 — 피해 60 (전체 공격)</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🔻 적 약화 2</t>
+        </is>
+      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>2 3 4 5 6</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>bigwave</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>yahtzee</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>야찌</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>judgment_night</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>심판의 밤</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>주사위 5개가 모두 같은 눈이면 성립. 피해 50.</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🩸 출혈 6 · 🔻 약화 4 · 🛡 방어 12</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>6 6 6 6 6</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>judgment</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>yahtzee</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>야찌</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>blood_moon</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>핏빛 만월</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>주사위 5개가 모두 같은 눈이면 성립. 피해 50.</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>🗡️ 힘 +6 + 🩸 출혈 +5</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>6 6 6 6 6</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>judgment</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>fullHouse</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>풀하우스</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>cottage</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>오두막</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>uncommon</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>방어도 +15</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>5 5 5 2 2</t>
         </is>
       </c>
-      <c r="J19" s="10" t="inlineStr">
+      <c r="J26" s="10" t="inlineStr">
         <is>
           <t>ring</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>fullHouse</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>풀하우스</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>hearth</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>따뜻한 화덕</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>❤️ 재생 +2 + 방어도 8</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr">
+      <c r="I27" s="12" t="inlineStr">
         <is>
           <t>5 5 5 2 2</t>
         </is>
       </c>
-      <c r="J20" s="12" t="inlineStr">
+      <c r="J27" s="12" t="inlineStr">
         <is>
           <t>ring</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>fullHouse</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>풀하우스</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>wedge</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>쐐기</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="F21" s="13" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H28" s="13" t="inlineStr">
         <is>
           <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🎯 취약 2</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="I28" s="12" t="inlineStr">
         <is>
           <t>5 5 5 2 2</t>
         </is>
       </c>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="J28" s="12" t="inlineStr">
         <is>
           <t>ring</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>smallStraight</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>스몰 스트레이트</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>windpath</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>바람길</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>연속된 눈 4개(예: 2·3·4·5)면 성립. 모든 적에게 피해 30.</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>🔻 적 약화 2 · 🔥 벼름 +1</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>2 3 4 5</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>wave</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>smallStraight</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>스몰 스트레이트</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>hunt_drive</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>몰이사냥</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>연속된 눈 4개(예: 2·3·4·5)면 성립. 모든 적에게 피해 30.</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>방어도 +10</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>2 3 4 5</t>
-        </is>
-      </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>wave</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>smallStraight</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>스몰 스트레이트</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>snare</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>덫 놓기</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>연속된 눈 4개(예: 2·3·4·5)면 성립. 모든 적에게 피해 30.</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🔻 적 약화 2</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>2 3 4 5</t>
-        </is>
-      </c>
-      <c r="J24" s="12" t="inlineStr">
-        <is>
-          <t>wave</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>largeStraight</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>라지 스트레이트</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>moonpath</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>달빛 오솔길</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>연속된 눈 5개(1~5 또는 2~6)면 성립. 모든 적에게 피해 40.</t>
-        </is>
-      </c>
-      <c r="G25" s="12" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="inlineStr">
-        <is>
-          <t>🎯 맞은 모든 적 취약 +3 + 🎲 집중 +1</t>
-        </is>
-      </c>
-      <c r="I25" s="12" t="inlineStr">
-        <is>
-          <t>2 3 4 5 6</t>
-        </is>
-      </c>
-      <c r="J25" s="12" t="inlineStr">
-        <is>
-          <t>bigwave</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>largeStraight</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>라지 스트레이트</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>storm_run</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>폭풍 질주</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="inlineStr">
-        <is>
-          <t>연속된 눈 5개(1~5 또는 2~6)면 성립. 모든 적에게 피해 40.</t>
-        </is>
-      </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="inlineStr">
-        <is>
-          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🗡️ 힘 +4 · 🔻 약화 2</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>2 3 4 5 6</t>
-        </is>
-      </c>
-      <c r="J26" s="14" t="inlineStr">
-        <is>
-          <t>bigwave</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>yahtzee</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>야찌</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>judgment_night</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>심판의 밤</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="inlineStr">
-        <is>
-          <t>주사위 5개가 모두 같은 눈이면 성립. 피해 50.</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H27" s="15" t="inlineStr">
-        <is>
-          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🩸 출혈 6 · 🔻 약화 4 · 🛡 방어 12</t>
-        </is>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>6 6 6 6 6</t>
-        </is>
-      </c>
-      <c r="J27" s="14" t="inlineStr">
-        <is>
-          <t>judgment</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>yahtzee</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>야찌</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>blood_moon</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>핏빛 만월</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>epic</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="inlineStr">
-        <is>
-          <t>주사위 5개가 모두 같은 눈이면 성립. 피해 50.</t>
-        </is>
-      </c>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H28" s="14" t="inlineStr">
-        <is>
-          <t>🗡️ 힘 +6 + 🩸 출혈 +5</t>
-        </is>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>6 6 6 6 6</t>
-        </is>
-      </c>
-      <c r="J28" s="14" t="inlineStr">
-        <is>
-          <t>judgment</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>스몰 스트레이트 피해 +8.</t>
+          <t>스트레이트 피해 +8.</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>37~42</t>
+          <t>36~41</t>
         </is>
       </c>
       <c r="G4" s="8" t="n">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>45~48</t>
+          <t>44~47</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>40~45</t>
+          <t>39~44</t>
         </is>
       </c>
       <c r="G6" s="8" t="n">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>48~52</t>
+          <t>47~50</t>
         </is>
       </c>
       <c r="G7" s="8" t="n">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>78</t>
         </is>
       </c>
       <c r="G8" s="10" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G9" s="16" t="n">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>35~40</t>
+          <t>34~39</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>31~35</t>
+          <t>30~34</t>
         </is>
       </c>
       <c r="G11" s="8" t="n">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>82</t>
         </is>
       </c>
       <c r="G12" s="10" t="n">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>131</t>
         </is>
       </c>
       <c r="G13" s="16" t="n">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>33~38</t>
+          <t>32~37</t>
         </is>
       </c>
       <c r="G14" s="8" t="n">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>38~43</t>
+          <t>37~42</t>
         </is>
       </c>
       <c r="G15" s="8" t="n">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>55~61</t>
+          <t>54~60</t>
         </is>
       </c>
       <c r="G16" s="8" t="n">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G17" s="10" t="n">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G18" s="16" t="n">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>40~45</t>
+          <t>39~44</t>
         </is>
       </c>
       <c r="G19" s="8" t="n">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>28~33</t>
+          <t>28~32</t>
         </is>
       </c>
       <c r="G20" s="8" t="n">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>89</t>
         </is>
       </c>
       <c r="G21" s="10" t="n">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>139</t>
         </is>
       </c>
       <c r="G22" s="16" t="n">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>37~42</t>
+          <t>36~41</t>
         </is>
       </c>
       <c r="G23" s="8" t="n">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>33~38</t>
+          <t>32~37</t>
         </is>
       </c>
       <c r="G24" s="8" t="n">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>43~47</t>
+          <t>42~46</t>
         </is>
       </c>
       <c r="G25" s="8" t="n">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G26" s="10" t="n">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G27" s="16" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>40~45</t>
+          <t>39~44</t>
         </is>
       </c>
       <c r="G28" s="8" t="n">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>35~39</t>
+          <t>34~38</t>
         </is>
       </c>
       <c r="G29" s="8" t="n">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>87</t>
         </is>
       </c>
       <c r="G30" s="10" t="n">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>142</t>
         </is>
       </c>
       <c r="G31" s="16" t="n">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>38~43</t>
+          <t>37~42</t>
         </is>
       </c>
       <c r="G32" s="8" t="n">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>33~38</t>
+          <t>32~37</t>
         </is>
       </c>
       <c r="G33" s="8" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>35~40</t>
+          <t>34~39</t>
         </is>
       </c>
       <c r="G34" s="8" t="n">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>87</t>
         </is>
       </c>
       <c r="G35" s="10" t="n">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F36" s="16" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>146</t>
         </is>
       </c>
       <c r="G36" s="16" t="n">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>40~45</t>
+          <t>39~44</t>
         </is>
       </c>
       <c r="G37" s="8" t="n">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>38~43</t>
+          <t>37~42</t>
         </is>
       </c>
       <c r="G38" s="8" t="n">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>47~51</t>
+          <t>46~49</t>
         </is>
       </c>
       <c r="G39" s="8" t="n">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>89</t>
         </is>
       </c>
       <c r="G40" s="10" t="n">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>149</t>
         </is>
       </c>
       <c r="G41" s="16" t="n">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>40~45</t>
+          <t>39~44</t>
         </is>
       </c>
       <c r="G42" s="8" t="n">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>35~40</t>
+          <t>34~39</t>
         </is>
       </c>
       <c r="G43" s="8" t="n">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>33~38</t>
+          <t>32~37</t>
         </is>
       </c>
       <c r="G44" s="8" t="n">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>83</t>
         </is>
       </c>
       <c r="G45" s="10" t="n">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="F46" s="16" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>142</t>
         </is>
       </c>
       <c r="G46" s="16" t="n">
@@ -21009,7 +21009,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>노페어=들짐승 눈 · 스몰 스트레이트=바람길 · 원페어=맞부딪기</t>
+          <t>노페어=들짐승 눈 · 원페어=맞부딪기 · 스트레이트=바람길</t>
         </is>
       </c>
     </row>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.40</t>
+          <t>v1.41</t>
         </is>
       </c>
     </row>

--- a/docs/REDHOOD_game_db.xlsx
+++ b/docs/REDHOOD_game_db.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>v1.41</t>
+          <t>v1.42</t>
         </is>
       </c>
     </row>
@@ -3949,128 +3949,128 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>fourKind</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>포카드</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>four_fangs</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>네 송곳니</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>fullHouse</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>풀하우스</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>cottage</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>오두막</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>방어도 +15</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>5 5 5 2 2</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>ring</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>fullHouse</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>풀하우스</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>hearth</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>따뜻한 화덕</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>rare</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>같은 눈 4개 이상 — 피해: 같은 눈들의 합 ×3</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>matchedSum</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>🩸 맞은 적 출혈 +4 (행동마다 피해, 점차 감소)</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>4 4 4 4</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="inlineStr">
-        <is>
-          <t>smash</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>fourKind</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>포카드</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>heavy_blow</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>묵직한 일격</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
-        <is>
-          <t>같은 눈 4개 이상 — 피해: 같은 눈들의 합 ×3</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>matchedSum</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🗡️ 힘 +3</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>4 4 4 4</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>smash</t>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>❤️ 재생 +2 + 방어도 8</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>5 5 5 2 2</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="inlineStr">
+        <is>
+          <t>ring</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>fourKind</t>
+          <t>fullHouse</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>포카드</t>
+          <t>풀하우스</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>hunger</t>
+          <t>wedge</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>굶주림</t>
+          <t>쐐기</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
@@ -4080,27 +4080,27 @@
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>같은 눈 4개 이상 — 피해: 같은 눈들의 합 ×3</t>
+          <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>matchedSum</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>🔥 벼름 +2 — 크게 벼려 다음을 노린다</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🎯 취약 2</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>4 4 4 4</t>
+          <t>5 5 5 2 2</t>
         </is>
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>smash</t>
+          <t>ring</t>
         </is>
       </c>
     </row>
@@ -4365,262 +4365,262 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>fourKind</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>포카드</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>four_fangs</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>네 송곳니</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>같은 눈 4개 이상 — 피해: 같은 눈들의 합 ×3</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>matchedSum</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>🩸 맞은 적 출혈 +4 (행동마다 피해, 점차 감소)</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>4 4 4 4</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>smash</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>fourKind</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>포카드</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>heavy_blow</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>묵직한 일격</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>uncommon</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>같은 눈 4개 이상 — 피해: 같은 눈들의 합 ×3</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>matchedSum</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🗡️ 힘 +3</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>4 4 4 4</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>smash</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>fourKind</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>포카드</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>hunger</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>굶주림</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>같은 눈 4개 이상 — 피해: 같은 눈들의 합 ×3</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>matchedSum</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>🔥 벼름 +2 — 크게 벼려 다음을 노린다</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>4 4 4 4</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>smash</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>yahtzee</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>야찌</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>judgment_night</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>심판의 밤</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>epic</t>
         </is>
       </c>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="F27" s="15" t="inlineStr">
         <is>
           <t>주사위 5개가 모두 같은 눈이면 성립. 피해 50.</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G27" s="14" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="H24" s="15" t="inlineStr">
+      <c r="H27" s="15" t="inlineStr">
         <is>
           <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🩸 출혈 6 · 🔻 약화 4 · 🛡 방어 12</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
+      <c r="I27" s="14" t="inlineStr">
         <is>
           <t>6 6 6 6 6</t>
         </is>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="J27" s="14" t="inlineStr">
         <is>
           <t>judgment</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>yahtzee</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>야찌</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>blood_moon</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>핏빛 만월</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>epic</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="F28" s="15" t="inlineStr">
         <is>
           <t>주사위 5개가 모두 같은 눈이면 성립. 피해 50.</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="G28" s="14" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H28" s="14" t="inlineStr">
         <is>
           <t>🗡️ 힘 +6 + 🩸 출혈 +5</t>
         </is>
       </c>
-      <c r="I25" s="14" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
         <is>
           <t>6 6 6 6 6</t>
         </is>
       </c>
-      <c r="J25" s="14" t="inlineStr">
+      <c r="J28" s="14" t="inlineStr">
         <is>
           <t>judgment</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>fullHouse</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>풀하우스</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>cottage</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>오두막</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>uncommon</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>방어도 +15</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>5 5 5 2 2</t>
-        </is>
-      </c>
-      <c r="J26" s="10" t="inlineStr">
-        <is>
-          <t>ring</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>fullHouse</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>풀하우스</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>hearth</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>따뜻한 화덕</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="inlineStr">
-        <is>
-          <t>❤️ 재생 +2 + 방어도 8</t>
-        </is>
-      </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>5 5 5 2 2</t>
-        </is>
-      </c>
-      <c r="J27" s="12" t="inlineStr">
-        <is>
-          <t>ring</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>fullHouse</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>풀하우스</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>wedge</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>쐐기</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>rare</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="inlineStr">
-        <is>
-          <t>같은 눈 3개 + 다른 같은 눈 2개(예: 5·5·5·2·2)면 성립. 피해 25.</t>
-        </is>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H28" s="13" t="inlineStr">
-        <is>
-          <t>⚡ 일격 — 🔥벼름을 전부 태운다 · 🎯 취약 2</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>5 5 5 2 2</t>
-        </is>
-      </c>
-      <c r="J28" s="12" t="inlineStr">
-        <is>
-          <t>ring</t>
         </is>
       </c>
     </row>
